--- a/database/event/8246/event_8246_evp_summary.xlsx
+++ b/database/event/8246/event_8246_evp_summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVP_Summary_8246" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="EVP_Summary_8246" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>evp_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weighted_evp_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>normalized_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Norm_Group_Score_Scaled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Norm_Playoff_Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Norm_Group_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Raw_Group_Score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Raw_Playoff_Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>group_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>playoff_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_weighted_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_weighted_rounds_played</t>
         </is>
@@ -508,40 +496,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.371</v>
+        <v>5.5513</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9120115165474604</v>
+        <v>2.1353</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5389269249976254</v>
+        <v>1.5695</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9314</v>
+        <v>5.5513</v>
       </c>
       <c r="F2" t="n">
-        <v>5.931361216344049</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>5.5513</v>
       </c>
       <c r="H2" t="n">
-        <v>5.931361216344049</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>11.09241578121484</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>4.2702</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>180</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
-        <v>11.0924</v>
+        <v>4.2702</v>
       </c>
       <c r="N2" t="n">
         <v>180</v>
@@ -550,274 +538,274 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>nota</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.9946</v>
+        <v>4.24</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7672282458479815</v>
+        <v>1.6309</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4371332836195506</v>
+        <v>1.0843</v>
       </c>
       <c r="E3" t="n">
-        <v>4.811</v>
+        <v>4.24</v>
       </c>
       <c r="F3" t="n">
-        <v>4.811033341571402</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="H3" t="n">
-        <v>4.811033341571402</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3.325959169815587</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3.2615</v>
       </c>
       <c r="K3" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="M3" t="n">
-        <v>3.326</v>
+        <v>3.2615</v>
       </c>
       <c r="N3" t="n">
-        <v>46</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>molodoy</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.9409</v>
+        <v>4.2395</v>
       </c>
       <c r="C4" t="n">
-        <v>0.74657239665414</v>
+        <v>1.6307</v>
       </c>
       <c r="D4" t="n">
-        <v>0.423180000131841</v>
+        <v>1.0841</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6575</v>
+        <v>4.2395</v>
       </c>
       <c r="F4" t="n">
-        <v>4.657465277552297</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>4.2395</v>
       </c>
       <c r="H4" t="n">
-        <v>4.657465277552297</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>4.742146464416884</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>3.2612</v>
       </c>
       <c r="K4" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7421</v>
+        <v>3.2612</v>
       </c>
       <c r="N4" t="n">
-        <v>98</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.8516</v>
+        <v>3.7284</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7122229118681053</v>
+        <v>1.4341</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4002595616845325</v>
+        <v>0.895</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4052</v>
+        <v>3.7284</v>
       </c>
       <c r="F5" t="n">
-        <v>4.405205846148744</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3.7284</v>
       </c>
       <c r="H5" t="n">
-        <v>4.405205846148744</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>4.805679104889538</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2.868</v>
       </c>
       <c r="K5" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="M5" t="n">
-        <v>4.8057</v>
+        <v>2.868</v>
       </c>
       <c r="N5" t="n">
-        <v>105</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xfl0ud</t>
+          <t>molodoy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.8274</v>
+        <v>3.1616</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7029143168868954</v>
+        <v>1.2161</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3941148150821042</v>
+        <v>0.6853</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3376</v>
+        <v>3.1616</v>
       </c>
       <c r="F6" t="n">
-        <v>4.337577546297022</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3.1616</v>
       </c>
       <c r="H6" t="n">
-        <v>4.337577546297022</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3.218732000749452</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2.432</v>
       </c>
       <c r="K6" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2187</v>
+        <v>2.432</v>
       </c>
       <c r="N6" t="n">
-        <v>53</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.7025</v>
+        <v>2.4915</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6548711965086678</v>
+        <v>0.9584</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3627974546978797</v>
+        <v>0.4373</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9929</v>
+        <v>2.4915</v>
       </c>
       <c r="F7" t="n">
-        <v>3.992902659656172</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2.4915</v>
       </c>
       <c r="H7" t="n">
-        <v>3.992902659656172</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>7.467246532344009</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.9165</v>
       </c>
       <c r="K7" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="M7" t="n">
-        <v>7.4672</v>
+        <v>1.9165</v>
       </c>
       <c r="N7" t="n">
-        <v>180</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.5975</v>
+        <v>2.3085</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6144826645654019</v>
+        <v>0.888</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3370353935064862</v>
+        <v>0.3696</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7094</v>
+        <v>2.3085</v>
       </c>
       <c r="F8" t="n">
-        <v>3.709368689620463</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2.3085</v>
       </c>
       <c r="H8" t="n">
-        <v>3.709368689620463</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>6.782845603877417</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.7758</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>176</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
-        <v>6.7828</v>
+        <v>1.7758</v>
       </c>
       <c r="N8" t="n">
         <v>176</v>
@@ -826,320 +814,320 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>xiELO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.4507</v>
+        <v>2.2983</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5580156503818645</v>
+        <v>0.884</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3018151362792446</v>
+        <v>0.3659</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3217</v>
+        <v>2.2983</v>
       </c>
       <c r="F9" t="n">
-        <v>3.321739016546989</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2.2983</v>
       </c>
       <c r="H9" t="n">
-        <v>3.321739016546989</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3.623715290778533</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1.7679</v>
       </c>
       <c r="K9" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6237</v>
+        <v>1.7679</v>
       </c>
       <c r="N9" t="n">
-        <v>105</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.3467</v>
+        <v>1.9119</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5180117711237726</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2774302318493319</v>
+        <v>0.2229</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0534</v>
+        <v>1.9119</v>
       </c>
       <c r="F10" t="n">
-        <v>3.053361858733845</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1.9119</v>
       </c>
       <c r="H10" t="n">
-        <v>3.053361858733845</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>5.583290255970459</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.4707</v>
       </c>
       <c r="K10" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M10" t="n">
-        <v>5.5833</v>
+        <v>1.4707</v>
       </c>
       <c r="N10" t="n">
-        <v>176</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.3444</v>
+        <v>1.7896</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5171270699478725</v>
+        <v>0.6884</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2768986098589023</v>
+        <v>0.1776</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0475</v>
+        <v>1.7896</v>
       </c>
       <c r="F11" t="n">
-        <v>3.047510894698593</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1.7896</v>
       </c>
       <c r="H11" t="n">
-        <v>3.047510894698593</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.426106242471249</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1.3766</v>
       </c>
       <c r="K11" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
-        <v>2.4261</v>
+        <v>1.3766</v>
       </c>
       <c r="N11" t="n">
-        <v>61</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>nilo</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.3148</v>
+        <v>1.7874</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5057413504667233</v>
+        <v>0.6875</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2700589444874785</v>
+        <v>0.1768</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9722</v>
+        <v>1.7874</v>
       </c>
       <c r="F12" t="n">
-        <v>2.972234407228584</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1.7874</v>
       </c>
       <c r="H12" t="n">
-        <v>2.972234407228584</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2.205568868375021</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1.3749</v>
       </c>
       <c r="K12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2056</v>
+        <v>1.3749</v>
       </c>
       <c r="N12" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.2524</v>
+        <v>1.4299</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4817390229118681</v>
+        <v>0.55</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2557238227130682</v>
+        <v>0.0445</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8145</v>
+        <v>1.4299</v>
       </c>
       <c r="F13" t="n">
-        <v>2.814463879573687</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.4299</v>
       </c>
       <c r="H13" t="n">
-        <v>2.814463879573687</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2.86563595011139</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1.0999</v>
       </c>
       <c r="K13" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8656</v>
+        <v>1.0999</v>
       </c>
       <c r="N13" t="n">
-        <v>98</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>xfl0ud</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.2235</v>
+        <v>1.3374</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4706225603103407</v>
+        <v>0.5144</v>
       </c>
       <c r="D14" t="n">
-        <v>0.249138710138864</v>
+        <v>0.0103</v>
       </c>
       <c r="E14" t="n">
-        <v>2.742</v>
+        <v>1.3374</v>
       </c>
       <c r="F14" t="n">
-        <v>2.741988967825557</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1.3374</v>
       </c>
       <c r="H14" t="n">
-        <v>2.741988967825557</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2.991260692173334</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.0288</v>
       </c>
       <c r="K14" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9913</v>
+        <v>1.0288</v>
       </c>
       <c r="N14" t="n">
-        <v>105</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>xiELO</t>
+          <t>BELCHONOKK</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.1835</v>
+        <v>1.299</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4552364529033823</v>
+        <v>0.4997</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2400843585060287</v>
+        <v>-0.0039</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6423</v>
+        <v>1.299</v>
       </c>
       <c r="F15" t="n">
-        <v>2.642337924941816</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1.299</v>
       </c>
       <c r="H15" t="n">
-        <v>2.642337924941816</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4.83170363417932</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.9992</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>176</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
-        <v>4.8317</v>
+        <v>0.9992</v>
       </c>
       <c r="N15" t="n">
         <v>176</v>
@@ -1148,228 +1136,228 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1376</v>
+        <v>1.1834</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4375808946538974</v>
+        <v>0.4552</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2297793986446129</v>
+        <v>-0.0467</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5289</v>
+        <v>1.1834</v>
       </c>
       <c r="F16" t="n">
-        <v>2.528922846898994</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1.1834</v>
       </c>
       <c r="H16" t="n">
-        <v>2.528922846898994</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>4.624316062901018</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.9103</v>
       </c>
       <c r="K16" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6243</v>
+        <v>0.9103</v>
       </c>
       <c r="N16" t="n">
-        <v>176</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.0419</v>
+        <v>0.6626</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4007696326827495</v>
+        <v>0.2549</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2085687385429944</v>
+        <v>-0.2394</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2955</v>
+        <v>0.6626</v>
       </c>
       <c r="F17" t="n">
-        <v>2.295481018583679</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.6626</v>
       </c>
       <c r="H17" t="n">
-        <v>2.295481018583679</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>4.292847619169477</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.5097</v>
       </c>
       <c r="K17" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2928</v>
+        <v>0.5097</v>
       </c>
       <c r="N17" t="n">
-        <v>180</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9164</v>
+        <v>0.6365</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3524957206934174</v>
+        <v>0.2448</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1813089061930429</v>
+        <v>-0.249</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9955</v>
+        <v>0.6365</v>
       </c>
       <c r="F18" t="n">
-        <v>1.995462769606314</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.6365</v>
       </c>
       <c r="H18" t="n">
-        <v>1.995462769606314</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1.452540827721807</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.4896</v>
       </c>
       <c r="K18" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4525</v>
+        <v>0.4896</v>
       </c>
       <c r="N18" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8792</v>
+        <v>0.5169</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3381866408049461</v>
+        <v>0.1988</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1733313803073273</v>
+        <v>-0.2933</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9077</v>
+        <v>0.5169</v>
       </c>
       <c r="F19" t="n">
-        <v>1.907663133985729</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.5169</v>
       </c>
       <c r="H19" t="n">
-        <v>1.907663133985729</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1.38862955994949</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.3976</v>
       </c>
       <c r="K19" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3886</v>
+        <v>0.3976</v>
       </c>
       <c r="N19" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.775</v>
+        <v>0.4939</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2981058310098194</v>
+        <v>0.19</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1513112551211788</v>
+        <v>-0.3018</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6653</v>
+        <v>0.4939</v>
       </c>
       <c r="F20" t="n">
-        <v>1.665312435866986</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.4939</v>
       </c>
       <c r="H20" t="n">
-        <v>1.665312435866986</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1.32574584174587</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.3799</v>
       </c>
       <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>61</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
-        <v>1.3257</v>
+        <v>0.3799</v>
       </c>
       <c r="N20" t="n">
         <v>61</v>
@@ -1378,320 +1366,320 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>hypex</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6698</v>
+        <v>0.3868</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2576403685295187</v>
+        <v>0.1488</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1295013399004963</v>
+        <v>-0.3414</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4253</v>
+        <v>0.3868</v>
       </c>
       <c r="F21" t="n">
-        <v>1.425275281901672</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.3868</v>
       </c>
       <c r="H21" t="n">
-        <v>1.425275281901672</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9853200044138604</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.2975</v>
       </c>
       <c r="K21" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9853</v>
+        <v>0.2975</v>
       </c>
       <c r="N21" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6656</v>
+        <v>0.3825</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2560248272517881</v>
+        <v>0.1471</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1286353766629345</v>
+        <v>-0.343</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4157</v>
+        <v>0.3825</v>
       </c>
       <c r="F22" t="n">
-        <v>1.415744600609257</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.3825</v>
       </c>
       <c r="H22" t="n">
-        <v>1.415744600609257</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1.127066295073176</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.2942</v>
       </c>
       <c r="K22" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1271</v>
+        <v>0.2942</v>
       </c>
       <c r="N22" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6611</v>
+        <v>0.3076</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2542938901685053</v>
+        <v>0.1183</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1277217252503741</v>
+        <v>-0.3707</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4057</v>
+        <v>0.3076</v>
       </c>
       <c r="F23" t="n">
-        <v>1.405689069325971</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.3076</v>
       </c>
       <c r="H23" t="n">
-        <v>1.405689069325971</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1.431247052404625</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.2366</v>
       </c>
       <c r="K23" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M23" t="n">
-        <v>1.4312</v>
+        <v>0.2366</v>
       </c>
       <c r="N23" t="n">
-        <v>98</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5657</v>
+        <v>0.3067</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2175980240029095</v>
+        <v>0.118</v>
       </c>
       <c r="D24" t="n">
-        <v>0.108320608933028</v>
+        <v>-0.371</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1922</v>
+        <v>0.3067</v>
       </c>
       <c r="F24" t="n">
-        <v>1.192162849831569</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.3067</v>
       </c>
       <c r="H24" t="n">
-        <v>1.192162849831569</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9490741237546062</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.2359</v>
       </c>
       <c r="K24" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.2359</v>
       </c>
       <c r="N24" t="n">
-        <v>61</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5633</v>
+        <v>0.2831</v>
       </c>
       <c r="C25" t="n">
-        <v>0.216674857558492</v>
+        <v>0.1089</v>
       </c>
       <c r="D25" t="n">
-        <v>0.107846514843909</v>
+        <v>-0.3798</v>
       </c>
       <c r="E25" t="n">
-        <v>1.1869</v>
+        <v>0.2831</v>
       </c>
       <c r="F25" t="n">
-        <v>1.186945030563936</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.2831</v>
       </c>
       <c r="H25" t="n">
-        <v>1.186945030563936</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8640031492523265</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.2178</v>
       </c>
       <c r="K25" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M25" t="n">
-        <v>0.864</v>
+        <v>0.2178</v>
       </c>
       <c r="N25" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>hypex</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4879</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1876720450963753</v>
+        <v>0.0357</v>
       </c>
       <c r="D26" t="n">
-        <v>0.09276742235589805</v>
+        <v>-0.4502</v>
       </c>
       <c r="E26" t="n">
-        <v>1.021</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>1.020986455824982</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>1.020986455824982</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7431982867459666</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7432</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Chr1zN</t>
+          <t>nilo</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4454</v>
+        <v>0.0476</v>
       </c>
       <c r="C27" t="n">
-        <v>0.171324305976482</v>
+        <v>0.0183</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0843582007065176</v>
+        <v>-0.4669</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9284</v>
+        <v>0.0476</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9284356315161101</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.0476</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9284356315161101</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6889526344832974</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.0366</v>
       </c>
       <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>53</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.0366</v>
       </c>
       <c r="N27" t="n">
         <v>53</v>
@@ -1700,369 +1688,369 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>Chr1zN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4387</v>
+        <v>0.0408</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1687471329858165</v>
+        <v>0.0157</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08302633722270122</v>
+        <v>-0.4694</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9137999999999999</v>
+        <v>0.0408</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9137773113488479</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.0408</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9137773113488479</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9303914442824632</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.0314</v>
       </c>
       <c r="K28" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M28" t="n">
-        <v>0.9304</v>
+        <v>0.0314</v>
       </c>
       <c r="N28" t="n">
-        <v>98</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2899</v>
+        <v>0.0061</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1115108134319311</v>
+        <v>0.0023</v>
       </c>
       <c r="D29" t="n">
-        <v>0.05411592708596363</v>
+        <v>-0.4823</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5956</v>
+        <v>0.0061</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5955930131076702</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.0061</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5955930131076702</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4741482399903579</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.0047</v>
       </c>
       <c r="K29" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4741</v>
+        <v>0.0047</v>
       </c>
       <c r="N29" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2787</v>
+        <v>-0.0659</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1072027033579828</v>
+        <v>-0.0253</v>
       </c>
       <c r="D30" t="n">
-        <v>0.05198140794952661</v>
+        <v>-0.5089</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5721000000000001</v>
+        <v>-0.0659</v>
       </c>
       <c r="F30" t="n">
-        <v>0.57210076687881</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.0659</v>
       </c>
       <c r="H30" t="n">
-        <v>0.57210076687881</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6241099275041563</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.0507</v>
       </c>
       <c r="K30" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6241</v>
+        <v>-0.0507</v>
       </c>
       <c r="N30" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yxngstxr</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.1325</v>
+        <v>-0.168</v>
       </c>
       <c r="C31" t="n">
-        <v>0.05096648078554977</v>
+        <v>-0.0646</v>
       </c>
       <c r="D31" t="n">
-        <v>0.02437585463846282</v>
+        <v>-0.5467</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2683</v>
+        <v>-0.168</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2682775569590545</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.168</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2682775569590545</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1990773763581868</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.1292</v>
       </c>
       <c r="K31" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1991</v>
+        <v>-0.1292</v>
       </c>
       <c r="N31" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BELCHONOKK</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.1075</v>
+        <v>-0.189</v>
       </c>
       <c r="C32" t="n">
-        <v>0.04135016365620076</v>
+        <v>-0.0727</v>
       </c>
       <c r="D32" t="n">
-        <v>0.01974634437775915</v>
+        <v>-0.5544</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2173</v>
+        <v>-0.189</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2173257556343655</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.189</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2173257556343655</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0.397395667445697</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.1454</v>
       </c>
       <c r="K32" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M32" t="n">
-        <v>0.3974</v>
+        <v>-0.1454</v>
       </c>
       <c r="N32" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NucleonZ</t>
+          <t>yxngstxr</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.04</v>
+        <v>-0.62</v>
       </c>
       <c r="C33" t="n">
-        <v>0.01538610740695842</v>
+        <v>-0.2385</v>
       </c>
       <c r="D33" t="n">
-        <v>0.007306508516281268</v>
+        <v>-0.7139</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0804</v>
+        <v>-0.62</v>
       </c>
       <c r="F33" t="n">
-        <v>0.08041450376699803</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="H33" t="n">
-        <v>0.08041450376699803</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0.150385565486334</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.4769</v>
       </c>
       <c r="K33" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1504</v>
+        <v>-0.4769</v>
       </c>
       <c r="N33" t="n">
-        <v>180</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>Tauson</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.021</v>
+        <v>-0.8428</v>
       </c>
       <c r="C34" t="n">
-        <v>0.008077706388653171</v>
+        <v>-0.3242</v>
       </c>
       <c r="D34" t="n">
-        <v>0.003824682438221208</v>
+        <v>-0.7964</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0421</v>
+        <v>-0.8428</v>
       </c>
       <c r="F34" t="n">
-        <v>0.04209396863776554</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.8428</v>
       </c>
       <c r="H34" t="n">
-        <v>0.04209396863776554</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0.04285931352208855</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.6483</v>
       </c>
       <c r="K34" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0429</v>
+        <v>-0.6483</v>
       </c>
       <c r="N34" t="n">
-        <v>98</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tauson</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.1186</v>
+        <v>-0.8844</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.04561980846163172</v>
+        <v>-0.3402</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.02180541825885842</v>
+        <v>-0.8117</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.24</v>
+        <v>-0.8844</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2399876609752297</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.8844</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2399876609752297</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1659080503072239</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.6803</v>
       </c>
       <c r="K35" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.1659</v>
+        <v>-0.6803</v>
       </c>
       <c r="N35" t="n">
-        <v>46</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36">
@@ -2072,40 +2060,40 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.2415</v>
+        <v>-0.8947000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.09289362346951147</v>
+        <v>-0.3441</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.04489630184167737</v>
+        <v>-0.8156</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.4941</v>
+        <v>-0.8947000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4941229898694974</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.8947000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4941229898694974</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3415966534616374</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.6882</v>
       </c>
       <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>46</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
-        <v>-0.3416</v>
+        <v>-0.6882</v>
       </c>
       <c r="N36" t="n">
         <v>46</v>
@@ -2114,90 +2102,90 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.4522</v>
+        <v>-1.2006</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1739399442356649</v>
+        <v>-0.4618</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.08569647534908915</v>
+        <v>-0.9287</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9432</v>
+        <v>-1.2006</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9431645120815051</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-1.2006</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9431645120815051</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.028906740452551</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.9235</v>
       </c>
       <c r="K37" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0289</v>
+        <v>-0.9235</v>
       </c>
       <c r="N37" t="n">
-        <v>105</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>NucleonZ</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.5645</v>
+        <v>-1.224</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2171364407807007</v>
+        <v>-0.4708</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1080794007723048</v>
+        <v>-0.9374</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1895</v>
+        <v>-1.224</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.189508143482307</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-1.224</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.189508143482307</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>-2.224534709888989</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.9415</v>
       </c>
       <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
         <v>180</v>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
       <c r="M38" t="n">
-        <v>-2.2245</v>
+        <v>-0.9415</v>
       </c>
       <c r="N38" t="n">
         <v>180</v>
@@ -2206,139 +2194,139 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>susp</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.5874</v>
+        <v>-1.3</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2259449872711844</v>
+        <v>-0.5</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1127210012644946</v>
+        <v>-0.9655</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2406</v>
+        <v>-1.3</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.240593008357557</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.240593008357557</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.8576456239665587</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K39" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.8576</v>
+        <v>-1</v>
       </c>
       <c r="N39" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>susp</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.8486</v>
+        <v>-1.3</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3264162686386229</v>
+        <v>-0.5</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1668340930207317</v>
+        <v>-0.9655</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.8362</v>
+        <v>-1.3</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.836154816186747</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.836154816186747</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.362532473969471</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K40" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3625</v>
+        <v>-1</v>
       </c>
       <c r="N40" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.9898</v>
+        <v>-1.5038</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3807292277851861</v>
+        <v>-0.5784</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1971717365075099</v>
+        <v>-1.0409</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.17</v>
+        <v>-1.5038</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.170047063217347</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-1.5038</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.170047063217347</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.579624538934834</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-1.1568</v>
       </c>
       <c r="K41" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.5796</v>
+        <v>-1.1568</v>
       </c>
       <c r="N41" t="n">
-        <v>51</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2356,52 +2344,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>perf_score_raw</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>perf_score_weighted</t>
         </is>
@@ -2428,7 +2416,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -2441,10 +2429,10 @@
         <v>1.14</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02885367445665202</v>
+        <v>0.3124</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6347808380463446</v>
+        <v>6.8728</v>
       </c>
     </row>
     <row r="3">
@@ -2468,7 +2456,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -2481,10 +2469,10 @@
         <v>1.14</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02885367445665202</v>
+        <v>0.3124</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6347808380463446</v>
+        <v>6.8728</v>
       </c>
     </row>
     <row r="4">
@@ -2508,7 +2496,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -2521,10 +2509,10 @@
         <v>0.99</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01697521819500222</v>
+        <v>-0.0038</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3734548002900487</v>
+        <v>-0.08359999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2548,7 +2536,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -2561,10 +2549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004053372300488498</v>
+        <v>-0.3555</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08917419061074697</v>
+        <v>-7.821</v>
       </c>
     </row>
     <row r="6">
@@ -2588,7 +2576,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -2601,10 +2589,10 @@
         <v>0.66</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.008168999369870394</v>
+        <v>-0.5624</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1797179861371487</v>
+        <v>-12.3728</v>
       </c>
     </row>
     <row r="7">
@@ -2628,7 +2616,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -2641,10 +2629,10 @@
         <v>1.8</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1827395517576559</v>
+        <v>1.7867</v>
       </c>
       <c r="J7" t="n">
-        <v>4.020270138668431</v>
+        <v>39.3074</v>
       </c>
     </row>
     <row r="8">
@@ -2668,7 +2656,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -2681,10 +2669,10 @@
         <v>1.13</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01648359358462645</v>
+        <v>0.3264</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3626390588617819</v>
+        <v>7.1808</v>
       </c>
     </row>
     <row r="9">
@@ -2708,7 +2696,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2721,10 +2709,10 @@
         <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.006649812833636137</v>
+        <v>0.0533</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.146295882339995</v>
+        <v>1.1726</v>
       </c>
     </row>
     <row r="10">
@@ -2748,7 +2736,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2761,10 +2749,10 @@
         <v>1.02</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.01189032216939841</v>
+        <v>-0.0196</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.261587087726765</v>
+        <v>-0.4312</v>
       </c>
     </row>
     <row r="11">
@@ -2788,7 +2776,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -2801,10 +2789,10 @@
         <v>0.97</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.02485528466348572</v>
+        <v>-0.2582</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5468162625966858</v>
+        <v>-5.6804</v>
       </c>
     </row>
     <row r="12">
@@ -2828,7 +2816,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -2841,10 +2829,10 @@
         <v>1.35</v>
       </c>
       <c r="I12" t="n">
-        <v>0.048787547091586</v>
+        <v>0.6092</v>
       </c>
       <c r="J12" t="n">
-        <v>1.170901130198064</v>
+        <v>14.6208</v>
       </c>
     </row>
     <row r="13">
@@ -2868,7 +2856,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -2881,10 +2869,10 @@
         <v>0.95</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01720670659130942</v>
+        <v>-0.0882</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4129609581914261</v>
+        <v>-2.1168</v>
       </c>
     </row>
     <row r="14">
@@ -2908,7 +2896,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -2921,10 +2909,10 @@
         <v>0.87</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01201842943388232</v>
+        <v>-0.2533</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2884423064131757</v>
+        <v>-6.0792</v>
       </c>
     </row>
     <row r="15">
@@ -2948,7 +2936,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -2961,10 +2949,10 @@
         <v>0.85</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01047999815148473</v>
+        <v>-0.2866</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2515199556356335</v>
+        <v>-6.8784</v>
       </c>
     </row>
     <row r="16">
@@ -2988,7 +2976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -3001,10 +2989,10 @@
         <v>0.62</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.008237567326955752</v>
+        <v>-0.6095</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.197701615846938</v>
+        <v>-14.628</v>
       </c>
     </row>
     <row r="17">
@@ -3028,7 +3016,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -3041,10 +3029,10 @@
         <v>1.47</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1262437348357397</v>
+        <v>1.228</v>
       </c>
       <c r="J17" t="n">
-        <v>3.029849636057753</v>
+        <v>29.472</v>
       </c>
     </row>
     <row r="18">
@@ -3068,7 +3056,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -3081,10 +3069,10 @@
         <v>1.28</v>
       </c>
       <c r="I18" t="n">
-        <v>0.07642118015828203</v>
+        <v>0.8179</v>
       </c>
       <c r="J18" t="n">
-        <v>1.834108323798769</v>
+        <v>19.6296</v>
       </c>
     </row>
     <row r="19">
@@ -3108,7 +3096,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -3121,10 +3109,10 @@
         <v>0.99</v>
       </c>
       <c r="I19" t="n">
-        <v>0.006347288741013684</v>
+        <v>-0.1245</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1523349297843284</v>
+        <v>-2.988</v>
       </c>
     </row>
     <row r="20">
@@ -3148,7 +3136,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -3161,10 +3149,10 @@
         <v>0.84</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0316079889525598</v>
+        <v>-0.5935</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7585917348614352</v>
+        <v>-14.244</v>
       </c>
     </row>
     <row r="21">
@@ -3188,7 +3176,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -3201,10 +3189,10 @@
         <v>0.78</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.04749893261005296</v>
+        <v>-0.742</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.139974382641271</v>
+        <v>-17.808</v>
       </c>
     </row>
     <row r="22">
@@ -3228,7 +3216,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -3241,10 +3229,10 @@
         <v>1.4</v>
       </c>
       <c r="I22" t="n">
-        <v>0.04936068938108208</v>
+        <v>0.656</v>
       </c>
       <c r="J22" t="n">
-        <v>1.18465654514597</v>
+        <v>15.744</v>
       </c>
     </row>
     <row r="23">
@@ -3268,7 +3256,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -3281,10 +3269,10 @@
         <v>1.22</v>
       </c>
       <c r="I23" t="n">
-        <v>0.03474120662294194</v>
+        <v>0.4225</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8337889589506067</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="24">
@@ -3308,7 +3296,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -3321,10 +3309,10 @@
         <v>0.79</v>
       </c>
       <c r="I24" t="n">
-        <v>0.00217818424173935</v>
+        <v>-0.3908</v>
       </c>
       <c r="J24" t="n">
-        <v>0.05227642180174441</v>
+        <v>-9.379200000000001</v>
       </c>
     </row>
     <row r="25">
@@ -3348,7 +3336,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -3361,10 +3349,10 @@
         <v>0.78</v>
       </c>
       <c r="I25" t="n">
-        <v>0.001356956521841864</v>
+        <v>-0.4052</v>
       </c>
       <c r="J25" t="n">
-        <v>0.03256695652420474</v>
+        <v>-9.7248</v>
       </c>
     </row>
     <row r="26">
@@ -3388,7 +3376,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -3401,10 +3389,10 @@
         <v>0.66</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.008462620284377293</v>
+        <v>-0.5664</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.203102886825055</v>
+        <v>-13.5936</v>
       </c>
     </row>
     <row r="27">
@@ -3428,7 +3416,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -3441,10 +3429,10 @@
         <v>1.51</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1249023324267734</v>
+        <v>1.2837</v>
       </c>
       <c r="J27" t="n">
-        <v>2.997655978242561</v>
+        <v>30.8088</v>
       </c>
     </row>
     <row r="28">
@@ -3468,7 +3456,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -3481,10 +3469,10 @@
         <v>1.37</v>
       </c>
       <c r="I28" t="n">
-        <v>0.08831544573247345</v>
+        <v>0.9941</v>
       </c>
       <c r="J28" t="n">
-        <v>2.119570697579363</v>
+        <v>23.8584</v>
       </c>
     </row>
     <row r="29">
@@ -3508,7 +3496,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -3521,10 +3509,10 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.002483463404289777</v>
+        <v>-0.0888</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.05960312170295465</v>
+        <v>-2.1312</v>
       </c>
     </row>
     <row r="30">
@@ -3548,7 +3536,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -3561,10 +3549,10 @@
         <v>0.99</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.004985319641045094</v>
+        <v>-0.1482</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.1196476713850823</v>
+        <v>-3.5568</v>
       </c>
     </row>
     <row r="31">
@@ -3588,7 +3576,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Grand final</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -3601,10 +3589,10 @@
         <v>0.72</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.07516668703644659</v>
+        <v>-0.8933</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.804000488874718</v>
+        <v>-21.4392</v>
       </c>
     </row>
     <row r="32">
@@ -3628,7 +3616,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -3641,10 +3629,10 @@
         <v>1.51</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1104266546699161</v>
+        <v>1.2226</v>
       </c>
       <c r="J32" t="n">
-        <v>2.318959748068239</v>
+        <v>25.6746</v>
       </c>
     </row>
     <row r="33">
@@ -3668,7 +3656,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -3681,10 +3669,10 @@
         <v>1.36</v>
       </c>
       <c r="I33" t="n">
-        <v>0.06780353727258698</v>
+        <v>0.907</v>
       </c>
       <c r="J33" t="n">
-        <v>1.423874282724326</v>
+        <v>19.047</v>
       </c>
     </row>
     <row r="34">
@@ -3708,7 +3696,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -3721,10 +3709,10 @@
         <v>1.34</v>
       </c>
       <c r="I34" t="n">
-        <v>0.06222094355761669</v>
+        <v>0.8617</v>
       </c>
       <c r="J34" t="n">
-        <v>1.30663981470995</v>
+        <v>18.0957</v>
       </c>
     </row>
     <row r="35">
@@ -3748,7 +3736,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -3761,10 +3749,10 @@
         <v>1.25</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03906617724390715</v>
+        <v>0.6382</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8203897221220502</v>
+        <v>13.4022</v>
       </c>
     </row>
     <row r="36">
@@ -3788,7 +3776,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -3801,10 +3789,10 @@
         <v>0.74</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.09992852671694737</v>
+        <v>-0.876</v>
       </c>
       <c r="J36" t="n">
-        <v>-2.098499061055895</v>
+        <v>-18.396</v>
       </c>
     </row>
     <row r="37">
@@ -3828,7 +3816,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -3841,10 +3829,10 @@
         <v>1.11</v>
       </c>
       <c r="I37" t="n">
-        <v>0.02948790929608261</v>
+        <v>0.2863</v>
       </c>
       <c r="J37" t="n">
-        <v>0.6192460952177348</v>
+        <v>6.0123</v>
       </c>
     </row>
     <row r="38">
@@ -3868,7 +3856,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -3881,10 +3869,10 @@
         <v>0.96</v>
       </c>
       <c r="I38" t="n">
-        <v>0.01733494402159859</v>
+        <v>-0.0478</v>
       </c>
       <c r="J38" t="n">
-        <v>0.3640338244535703</v>
+        <v>-1.0038</v>
       </c>
     </row>
     <row r="39">
@@ -3908,7 +3896,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -3921,10 +3909,10 @@
         <v>0.86</v>
       </c>
       <c r="I39" t="n">
-        <v>0.01069207105661912</v>
+        <v>-0.2534</v>
       </c>
       <c r="J39" t="n">
-        <v>0.2245334921890015</v>
+        <v>-5.3214</v>
       </c>
     </row>
     <row r="40">
@@ -3948,7 +3936,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -3961,10 +3949,10 @@
         <v>0.8</v>
       </c>
       <c r="I40" t="n">
-        <v>0.006197219020767907</v>
+        <v>-0.3523</v>
       </c>
       <c r="J40" t="n">
-        <v>0.130141599436126</v>
+        <v>-7.3983</v>
       </c>
     </row>
     <row r="41">
@@ -3988,7 +3976,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -4001,10 +3989,10 @@
         <v>0.72</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.0002084632311454108</v>
+        <v>-0.4692</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.004377727854053628</v>
+        <v>-9.853199999999999</v>
       </c>
     </row>
     <row r="42">
@@ -4028,7 +4016,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -4041,10 +4029,10 @@
         <v>1.2</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0586242874162787</v>
+        <v>0.6287</v>
       </c>
       <c r="J42" t="n">
-        <v>1.406982897990689</v>
+        <v>15.0888</v>
       </c>
     </row>
     <row r="43">
@@ -4068,7 +4056,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -4081,10 +4069,10 @@
         <v>1.16</v>
       </c>
       <c r="I43" t="n">
-        <v>0.04730837085656006</v>
+        <v>0.524</v>
       </c>
       <c r="J43" t="n">
-        <v>1.135400900557441</v>
+        <v>12.576</v>
       </c>
     </row>
     <row r="44">
@@ -4108,7 +4096,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -4121,10 +4109,10 @@
         <v>1.11</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0337847897653782</v>
+        <v>0.3812</v>
       </c>
       <c r="J44" t="n">
-        <v>0.8108349543690768</v>
+        <v>9.1488</v>
       </c>
     </row>
     <row r="45">
@@ -4148,7 +4136,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -4161,10 +4149,10 @@
         <v>1.01</v>
       </c>
       <c r="I45" t="n">
-        <v>0.01087136867219056</v>
+        <v>0.0016</v>
       </c>
       <c r="J45" t="n">
-        <v>0.2609128481325735</v>
+        <v>0.0384</v>
       </c>
     </row>
     <row r="46">
@@ -4188,7 +4176,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -4201,10 +4189,10 @@
         <v>0.84</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.03556129230833457</v>
+        <v>-0.5906</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.8534710154000298</v>
+        <v>-14.1744</v>
       </c>
     </row>
     <row r="47">
@@ -4228,7 +4216,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -4241,10 +4229,10 @@
         <v>1.34</v>
       </c>
       <c r="I47" t="n">
-        <v>0.04632784236992764</v>
+        <v>0.5867</v>
       </c>
       <c r="J47" t="n">
-        <v>1.111868216878263</v>
+        <v>14.0808</v>
       </c>
     </row>
     <row r="48">
@@ -4268,7 +4256,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -4281,10 +4269,10 @@
         <v>1.24</v>
       </c>
       <c r="I48" t="n">
-        <v>0.03817871054265265</v>
+        <v>0.4552</v>
       </c>
       <c r="J48" t="n">
-        <v>0.9162890530236636</v>
+        <v>10.9248</v>
       </c>
     </row>
     <row r="49">
@@ -4308,7 +4296,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -4321,10 +4309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>0.005619495100416708</v>
+        <v>-0.3578</v>
       </c>
       <c r="J49" t="n">
-        <v>0.134867882410001</v>
+        <v>-8.587199999999999</v>
       </c>
     </row>
     <row r="50">
@@ -4348,7 +4336,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -4361,10 +4349,10 @@
         <v>0.72</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.001776426033182326</v>
+        <v>-0.4851</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.04263422479637582</v>
+        <v>-11.6424</v>
       </c>
     </row>
     <row r="51">
@@ -4388,7 +4376,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -4401,10 +4389,10 @@
         <v>0.67</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.005875391553690254</v>
+        <v>-0.551</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.1410093972885661</v>
+        <v>-13.224</v>
       </c>
     </row>
     <row r="52">
@@ -4428,7 +4416,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -4441,10 +4429,10 @@
         <v>1.49</v>
       </c>
       <c r="I52" t="n">
-        <v>0.08228392074558684</v>
+        <v>0.7725</v>
       </c>
       <c r="J52" t="n">
-        <v>1.892530177148497</v>
+        <v>17.7675</v>
       </c>
     </row>
     <row r="53">
@@ -4468,7 +4456,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -4481,10 +4469,10 @@
         <v>1.23</v>
       </c>
       <c r="I53" t="n">
-        <v>0.04872019268061505</v>
+        <v>0.4464</v>
       </c>
       <c r="J53" t="n">
-        <v>1.120564431654146</v>
+        <v>10.2672</v>
       </c>
     </row>
     <row r="54">
@@ -4508,7 +4496,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -4521,10 +4509,10 @@
         <v>0.78</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.006625735026744704</v>
+        <v>-0.398</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.1523919056151282</v>
+        <v>-9.154</v>
       </c>
     </row>
     <row r="55">
@@ -4548,7 +4536,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -4561,10 +4549,10 @@
         <v>0.67</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.02118029586326546</v>
+        <v>-0.5483</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.4871468048551055</v>
+        <v>-12.6109</v>
       </c>
     </row>
     <row r="56">
@@ -4588,7 +4576,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -4601,10 +4589,10 @@
         <v>0.54</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.03804935252092445</v>
+        <v>-0.7096</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.8751351079812624</v>
+        <v>-16.3208</v>
       </c>
     </row>
     <row r="57">
@@ -4628,7 +4616,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -4641,10 +4629,10 @@
         <v>1.49</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1352427279461306</v>
+        <v>1.2303</v>
       </c>
       <c r="J57" t="n">
-        <v>3.110582742761003</v>
+        <v>28.2969</v>
       </c>
     </row>
     <row r="58">
@@ -4668,7 +4656,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -4681,10 +4669,10 @@
         <v>1.36</v>
       </c>
       <c r="I58" t="n">
-        <v>0.09426761099994584</v>
+        <v>0.9585</v>
       </c>
       <c r="J58" t="n">
-        <v>2.168155052998754</v>
+        <v>22.0455</v>
       </c>
     </row>
     <row r="59">
@@ -4708,7 +4696,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -4721,10 +4709,10 @@
         <v>1.08</v>
       </c>
       <c r="I59" t="n">
-        <v>0.01292001759093562</v>
+        <v>0.2064</v>
       </c>
       <c r="J59" t="n">
-        <v>0.2971604045915192</v>
+        <v>4.7472</v>
       </c>
     </row>
     <row r="60">
@@ -4748,7 +4736,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -4761,10 +4749,10 @@
         <v>0.97</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0208376310697585</v>
+        <v>-0.2401</v>
       </c>
       <c r="J60" t="n">
-        <v>-0.4792655146044456</v>
+        <v>-5.5223</v>
       </c>
     </row>
     <row r="61">
@@ -4788,7 +4776,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -4801,10 +4789,10 @@
         <v>0.82</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.0670870345384622</v>
+        <v>-0.6669</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.543001794384631</v>
+        <v>-15.3387</v>
       </c>
     </row>
     <row r="62">
@@ -4828,7 +4816,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -4841,10 +4829,10 @@
         <v>1.93</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1752117588241251</v>
+        <v>1.1001</v>
       </c>
       <c r="J62" t="n">
-        <v>2.978599900010127</v>
+        <v>18.7017</v>
       </c>
     </row>
     <row r="63">
@@ -4868,7 +4856,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -4881,10 +4869,10 @@
         <v>1.83</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1508396283741476</v>
+        <v>1.0016</v>
       </c>
       <c r="J63" t="n">
-        <v>2.56427368236051</v>
+        <v>17.0272</v>
       </c>
     </row>
     <row r="64">
@@ -4908,7 +4896,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -4921,10 +4909,10 @@
         <v>1.3</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0208429673311969</v>
+        <v>0.372</v>
       </c>
       <c r="J64" t="n">
-        <v>0.3543304446303474</v>
+        <v>6.324</v>
       </c>
     </row>
     <row r="65">
@@ -4948,7 +4936,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -4961,10 +4949,10 @@
         <v>1.02</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.05310360289866309</v>
+        <v>-0.0489</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.9027612492772725</v>
+        <v>-0.8313</v>
       </c>
     </row>
     <row r="66">
@@ -4988,7 +4976,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -5001,10 +4989,10 @@
         <v>0.95</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.07111006481790758</v>
+        <v>-0.22</v>
       </c>
       <c r="J66" t="n">
-        <v>-1.208871101904429</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="67">
@@ -5028,7 +5016,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -5041,10 +5029,10 @@
         <v>1.32</v>
       </c>
       <c r="I67" t="n">
-        <v>0.07085740597713312</v>
+        <v>0.5936</v>
       </c>
       <c r="J67" t="n">
-        <v>1.204575901611263</v>
+        <v>10.0912</v>
       </c>
     </row>
     <row r="68">
@@ -5068,7 +5056,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -5081,10 +5069,10 @@
         <v>0.89</v>
       </c>
       <c r="I68" t="n">
-        <v>0.004110250137151807</v>
+        <v>-0.174</v>
       </c>
       <c r="J68" t="n">
-        <v>0.06987425233158071</v>
+        <v>-2.958</v>
       </c>
     </row>
     <row r="69">
@@ -5108,7 +5096,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -5121,10 +5109,10 @@
         <v>0.88</v>
       </c>
       <c r="I69" t="n">
-        <v>0.002875547995265432</v>
+        <v>-0.1936</v>
       </c>
       <c r="J69" t="n">
-        <v>0.04888431591951234</v>
+        <v>-3.2912</v>
       </c>
     </row>
     <row r="70">
@@ -5148,7 +5136,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -5161,10 +5149,10 @@
         <v>0.63</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.03335235408395117</v>
+        <v>-0.5847</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.5669900194271699</v>
+        <v>-9.9399</v>
       </c>
     </row>
     <row r="71">
@@ -5188,7 +5176,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -5201,10 +5189,10 @@
         <v>0.62</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.03490479103654577</v>
+        <v>-0.5976</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.5933814476212781</v>
+        <v>-10.1592</v>
       </c>
     </row>
     <row r="72">
@@ -5228,7 +5216,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -5241,10 +5229,10 @@
         <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>0.02803687410881835</v>
+        <v>0.0949</v>
       </c>
       <c r="J72" t="n">
-        <v>0.5327006080675487</v>
+        <v>1.8031</v>
       </c>
     </row>
     <row r="73">
@@ -5268,7 +5256,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -5281,10 +5269,10 @@
         <v>0.97</v>
       </c>
       <c r="I73" t="n">
-        <v>0.02406289889129126</v>
+        <v>0.0128</v>
       </c>
       <c r="J73" t="n">
-        <v>0.4571950789345339</v>
+        <v>0.2432</v>
       </c>
     </row>
     <row r="74">
@@ -5308,7 +5296,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -5321,10 +5309,10 @@
         <v>0.83</v>
       </c>
       <c r="I74" t="n">
-        <v>0.006454699481573966</v>
+        <v>-0.2434</v>
       </c>
       <c r="J74" t="n">
-        <v>0.1226392901499054</v>
+        <v>-4.6246</v>
       </c>
     </row>
     <row r="75">
@@ -5348,7 +5336,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -5361,10 +5349,10 @@
         <v>0.64</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.01547312802364408</v>
+        <v>-0.5541</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.2939894324492375</v>
+        <v>-10.5279</v>
       </c>
     </row>
     <row r="76">
@@ -5388,7 +5376,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -5401,10 +5389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.02581819360741279</v>
+        <v>-0.6595</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.4905456785408431</v>
+        <v>-12.5305</v>
       </c>
     </row>
     <row r="77">
@@ -5428,7 +5416,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -5441,10 +5429,10 @@
         <v>2.18</v>
       </c>
       <c r="I77" t="n">
-        <v>0.285836874569435</v>
+        <v>2.0596</v>
       </c>
       <c r="J77" t="n">
-        <v>5.430900616819264</v>
+        <v>39.1324</v>
       </c>
     </row>
     <row r="78">
@@ -5468,7 +5456,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -5481,10 +5469,10 @@
         <v>1.57</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1101264259634482</v>
+        <v>1.279</v>
       </c>
       <c r="J78" t="n">
-        <v>2.092402093305516</v>
+        <v>24.301</v>
       </c>
     </row>
     <row r="79">
@@ -5508,7 +5496,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -5521,10 +5509,10 @@
         <v>1.17</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.006725900539774381</v>
+        <v>0.3529</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.1277921102557132</v>
+        <v>6.7051</v>
       </c>
     </row>
     <row r="80">
@@ -5548,7 +5536,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -5561,10 +5549,10 @@
         <v>1.14</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.01629920797218754</v>
+        <v>0.2772</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.3096849514715632</v>
+        <v>5.2668</v>
       </c>
     </row>
     <row r="81">
@@ -5588,7 +5576,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -5601,10 +5589,10 @@
         <v>0.8</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.1209538261366494</v>
+        <v>-0.7654</v>
       </c>
       <c r="J81" t="n">
-        <v>-2.298122696596339</v>
+        <v>-14.5426</v>
       </c>
     </row>
     <row r="82">
@@ -5628,7 +5616,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -5641,10 +5629,10 @@
         <v>1.2</v>
       </c>
       <c r="I82" t="n">
-        <v>0.03426882888561639</v>
+        <v>0.4005</v>
       </c>
       <c r="J82" t="n">
-        <v>0.6168389199410951</v>
+        <v>7.209</v>
       </c>
     </row>
     <row r="83">
@@ -5668,7 +5656,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -5681,10 +5669,10 @@
         <v>1.07</v>
       </c>
       <c r="I83" t="n">
-        <v>0.019844960123067</v>
+        <v>0.1936</v>
       </c>
       <c r="J83" t="n">
-        <v>0.357209282215206</v>
+        <v>3.4848</v>
       </c>
     </row>
     <row r="84">
@@ -5708,7 +5696,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -5721,10 +5709,10 @@
         <v>0.88</v>
       </c>
       <c r="I84" t="n">
-        <v>0.001641008618818472</v>
+        <v>-0.2455</v>
       </c>
       <c r="J84" t="n">
-        <v>0.02953815513873249</v>
+        <v>-4.419</v>
       </c>
     </row>
     <row r="85">
@@ -5748,7 +5736,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -5761,10 +5749,10 @@
         <v>0.82</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.004717882803871264</v>
+        <v>-0.3416</v>
       </c>
       <c r="J85" t="n">
-        <v>-0.08492189046968276</v>
+        <v>-6.1488</v>
       </c>
     </row>
     <row r="86">
@@ -5788,7 +5776,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -5801,10 +5789,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.007969202720501233</v>
+        <v>-0.3862</v>
       </c>
       <c r="J86" t="n">
-        <v>-0.1434456489690222</v>
+        <v>-6.9516</v>
       </c>
     </row>
     <row r="87">
@@ -5828,7 +5816,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -5841,10 +5829,10 @@
         <v>2.11</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1385319738035432</v>
+        <v>1.2692</v>
       </c>
       <c r="J87" t="n">
-        <v>2.493575528463777</v>
+        <v>22.8456</v>
       </c>
     </row>
     <row r="88">
@@ -5868,7 +5856,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -5881,10 +5869,10 @@
         <v>1.53</v>
       </c>
       <c r="I88" t="n">
-        <v>0.04967364208027925</v>
+        <v>0.6788</v>
       </c>
       <c r="J88" t="n">
-        <v>0.8941255574450264</v>
+        <v>12.2184</v>
       </c>
     </row>
     <row r="89">
@@ -5908,7 +5896,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -5921,10 +5909,10 @@
         <v>1.3</v>
       </c>
       <c r="I89" t="n">
-        <v>0.01655610769314877</v>
+        <v>0.371</v>
       </c>
       <c r="J89" t="n">
-        <v>0.2980099384766779</v>
+        <v>6.678</v>
       </c>
     </row>
     <row r="90">
@@ -5948,7 +5936,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -5961,10 +5949,10 @@
         <v>1.22</v>
       </c>
       <c r="I90" t="n">
-        <v>0.003519180571972499</v>
+        <v>0.2647</v>
       </c>
       <c r="J90" t="n">
-        <v>0.06334525029550499</v>
+        <v>4.7646</v>
       </c>
     </row>
     <row r="91">
@@ -5988,7 +5976,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -6001,10 +5989,10 @@
         <v>0.89</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.04883261981128181</v>
+        <v>-0.3177</v>
       </c>
       <c r="J91" t="n">
-        <v>-0.8789871566030727</v>
+        <v>-5.7186</v>
       </c>
     </row>
     <row r="92">
@@ -6028,7 +6016,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -6041,10 +6029,10 @@
         <v>1.14</v>
       </c>
       <c r="I92" t="n">
-        <v>0.03822913214620201</v>
+        <v>0.4874</v>
       </c>
       <c r="J92" t="n">
-        <v>0.8410409072164442</v>
+        <v>10.7228</v>
       </c>
     </row>
     <row r="93">
@@ -6068,7 +6056,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -6081,10 +6069,10 @@
         <v>1.11</v>
       </c>
       <c r="I93" t="n">
-        <v>0.0318760647752429</v>
+        <v>0.4015</v>
       </c>
       <c r="J93" t="n">
-        <v>0.7012734250553438</v>
+        <v>8.833</v>
       </c>
     </row>
     <row r="94">
@@ -6108,7 +6096,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -6121,10 +6109,10 @@
         <v>0.98</v>
       </c>
       <c r="I94" t="n">
-        <v>0.009072963066845612</v>
+        <v>-0.1464</v>
       </c>
       <c r="J94" t="n">
-        <v>0.1996051874706035</v>
+        <v>-3.2208</v>
       </c>
     </row>
     <row r="95">
@@ -6148,7 +6136,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -6161,10 +6149,10 @@
         <v>0.98</v>
       </c>
       <c r="I95" t="n">
-        <v>0.009072963066845612</v>
+        <v>-0.1464</v>
       </c>
       <c r="J95" t="n">
-        <v>0.1996051874706035</v>
+        <v>-3.2208</v>
       </c>
     </row>
     <row r="96">
@@ -6188,7 +6176,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -6201,10 +6189,10 @@
         <v>0.97</v>
       </c>
       <c r="I96" t="n">
-        <v>0.007075360122149901</v>
+        <v>-0.1863</v>
       </c>
       <c r="J96" t="n">
-        <v>0.1556579226872978</v>
+        <v>-4.0986</v>
       </c>
     </row>
     <row r="97">
@@ -6228,7 +6216,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -6241,10 +6229,10 @@
         <v>1.32</v>
       </c>
       <c r="I97" t="n">
-        <v>0.0410080045686284</v>
+        <v>0.5394</v>
       </c>
       <c r="J97" t="n">
-        <v>0.9021761005098249</v>
+        <v>11.8668</v>
       </c>
     </row>
     <row r="98">
@@ -6268,7 +6256,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -6281,10 +6269,10 @@
         <v>1.21</v>
       </c>
       <c r="I98" t="n">
-        <v>0.03194809099898734</v>
+        <v>0.391</v>
       </c>
       <c r="J98" t="n">
-        <v>0.7028580019777214</v>
+        <v>8.602</v>
       </c>
     </row>
     <row r="99">
@@ -6308,7 +6296,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -6321,10 +6309,10 @@
         <v>0.99</v>
       </c>
       <c r="I99" t="n">
-        <v>0.01608405895497324</v>
+        <v>-0.0514</v>
       </c>
       <c r="J99" t="n">
-        <v>0.3538492970094113</v>
+        <v>-1.1308</v>
       </c>
     </row>
     <row r="100">
@@ -6348,7 +6336,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -6361,10 +6349,10 @@
         <v>0.92</v>
       </c>
       <c r="I100" t="n">
-        <v>0.01084155611264388</v>
+        <v>-0.1993</v>
       </c>
       <c r="J100" t="n">
-        <v>0.2385142344781654</v>
+        <v>-4.3846</v>
       </c>
     </row>
     <row r="101">
@@ -6388,7 +6376,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -6401,10 +6389,10 @@
         <v>0.66</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.01040973773910792</v>
+        <v>-0.5748</v>
       </c>
       <c r="J101" t="n">
-        <v>-0.2290142302603742</v>
+        <v>-12.6456</v>
       </c>
     </row>
     <row r="102">
@@ -6428,7 +6416,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -6441,10 +6429,10 @@
         <v>1.51</v>
       </c>
       <c r="I102" t="n">
-        <v>0.09666512888378033</v>
+        <v>1.2461</v>
       </c>
       <c r="J102" t="n">
-        <v>2.029967706559387</v>
+        <v>26.1681</v>
       </c>
     </row>
     <row r="103">
@@ -6468,7 +6456,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -6481,10 +6469,10 @@
         <v>1.28</v>
       </c>
       <c r="I103" t="n">
-        <v>0.04631503108128192</v>
+        <v>0.749</v>
       </c>
       <c r="J103" t="n">
-        <v>0.9726156527069203</v>
+        <v>15.729</v>
       </c>
     </row>
     <row r="104">
@@ -6508,7 +6496,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -6521,10 +6509,10 @@
         <v>1.16</v>
       </c>
       <c r="I104" t="n">
-        <v>0.02414384509194363</v>
+        <v>0.4115</v>
       </c>
       <c r="J104" t="n">
-        <v>0.5070207469308162</v>
+        <v>8.641500000000001</v>
       </c>
     </row>
     <row r="105">
@@ -6548,7 +6536,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -6561,10 +6549,10 @@
         <v>1.06</v>
       </c>
       <c r="I105" t="n">
-        <v>0.003158911057708729</v>
+        <v>0.1191</v>
       </c>
       <c r="J105" t="n">
-        <v>0.06633713221188331</v>
+        <v>2.5011</v>
       </c>
     </row>
     <row r="106">
@@ -6588,7 +6576,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -6601,10 +6589,10 @@
         <v>0.95</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.02098708023210562</v>
+        <v>-0.3258</v>
       </c>
       <c r="J106" t="n">
-        <v>-0.4407286848742181</v>
+        <v>-6.8418</v>
       </c>
     </row>
     <row r="107">
@@ -6628,7 +6616,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -6641,10 +6629,10 @@
         <v>1.14</v>
       </c>
       <c r="I107" t="n">
-        <v>0.03096559021979568</v>
+        <v>0.3243</v>
       </c>
       <c r="J107" t="n">
-        <v>0.6502773946157092</v>
+        <v>6.8103</v>
       </c>
     </row>
     <row r="108">
@@ -6668,7 +6656,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -6681,10 +6669,10 @@
         <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.01964523575236966</v>
+        <v>0.0461</v>
       </c>
       <c r="J108" t="n">
-        <v>0.4125499507997629</v>
+        <v>0.9681</v>
       </c>
     </row>
     <row r="109">
@@ -6708,7 +6696,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -6721,10 +6709,10 @@
         <v>0.83</v>
       </c>
       <c r="I109" t="n">
-        <v>0.007692616393706954</v>
+        <v>-0.3145</v>
       </c>
       <c r="J109" t="n">
-        <v>0.161544944267846</v>
+        <v>-6.6045</v>
       </c>
     </row>
     <row r="110">
@@ -6748,7 +6736,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -6761,10 +6749,10 @@
         <v>0.83</v>
       </c>
       <c r="I110" t="n">
-        <v>0.007692616393706954</v>
+        <v>-0.3145</v>
       </c>
       <c r="J110" t="n">
-        <v>0.161544944267846</v>
+        <v>-6.6045</v>
       </c>
     </row>
     <row r="111">
@@ -6788,7 +6776,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -6801,10 +6789,10 @@
         <v>0.78</v>
       </c>
       <c r="I111" t="n">
-        <v>0.003703380347211051</v>
+        <v>-0.3908</v>
       </c>
       <c r="J111" t="n">
-        <v>0.07777098729143206</v>
+        <v>-8.206799999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6828,7 +6816,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -6841,10 +6829,10 @@
         <v>1.11</v>
       </c>
       <c r="I112" t="n">
-        <v>0.03708183432549336</v>
+        <v>0.2666</v>
       </c>
       <c r="J112" t="n">
-        <v>0.8158003551608539</v>
+        <v>5.8652</v>
       </c>
     </row>
     <row r="113">
@@ -6868,7 +6856,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -6881,10 +6869,10 @@
         <v>0.97</v>
       </c>
       <c r="I113" t="n">
-        <v>0.01618159314434925</v>
+        <v>-0.0511</v>
       </c>
       <c r="J113" t="n">
-        <v>0.3559950491756835</v>
+        <v>-1.1242</v>
       </c>
     </row>
     <row r="114">
@@ -6908,7 +6896,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -6921,10 +6909,10 @@
         <v>0.92</v>
       </c>
       <c r="I114" t="n">
-        <v>0.01034082521573495</v>
+        <v>-0.1682</v>
       </c>
       <c r="J114" t="n">
-        <v>0.2274981547461689</v>
+        <v>-3.7004</v>
       </c>
     </row>
     <row r="115">
@@ -6948,7 +6936,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -6961,10 +6949,10 @@
         <v>0.89</v>
       </c>
       <c r="I115" t="n">
-        <v>0.006175637596780352</v>
+        <v>-0.2242</v>
       </c>
       <c r="J115" t="n">
-        <v>0.1358640271291677</v>
+        <v>-4.9324</v>
       </c>
     </row>
     <row r="116">
@@ -6988,7 +6976,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -7001,10 +6989,10 @@
         <v>0.82</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.004481235229308659</v>
+        <v>-0.3386</v>
       </c>
       <c r="J116" t="n">
-        <v>-0.0985871750447905</v>
+        <v>-7.4492</v>
       </c>
     </row>
     <row r="117">
@@ -7028,7 +7016,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -7041,10 +7029,10 @@
         <v>1.31</v>
       </c>
       <c r="I117" t="n">
-        <v>0.05124961702227133</v>
+        <v>0.86</v>
       </c>
       <c r="J117" t="n">
-        <v>1.127491574489969</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="118">
@@ -7068,7 +7056,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -7081,10 +7069,10 @@
         <v>1.28</v>
       </c>
       <c r="I118" t="n">
-        <v>0.04647924439448368</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="J118" t="n">
-        <v>1.022543376678641</v>
+        <v>17.3976</v>
       </c>
     </row>
     <row r="119">
@@ -7108,7 +7096,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -7121,10 +7109,10 @@
         <v>1.22</v>
       </c>
       <c r="I119" t="n">
-        <v>0.03705488365102692</v>
+        <v>0.6452</v>
       </c>
       <c r="J119" t="n">
-        <v>0.8152074403225923</v>
+        <v>14.1944</v>
       </c>
     </row>
     <row r="120">
@@ -7148,7 +7136,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -7161,10 +7149,10 @@
         <v>0.95</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.001378410262629637</v>
+        <v>-0.299</v>
       </c>
       <c r="J120" t="n">
-        <v>-0.03032502577785201</v>
+        <v>-6.578</v>
       </c>
     </row>
     <row r="121">
@@ -7188,7 +7176,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -7201,10 +7189,10 @@
         <v>0.84</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.01833196712269557</v>
+        <v>-0.6098</v>
       </c>
       <c r="J121" t="n">
-        <v>-0.4033032766993025</v>
+        <v>-13.4156</v>
       </c>
     </row>
     <row r="122">
@@ -7228,7 +7216,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -7241,10 +7229,10 @@
         <v>1.54</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1045899506106139</v>
+        <v>0.8333</v>
       </c>
       <c r="J122" t="n">
-        <v>2.510158814654734</v>
+        <v>19.9992</v>
       </c>
     </row>
     <row r="123">
@@ -7268,7 +7256,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -7281,10 +7269,10 @@
         <v>1.03</v>
       </c>
       <c r="I123" t="n">
-        <v>0.02622187313492404</v>
+        <v>0.1225</v>
       </c>
       <c r="J123" t="n">
-        <v>0.6293249552381769</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="124">
@@ -7308,7 +7296,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -7321,10 +7309,10 @@
         <v>0.76</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.01257383655984965</v>
+        <v>-0.4241</v>
       </c>
       <c r="J124" t="n">
-        <v>-0.3017720774363917</v>
+        <v>-10.1784</v>
       </c>
     </row>
     <row r="125">
@@ -7348,7 +7336,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -7361,10 +7349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.02371228367532527</v>
+        <v>-0.52</v>
       </c>
       <c r="J125" t="n">
-        <v>-0.5690948082078063</v>
+        <v>-12.48</v>
       </c>
     </row>
     <row r="126">
@@ -7388,7 +7376,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -7401,10 +7389,10 @@
         <v>0.64</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.03162743537174034</v>
+        <v>-0.5849</v>
       </c>
       <c r="J126" t="n">
-        <v>-0.7590584489217682</v>
+        <v>-14.0376</v>
       </c>
     </row>
     <row r="127">
@@ -7428,7 +7416,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -7441,10 +7429,10 @@
         <v>1.35</v>
       </c>
       <c r="I127" t="n">
-        <v>0.05844079242756195</v>
+        <v>0.9516</v>
       </c>
       <c r="J127" t="n">
-        <v>1.402579018261487</v>
+        <v>22.8384</v>
       </c>
     </row>
     <row r="128">
@@ -7468,7 +7456,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -7481,10 +7469,10 @@
         <v>1.34</v>
       </c>
       <c r="I128" t="n">
-        <v>0.05685016147731348</v>
+        <v>0.9295</v>
       </c>
       <c r="J128" t="n">
-        <v>1.364403875455523</v>
+        <v>22.308</v>
       </c>
     </row>
     <row r="129">
@@ -7508,7 +7496,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -7521,10 +7509,10 @@
         <v>1</v>
       </c>
       <c r="I129" t="n">
-        <v>0.007019073645779153</v>
+        <v>-0.0878</v>
       </c>
       <c r="J129" t="n">
-        <v>0.1684577674986997</v>
+        <v>-2.1072</v>
       </c>
     </row>
     <row r="130">
@@ -7548,7 +7536,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -7561,10 +7549,10 @@
         <v>0.98</v>
       </c>
       <c r="I130" t="n">
-        <v>0.00394068454050224</v>
+        <v>-0.19</v>
       </c>
       <c r="J130" t="n">
-        <v>0.09457642897205376</v>
+        <v>-4.56</v>
       </c>
     </row>
     <row r="131">
@@ -7588,7 +7576,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -7601,10 +7589,10 @@
         <v>0.91</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.006573551526714135</v>
+        <v>-0.4199</v>
       </c>
       <c r="J131" t="n">
-        <v>-0.1577652366411392</v>
+        <v>-10.0776</v>
       </c>
     </row>
     <row r="132">
@@ -7628,7 +7616,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -7641,10 +7629,10 @@
         <v>1.74</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1524574958956902</v>
+        <v>0.9202</v>
       </c>
       <c r="J132" t="n">
-        <v>2.439319934331043</v>
+        <v>14.7232</v>
       </c>
     </row>
     <row r="133">
@@ -7668,7 +7656,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -7681,10 +7669,10 @@
         <v>1.52</v>
       </c>
       <c r="I133" t="n">
-        <v>0.09135689491090324</v>
+        <v>0.68</v>
       </c>
       <c r="J133" t="n">
-        <v>1.461710318574452</v>
+        <v>10.88</v>
       </c>
     </row>
     <row r="134">
@@ -7708,7 +7696,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -7721,10 +7709,10 @@
         <v>1.35</v>
       </c>
       <c r="I134" t="n">
-        <v>0.04866675638965409</v>
+        <v>0.4538</v>
       </c>
       <c r="J134" t="n">
-        <v>0.7786681022344655</v>
+        <v>7.2608</v>
       </c>
     </row>
     <row r="135">
@@ -7748,7 +7736,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -7761,10 +7749,10 @@
         <v>1.19</v>
       </c>
       <c r="I135" t="n">
-        <v>0.005698390842863792</v>
+        <v>0.2328</v>
       </c>
       <c r="J135" t="n">
-        <v>0.09117425348582067</v>
+        <v>3.7248</v>
       </c>
     </row>
     <row r="136">
@@ -7788,7 +7776,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -7801,10 +7789,10 @@
         <v>1.02</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.04319811652981104</v>
+        <v>-0.0429</v>
       </c>
       <c r="J136" t="n">
-        <v>-0.6911698644769766</v>
+        <v>-0.6864</v>
       </c>
     </row>
     <row r="137">
@@ -7828,7 +7816,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -7841,10 +7829,10 @@
         <v>1.24</v>
       </c>
       <c r="I137" t="n">
-        <v>0.04541707282961711</v>
+        <v>0.5344</v>
       </c>
       <c r="J137" t="n">
-        <v>0.7266731652738738</v>
+        <v>8.5504</v>
       </c>
     </row>
     <row r="138">
@@ -7868,7 +7856,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -7881,10 +7869,10 @@
         <v>0.88</v>
       </c>
       <c r="I138" t="n">
-        <v>0.01748054477648847</v>
+        <v>-0.1353</v>
       </c>
       <c r="J138" t="n">
-        <v>0.2796887164238155</v>
+        <v>-2.1648</v>
       </c>
     </row>
     <row r="139">
@@ -7908,7 +7896,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -7921,10 +7909,10 @@
         <v>0.79</v>
       </c>
       <c r="I139" t="n">
-        <v>0.01090697442562011</v>
+        <v>-0.2866</v>
       </c>
       <c r="J139" t="n">
-        <v>0.1745115908099218</v>
+        <v>-4.5856</v>
       </c>
     </row>
     <row r="140">
@@ -7948,7 +7936,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -7961,10 +7949,10 @@
         <v>0.51</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.008871712528689509</v>
+        <v>-0.713</v>
       </c>
       <c r="J140" t="n">
-        <v>-0.1419474004590321</v>
+        <v>-11.408</v>
       </c>
     </row>
     <row r="141">
@@ -7988,7 +7976,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -8001,10 +7989,10 @@
         <v>0.36</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.02013462980309811</v>
+        <v>-0.8945</v>
       </c>
       <c r="J141" t="n">
-        <v>-0.3221540768495697</v>
+        <v>-14.312</v>
       </c>
     </row>
     <row r="142">
@@ -8028,7 +8016,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -8041,10 +8029,10 @@
         <v>0.71</v>
       </c>
       <c r="I142" t="n">
-        <v>0.000118824813921746</v>
+        <v>-0.3665</v>
       </c>
       <c r="J142" t="n">
-        <v>0.00178237220882619</v>
+        <v>-5.4975</v>
       </c>
     </row>
     <row r="143">
@@ -8068,7 +8056,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -8081,10 +8069,10 @@
         <v>0.7</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.001095741320059108</v>
+        <v>-0.3832</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.01643611980088663</v>
+        <v>-5.748</v>
       </c>
     </row>
     <row r="144">
@@ -8108,7 +8096,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -8121,10 +8109,10 @@
         <v>0.68</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.003348825631580125</v>
+        <v>-0.4185</v>
       </c>
       <c r="J144" t="n">
-        <v>-0.05023238447370187</v>
+        <v>-6.2775</v>
       </c>
     </row>
     <row r="145">
@@ -8148,7 +8136,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -8161,10 +8149,10 @@
         <v>0.66</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.005125379829999707</v>
+        <v>-0.4639</v>
       </c>
       <c r="J145" t="n">
-        <v>-0.07688069744999561</v>
+        <v>-6.9585</v>
       </c>
     </row>
     <row r="146">
@@ -8188,7 +8176,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -8201,10 +8189,10 @@
         <v>0.59</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.013578723444101</v>
+        <v>-0.5774</v>
       </c>
       <c r="J146" t="n">
-        <v>-0.2036808516615151</v>
+        <v>-8.661</v>
       </c>
     </row>
     <row r="147">
@@ -8228,7 +8216,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -8241,10 +8229,10 @@
         <v>1.83</v>
       </c>
       <c r="I147" t="n">
-        <v>0.08915845443390275</v>
+        <v>1.6952</v>
       </c>
       <c r="J147" t="n">
-        <v>1.337376816508541</v>
+        <v>25.428</v>
       </c>
     </row>
     <row r="148">
@@ -8268,7 +8256,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -8281,10 +8269,10 @@
         <v>1.56</v>
       </c>
       <c r="I148" t="n">
-        <v>0.04905697014410856</v>
+        <v>1.193</v>
       </c>
       <c r="J148" t="n">
-        <v>0.7358545521616284</v>
+        <v>17.895</v>
       </c>
     </row>
     <row r="149">
@@ -8308,7 +8296,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -8321,10 +8309,10 @@
         <v>1.47</v>
       </c>
       <c r="I149" t="n">
-        <v>0.03830031000920663</v>
+        <v>0.9781</v>
       </c>
       <c r="J149" t="n">
-        <v>0.5745046501380994</v>
+        <v>14.6715</v>
       </c>
     </row>
     <row r="150">
@@ -8348,7 +8336,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -8361,10 +8349,10 @@
         <v>1.34</v>
       </c>
       <c r="I150" t="n">
-        <v>0.01922660995463334</v>
+        <v>0.697</v>
       </c>
       <c r="J150" t="n">
-        <v>0.2883991493195002</v>
+        <v>10.455</v>
       </c>
     </row>
     <row r="151">
@@ -8388,7 +8376,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -8401,10 +8389,10 @@
         <v>1.33</v>
       </c>
       <c r="I151" t="n">
-        <v>0.01768906693792211</v>
+        <v>0.6753</v>
       </c>
       <c r="J151" t="n">
-        <v>0.2653360040688317</v>
+        <v>10.1295</v>
       </c>
     </row>
     <row r="152">
@@ -8428,7 +8416,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -8441,10 +8429,10 @@
         <v>1.44</v>
       </c>
       <c r="I152" t="n">
-        <v>0.07978360499846246</v>
+        <v>0.7153</v>
       </c>
       <c r="J152" t="n">
-        <v>1.755239309966174</v>
+        <v>15.7366</v>
       </c>
     </row>
     <row r="153">
@@ -8468,7 +8456,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -8481,10 +8469,10 @@
         <v>1.08</v>
       </c>
       <c r="I153" t="n">
-        <v>0.02945503479414448</v>
+        <v>0.2171</v>
       </c>
       <c r="J153" t="n">
-        <v>0.6480107654711785</v>
+        <v>4.7762</v>
       </c>
     </row>
     <row r="154">
@@ -8508,7 +8496,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -8521,10 +8509,10 @@
         <v>0.84</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.001366827922477585</v>
+        <v>-0.3062</v>
       </c>
       <c r="J154" t="n">
-        <v>-0.03007021429450687</v>
+        <v>-6.7364</v>
       </c>
     </row>
     <row r="155">
@@ -8548,7 +8536,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -8561,10 +8549,10 @@
         <v>0.67</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.02559793663979055</v>
+        <v>-0.5475</v>
       </c>
       <c r="J155" t="n">
-        <v>-0.563154606075392</v>
+        <v>-12.045</v>
       </c>
     </row>
     <row r="156">
@@ -8588,7 +8576,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -8601,10 +8589,10 @@
         <v>0.66</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.02702190509284087</v>
+        <v>-0.5604</v>
       </c>
       <c r="J156" t="n">
-        <v>-0.5944819120424991</v>
+        <v>-12.3288</v>
       </c>
     </row>
     <row r="157">
@@ -8628,7 +8616,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -8641,10 +8629,10 @@
         <v>1.79</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1134635097837201</v>
+        <v>1.7422</v>
       </c>
       <c r="J157" t="n">
-        <v>2.496197215241843</v>
+        <v>38.3284</v>
       </c>
     </row>
     <row r="158">
@@ -8668,7 +8656,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -8681,10 +8669,10 @@
         <v>1.27</v>
       </c>
       <c r="I158" t="n">
-        <v>0.03492613774367579</v>
+        <v>0.7198</v>
       </c>
       <c r="J158" t="n">
-        <v>0.7683750303608674</v>
+        <v>15.8356</v>
       </c>
     </row>
     <row r="159">
@@ -8708,7 +8696,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -8721,10 +8709,10 @@
         <v>1.26</v>
       </c>
       <c r="I159" t="n">
-        <v>0.03346334773488162</v>
+        <v>0.695</v>
       </c>
       <c r="J159" t="n">
-        <v>0.7361936501673956</v>
+        <v>15.29</v>
       </c>
     </row>
     <row r="160">
@@ -8748,7 +8736,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -8761,10 +8749,10 @@
         <v>0.88</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.02156821552784401</v>
+        <v>-0.5303</v>
       </c>
       <c r="J160" t="n">
-        <v>-0.4745007416125682</v>
+        <v>-11.6666</v>
       </c>
     </row>
     <row r="161">
@@ -8788,7 +8776,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -8801,10 +8789,10 @@
         <v>0.8</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.03387213229477555</v>
+        <v>-0.7299</v>
       </c>
       <c r="J161" t="n">
-        <v>-0.7451869104850621</v>
+        <v>-16.0578</v>
       </c>
     </row>
     <row r="162">
@@ -8828,7 +8816,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -8841,10 +8829,10 @@
         <v>1.18</v>
       </c>
       <c r="I162" t="n">
-        <v>0.03736691570690751</v>
+        <v>0.3551</v>
       </c>
       <c r="J162" t="n">
-        <v>1.121007471207225</v>
+        <v>10.653</v>
       </c>
     </row>
     <row r="163">
@@ -8868,7 +8856,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -8881,10 +8869,10 @@
         <v>1.15</v>
       </c>
       <c r="I163" t="n">
-        <v>0.03344911499987124</v>
+        <v>0.3098</v>
       </c>
       <c r="J163" t="n">
-        <v>1.003473449996137</v>
+        <v>9.294</v>
       </c>
     </row>
     <row r="164">
@@ -8908,7 +8896,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -8921,10 +8909,10 @@
         <v>1.01</v>
       </c>
       <c r="I164" t="n">
-        <v>0.01685951858561248</v>
+        <v>0.0418</v>
       </c>
       <c r="J164" t="n">
-        <v>0.5057855575683743</v>
+        <v>1.254</v>
       </c>
     </row>
     <row r="165">
@@ -8948,7 +8936,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -8961,10 +8949,10 @@
         <v>0.96</v>
       </c>
       <c r="I165" t="n">
-        <v>0.01193473922642046</v>
+        <v>-0.1136</v>
       </c>
       <c r="J165" t="n">
-        <v>0.3580421767926137</v>
+        <v>-3.408</v>
       </c>
     </row>
     <row r="166">
@@ -8988,7 +8976,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -9001,10 +8989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.02326430209814392</v>
+        <v>-0.5329</v>
       </c>
       <c r="J166" t="n">
-        <v>-0.6979290629443177</v>
+        <v>-15.987</v>
       </c>
     </row>
     <row r="167">
@@ -9028,7 +9016,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -9041,10 +9029,10 @@
         <v>1.4</v>
       </c>
       <c r="I167" t="n">
-        <v>0.0750327620937211</v>
+        <v>1.0701</v>
       </c>
       <c r="J167" t="n">
-        <v>2.250982862811633</v>
+        <v>32.103</v>
       </c>
     </row>
     <row r="168">
@@ -9068,7 +9056,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -9081,10 +9069,10 @@
         <v>1.09</v>
       </c>
       <c r="I168" t="n">
-        <v>0.02039058664628582</v>
+        <v>0.2766</v>
       </c>
       <c r="J168" t="n">
-        <v>0.6117175993885746</v>
+        <v>8.298</v>
       </c>
     </row>
     <row r="169">
@@ -9108,7 +9096,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -9121,10 +9109,10 @@
         <v>1.05</v>
       </c>
       <c r="I169" t="n">
-        <v>0.01438702442530046</v>
+        <v>0.138</v>
       </c>
       <c r="J169" t="n">
-        <v>0.4316107327590138</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="170">
@@ -9148,7 +9136,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -9161,10 +9149,10 @@
         <v>0.97</v>
       </c>
       <c r="I170" t="n">
-        <v>0.001021026361244105</v>
+        <v>-0.219</v>
       </c>
       <c r="J170" t="n">
-        <v>0.03063079083732316</v>
+        <v>-6.57</v>
       </c>
     </row>
     <row r="171">
@@ -9188,7 +9176,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -9201,10 +9189,10 @@
         <v>0.97</v>
       </c>
       <c r="I171" t="n">
-        <v>0.001021026361244105</v>
+        <v>-0.219</v>
       </c>
       <c r="J171" t="n">
-        <v>0.03063079083732316</v>
+        <v>-6.57</v>
       </c>
     </row>
     <row r="172">
@@ -9228,7 +9216,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -9241,10 +9229,10 @@
         <v>0.97</v>
       </c>
       <c r="I172" t="n">
-        <v>0.01834076714063585</v>
+        <v>-0.0156</v>
       </c>
       <c r="J172" t="n">
-        <v>0.3851561099533529</v>
+        <v>-0.3276</v>
       </c>
     </row>
     <row r="173">
@@ -9268,7 +9256,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -9281,10 +9269,10 @@
         <v>0.97</v>
       </c>
       <c r="I173" t="n">
-        <v>0.01834076714063585</v>
+        <v>-0.0156</v>
       </c>
       <c r="J173" t="n">
-        <v>0.3851561099533529</v>
+        <v>-0.3276</v>
       </c>
     </row>
     <row r="174">
@@ -9308,7 +9296,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -9321,10 +9309,10 @@
         <v>0.96</v>
       </c>
       <c r="I174" t="n">
-        <v>0.01705798055637868</v>
+        <v>-0.0371</v>
       </c>
       <c r="J174" t="n">
-        <v>0.3582175916839522</v>
+        <v>-0.7791</v>
       </c>
     </row>
     <row r="175">
@@ -9348,7 +9336,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -9361,10 +9349,10 @@
         <v>0.95</v>
       </c>
       <c r="I175" t="n">
-        <v>0.01578730269117056</v>
+        <v>-0.0576</v>
       </c>
       <c r="J175" t="n">
-        <v>0.3315333565145819</v>
+        <v>-1.2096</v>
       </c>
     </row>
     <row r="176">
@@ -9388,7 +9376,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -9401,10 +9389,10 @@
         <v>0.48</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.04198549885669127</v>
+        <v>-0.7698</v>
       </c>
       <c r="J176" t="n">
-        <v>-0.8816954759905167</v>
+        <v>-16.1658</v>
       </c>
     </row>
     <row r="177">
@@ -9428,7 +9416,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -9441,10 +9429,10 @@
         <v>1.96</v>
       </c>
       <c r="I177" t="n">
-        <v>0.1439684170752203</v>
+        <v>1.8742</v>
       </c>
       <c r="J177" t="n">
-        <v>3.023336758579627</v>
+        <v>39.3582</v>
       </c>
     </row>
     <row r="178">
@@ -9468,7 +9456,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -9481,10 +9469,10 @@
         <v>1.67</v>
       </c>
       <c r="I178" t="n">
-        <v>0.09453111568346828</v>
+        <v>1.49</v>
       </c>
       <c r="J178" t="n">
-        <v>1.985153429352834</v>
+        <v>31.29</v>
       </c>
     </row>
     <row r="179">
@@ -9508,7 +9496,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -9521,10 +9509,10 @@
         <v>1.1</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.005047110585048389</v>
+        <v>0.1858</v>
       </c>
       <c r="J179" t="n">
-        <v>-0.1059893222860162</v>
+        <v>3.9018</v>
       </c>
     </row>
     <row r="180">
@@ -9548,7 +9536,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -9561,10 +9549,10 @@
         <v>1.03</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0180979782572657</v>
+        <v>-0.0276</v>
       </c>
       <c r="J180" t="n">
-        <v>-0.3800575434025797</v>
+        <v>-0.5796</v>
       </c>
     </row>
     <row r="181">
@@ -9588,7 +9576,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -9601,10 +9589,10 @@
         <v>0.87</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.04679683655116658</v>
+        <v>-0.5874</v>
       </c>
       <c r="J181" t="n">
-        <v>-0.9827335675744981</v>
+        <v>-12.3354</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/8246/event_8246_evp_summary.xlsx
+++ b/database/event/8246/event_8246_evp_summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EVP_Summary_8246" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVP_Summary_8246" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,7 +502,7 @@
         <v>2.1353</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5695</v>
+        <v>1.8212</v>
       </c>
       <c r="E2" t="n">
         <v>5.5513</v>
@@ -548,7 +548,7 @@
         <v>1.6309</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0843</v>
+        <v>1.2915</v>
       </c>
       <c r="E3" t="n">
         <v>4.24</v>
@@ -594,7 +594,7 @@
         <v>1.6307</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0841</v>
+        <v>1.2913</v>
       </c>
       <c r="E4" t="n">
         <v>4.2395</v>
@@ -640,7 +640,7 @@
         <v>1.4341</v>
       </c>
       <c r="D5" t="n">
-        <v>0.895</v>
+        <v>1.0848</v>
       </c>
       <c r="E5" t="n">
         <v>3.7284</v>
@@ -686,7 +686,7 @@
         <v>1.2161</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6853</v>
+        <v>0.8559</v>
       </c>
       <c r="E6" t="n">
         <v>3.1616</v>
@@ -732,7 +732,7 @@
         <v>0.9584</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4373</v>
+        <v>0.5851</v>
       </c>
       <c r="E7" t="n">
         <v>2.4915</v>
@@ -778,7 +778,7 @@
         <v>0.888</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3696</v>
+        <v>0.5112</v>
       </c>
       <c r="E8" t="n">
         <v>2.3085</v>
@@ -824,7 +824,7 @@
         <v>0.884</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3659</v>
+        <v>0.5071</v>
       </c>
       <c r="E9" t="n">
         <v>2.2983</v>
@@ -870,7 +870,7 @@
         <v>0.7354000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2229</v>
+        <v>0.351</v>
       </c>
       <c r="E10" t="n">
         <v>1.9119</v>
@@ -916,7 +916,7 @@
         <v>0.6884</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1776</v>
+        <v>0.3016</v>
       </c>
       <c r="E11" t="n">
         <v>1.7896</v>
@@ -962,7 +962,7 @@
         <v>0.6875</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1768</v>
+        <v>0.3007</v>
       </c>
       <c r="E12" t="n">
         <v>1.7874</v>
@@ -1008,7 +1008,7 @@
         <v>0.55</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0445</v>
+        <v>0.1563</v>
       </c>
       <c r="E13" t="n">
         <v>1.4299</v>
@@ -1054,7 +1054,7 @@
         <v>0.5144</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0103</v>
+        <v>0.1189</v>
       </c>
       <c r="E14" t="n">
         <v>1.3374</v>
@@ -1100,7 +1100,7 @@
         <v>0.4997</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0039</v>
+        <v>0.1034</v>
       </c>
       <c r="E15" t="n">
         <v>1.299</v>
@@ -1146,7 +1146,7 @@
         <v>0.4552</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0467</v>
+        <v>0.0567</v>
       </c>
       <c r="E16" t="n">
         <v>1.1834</v>
@@ -1192,7 +1192,7 @@
         <v>0.2549</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2394</v>
+        <v>-0.1537</v>
       </c>
       <c r="E17" t="n">
         <v>0.6626</v>
@@ -1238,7 +1238,7 @@
         <v>0.2448</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.249</v>
+        <v>-0.1642</v>
       </c>
       <c r="E18" t="n">
         <v>0.6365</v>
@@ -1284,7 +1284,7 @@
         <v>0.1988</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2933</v>
+        <v>-0.2125</v>
       </c>
       <c r="E19" t="n">
         <v>0.5169</v>
@@ -1330,7 +1330,7 @@
         <v>0.19</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3018</v>
+        <v>-0.2218</v>
       </c>
       <c r="E20" t="n">
         <v>0.4939</v>
@@ -1376,7 +1376,7 @@
         <v>0.1488</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3414</v>
+        <v>-0.2651</v>
       </c>
       <c r="E21" t="n">
         <v>0.3868</v>
@@ -1422,7 +1422,7 @@
         <v>0.1471</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.343</v>
+        <v>-0.2668</v>
       </c>
       <c r="E22" t="n">
         <v>0.3825</v>
@@ -1468,7 +1468,7 @@
         <v>0.1183</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3707</v>
+        <v>-0.2971</v>
       </c>
       <c r="E23" t="n">
         <v>0.3076</v>
@@ -1514,7 +1514,7 @@
         <v>0.118</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.371</v>
+        <v>-0.2975</v>
       </c>
       <c r="E24" t="n">
         <v>0.3067</v>
@@ -1560,7 +1560,7 @@
         <v>0.1089</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3798</v>
+        <v>-0.307</v>
       </c>
       <c r="E25" t="n">
         <v>0.2831</v>
@@ -1606,7 +1606,7 @@
         <v>0.0357</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4502</v>
+        <v>-0.3839</v>
       </c>
       <c r="E26" t="n">
         <v>0.09279999999999999</v>
@@ -1652,7 +1652,7 @@
         <v>0.0183</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4669</v>
+        <v>-0.4021</v>
       </c>
       <c r="E27" t="n">
         <v>0.0476</v>
@@ -1698,7 +1698,7 @@
         <v>0.0157</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4694</v>
+        <v>-0.4049</v>
       </c>
       <c r="E28" t="n">
         <v>0.0408</v>
@@ -1744,7 +1744,7 @@
         <v>0.0023</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4823</v>
+        <v>-0.4189</v>
       </c>
       <c r="E29" t="n">
         <v>0.0061</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0253</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5089</v>
+        <v>-0.448</v>
       </c>
       <c r="E30" t="n">
         <v>-0.0659</v>
@@ -1836,7 +1836,7 @@
         <v>-0.0646</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5467</v>
+        <v>-0.4892</v>
       </c>
       <c r="E31" t="n">
         <v>-0.168</v>
@@ -1882,7 +1882,7 @@
         <v>-0.0727</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5544</v>
+        <v>-0.4977</v>
       </c>
       <c r="E32" t="n">
         <v>-0.189</v>
@@ -1928,7 +1928,7 @@
         <v>-0.2385</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7139</v>
+        <v>-0.6718</v>
       </c>
       <c r="E33" t="n">
         <v>-0.62</v>
@@ -1974,7 +1974,7 @@
         <v>-0.3242</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7964</v>
+        <v>-0.7618</v>
       </c>
       <c r="E34" t="n">
         <v>-0.8428</v>
@@ -2020,7 +2020,7 @@
         <v>-0.3402</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8117</v>
+        <v>-0.7786</v>
       </c>
       <c r="E35" t="n">
         <v>-0.8844</v>
@@ -2066,7 +2066,7 @@
         <v>-0.3441</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8156</v>
+        <v>-0.7828000000000001</v>
       </c>
       <c r="E36" t="n">
         <v>-0.8947000000000001</v>
@@ -2112,7 +2112,7 @@
         <v>-0.4618</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9287</v>
+        <v>-0.9064</v>
       </c>
       <c r="E37" t="n">
         <v>-1.2006</v>
@@ -2158,7 +2158,7 @@
         <v>-0.4708</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9374</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="E38" t="n">
         <v>-1.224</v>
@@ -2204,7 +2204,7 @@
         <v>-0.5</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9655</v>
+        <v>-0.9465</v>
       </c>
       <c r="E39" t="n">
         <v>-1.3</v>
@@ -2250,7 +2250,7 @@
         <v>-0.5</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.9655</v>
+        <v>-0.9465</v>
       </c>
       <c r="E40" t="n">
         <v>-1.3</v>
@@ -2296,7 +2296,7 @@
         <v>-0.5784</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.0409</v>
+        <v>-1.0289</v>
       </c>
       <c r="E41" t="n">
         <v>-1.5038</v>

--- a/database/event/8246/event_8246_evp_summary.xlsx
+++ b/database/event/8246/event_8246_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>2.1353</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8212</v>
+        <v>1.7677</v>
       </c>
       <c r="E2" t="n">
         <v>5.5513</v>
@@ -548,7 +548,7 @@
         <v>1.6309</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2915</v>
+        <v>1.2453</v>
       </c>
       <c r="E3" t="n">
         <v>4.24</v>
@@ -594,7 +594,7 @@
         <v>1.6307</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2913</v>
+        <v>1.2451</v>
       </c>
       <c r="E4" t="n">
         <v>4.2395</v>
@@ -640,7 +640,7 @@
         <v>1.4341</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0848</v>
+        <v>1.0415</v>
       </c>
       <c r="E5" t="n">
         <v>3.7284</v>
@@ -686,7 +686,7 @@
         <v>1.2161</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8559</v>
+        <v>0.8157</v>
       </c>
       <c r="E6" t="n">
         <v>3.1616</v>
@@ -732,7 +732,7 @@
         <v>0.9584</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5851</v>
+        <v>0.5487</v>
       </c>
       <c r="E7" t="n">
         <v>2.4915</v>
@@ -778,7 +778,7 @@
         <v>0.888</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5112</v>
+        <v>0.4758</v>
       </c>
       <c r="E8" t="n">
         <v>2.3085</v>
@@ -824,7 +824,7 @@
         <v>0.884</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5071</v>
+        <v>0.4717</v>
       </c>
       <c r="E9" t="n">
         <v>2.2983</v>
@@ -870,7 +870,7 @@
         <v>0.7354000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.351</v>
+        <v>0.3178</v>
       </c>
       <c r="E10" t="n">
         <v>1.9119</v>
@@ -916,7 +916,7 @@
         <v>0.6884</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3016</v>
+        <v>0.2691</v>
       </c>
       <c r="E11" t="n">
         <v>1.7896</v>
@@ -962,7 +962,7 @@
         <v>0.6875</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3007</v>
+        <v>0.2682</v>
       </c>
       <c r="E12" t="n">
         <v>1.7874</v>
@@ -1008,7 +1008,7 @@
         <v>0.55</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1563</v>
+        <v>0.1258</v>
       </c>
       <c r="E13" t="n">
         <v>1.4299</v>
@@ -1054,7 +1054,7 @@
         <v>0.5144</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1189</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="E14" t="n">
         <v>1.3374</v>
@@ -1100,7 +1100,7 @@
         <v>0.4997</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1034</v>
+        <v>0.0736</v>
       </c>
       <c r="E15" t="n">
         <v>1.299</v>
@@ -1146,7 +1146,7 @@
         <v>0.4552</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0567</v>
+        <v>0.0276</v>
       </c>
       <c r="E16" t="n">
         <v>1.1834</v>
@@ -1192,7 +1192,7 @@
         <v>0.2549</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1537</v>
+        <v>-0.1799</v>
       </c>
       <c r="E17" t="n">
         <v>0.6626</v>
@@ -1238,7 +1238,7 @@
         <v>0.2448</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1642</v>
+        <v>-0.1903</v>
       </c>
       <c r="E18" t="n">
         <v>0.6365</v>
@@ -1284,7 +1284,7 @@
         <v>0.1988</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2125</v>
+        <v>-0.238</v>
       </c>
       <c r="E19" t="n">
         <v>0.5169</v>
@@ -1330,7 +1330,7 @@
         <v>0.19</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2218</v>
+        <v>-0.2471</v>
       </c>
       <c r="E20" t="n">
         <v>0.4939</v>
@@ -1376,7 +1376,7 @@
         <v>0.1488</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2651</v>
+        <v>-0.2898</v>
       </c>
       <c r="E21" t="n">
         <v>0.3868</v>
@@ -1422,7 +1422,7 @@
         <v>0.1471</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2668</v>
+        <v>-0.2915</v>
       </c>
       <c r="E22" t="n">
         <v>0.3825</v>
@@ -1468,7 +1468,7 @@
         <v>0.1183</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2971</v>
+        <v>-0.3214</v>
       </c>
       <c r="E23" t="n">
         <v>0.3076</v>
@@ -1514,7 +1514,7 @@
         <v>0.118</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2975</v>
+        <v>-0.3217</v>
       </c>
       <c r="E24" t="n">
         <v>0.3067</v>
@@ -1560,7 +1560,7 @@
         <v>0.1089</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.307</v>
+        <v>-0.3311</v>
       </c>
       <c r="E25" t="n">
         <v>0.2831</v>
@@ -1606,7 +1606,7 @@
         <v>0.0357</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3839</v>
+        <v>-0.4069</v>
       </c>
       <c r="E26" t="n">
         <v>0.09279999999999999</v>
@@ -1652,7 +1652,7 @@
         <v>0.0183</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4021</v>
+        <v>-0.4249</v>
       </c>
       <c r="E27" t="n">
         <v>0.0476</v>
@@ -1698,7 +1698,7 @@
         <v>0.0157</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4049</v>
+        <v>-0.4277</v>
       </c>
       <c r="E28" t="n">
         <v>0.0408</v>
@@ -1744,7 +1744,7 @@
         <v>0.0023</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4189</v>
+        <v>-0.4415</v>
       </c>
       <c r="E29" t="n">
         <v>0.0061</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0253</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.448</v>
+        <v>-0.4702</v>
       </c>
       <c r="E30" t="n">
         <v>-0.0659</v>
@@ -1836,7 +1836,7 @@
         <v>-0.0646</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4892</v>
+        <v>-0.5108</v>
       </c>
       <c r="E31" t="n">
         <v>-0.168</v>
@@ -1882,7 +1882,7 @@
         <v>-0.0727</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.4977</v>
+        <v>-0.5192</v>
       </c>
       <c r="E32" t="n">
         <v>-0.189</v>
@@ -1928,7 +1928,7 @@
         <v>-0.2385</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6718</v>
+        <v>-0.6909</v>
       </c>
       <c r="E33" t="n">
         <v>-0.62</v>
@@ -1974,7 +1974,7 @@
         <v>-0.3242</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7618</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="E34" t="n">
         <v>-0.8428</v>
@@ -2020,7 +2020,7 @@
         <v>-0.3402</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7786</v>
+        <v>-0.7963</v>
       </c>
       <c r="E35" t="n">
         <v>-0.8844</v>
@@ -2066,7 +2066,7 @@
         <v>-0.3441</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7828000000000001</v>
+        <v>-0.8004</v>
       </c>
       <c r="E36" t="n">
         <v>-0.8947000000000001</v>
@@ -2112,7 +2112,7 @@
         <v>-0.4618</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9064</v>
+        <v>-0.9222</v>
       </c>
       <c r="E37" t="n">
         <v>-1.2006</v>
@@ -2158,7 +2158,7 @@
         <v>-0.4708</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-0.9316</v>
       </c>
       <c r="E38" t="n">
         <v>-1.224</v>
@@ -2204,7 +2204,7 @@
         <v>-0.5</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E39" t="n">
         <v>-1.3</v>
@@ -2250,7 +2250,7 @@
         <v>-0.5</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E40" t="n">
         <v>-1.3</v>
@@ -2296,7 +2296,7 @@
         <v>-0.5784</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.0289</v>
+        <v>-1.043</v>
       </c>
       <c r="E41" t="n">
         <v>-1.5038</v>

--- a/database/event/8246/event_8246_evp_summary.xlsx
+++ b/database/event/8246/event_8246_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.5513</v>
+        <v>5.2786</v>
       </c>
       <c r="C2" t="n">
-        <v>2.1353</v>
+        <v>2.0304</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7677</v>
+        <v>1.745</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5513</v>
+        <v>5.2786</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5513</v>
+        <v>5.2786</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2702</v>
+        <v>3.783</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>180</v>
       </c>
       <c r="M2" t="n">
-        <v>4.2702</v>
+        <v>3.783</v>
       </c>
       <c r="N2" t="n">
         <v>180</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.24</v>
+        <v>4.0613</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6309</v>
+        <v>1.5622</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2453</v>
+        <v>1.1955</v>
       </c>
       <c r="E3" t="n">
-        <v>4.24</v>
+        <v>4.0613</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4.24</v>
+        <v>4.0613</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2615</v>
+        <v>2.9106</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>176</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2615</v>
+        <v>2.9106</v>
       </c>
       <c r="N3" t="n">
         <v>176</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.2395</v>
+        <v>4.043</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6307</v>
+        <v>1.5552</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2451</v>
+        <v>1.1872</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2395</v>
+        <v>4.043</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2395</v>
+        <v>4.043</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2612</v>
+        <v>2.8974</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>180</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2612</v>
+        <v>2.8974</v>
       </c>
       <c r="N4" t="n">
         <v>180</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.7284</v>
+        <v>3.4064</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4341</v>
+        <v>1.3103</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0415</v>
+        <v>0.8998</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7284</v>
+        <v>3.4064</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7284</v>
+        <v>3.4064</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.868</v>
+        <v>2.4412</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>176</v>
       </c>
       <c r="M5" t="n">
-        <v>2.868</v>
+        <v>2.4412</v>
       </c>
       <c r="N5" t="n">
         <v>176</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.1616</v>
+        <v>2.8814</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2161</v>
+        <v>1.1083</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8157</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1616</v>
+        <v>2.8814</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1616</v>
+        <v>2.8814</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.432</v>
+        <v>2.065</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>98</v>
       </c>
       <c r="M6" t="n">
-        <v>2.432</v>
+        <v>2.065</v>
       </c>
       <c r="N6" t="n">
         <v>98</v>
@@ -722,26 +722,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.4915</v>
+        <v>2.4939</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9584</v>
+        <v>0.9593</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5487</v>
+        <v>0.4879</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4915</v>
+        <v>2.4939</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4915</v>
+        <v>2.4939</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,44 +750,44 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9165</v>
+        <v>1.7873</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="M7" t="n">
-        <v>1.9165</v>
+        <v>1.7873</v>
       </c>
       <c r="N7" t="n">
-        <v>98</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.3085</v>
+        <v>2.382</v>
       </c>
       <c r="C8" t="n">
-        <v>0.888</v>
+        <v>0.9162</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4758</v>
+        <v>0.4373</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3085</v>
+        <v>2.382</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3085</v>
+        <v>2.382</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,19 +796,19 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7758</v>
+        <v>1.7071</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>176</v>
+        <v>98</v>
       </c>
       <c r="M8" t="n">
-        <v>1.7758</v>
+        <v>1.7071</v>
       </c>
       <c r="N8" t="n">
-        <v>176</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9">
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2983</v>
+        <v>2.2656</v>
       </c>
       <c r="C9" t="n">
-        <v>0.884</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4717</v>
+        <v>0.3848</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2983</v>
+        <v>2.2656</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2983</v>
+        <v>2.2656</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7679</v>
+        <v>1.6237</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>176</v>
       </c>
       <c r="M9" t="n">
-        <v>1.7679</v>
+        <v>1.6237</v>
       </c>
       <c r="N9" t="n">
         <v>176</v>
@@ -860,26 +860,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.9119</v>
+        <v>2.1465</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.8257</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3178</v>
+        <v>0.331</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9119</v>
+        <v>2.1465</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9119</v>
+        <v>2.1465</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,44 +888,44 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4707</v>
+        <v>1.5383</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>105</v>
+        <v>180</v>
       </c>
       <c r="M10" t="n">
-        <v>1.4707</v>
+        <v>1.5383</v>
       </c>
       <c r="N10" t="n">
-        <v>105</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.7896</v>
+        <v>1.8666</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6884</v>
+        <v>0.718</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2691</v>
+        <v>0.2047</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7896</v>
+        <v>1.8666</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7896</v>
+        <v>1.8666</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,44 +934,44 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3766</v>
+        <v>1.3377</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>180</v>
+        <v>105</v>
       </c>
       <c r="M11" t="n">
-        <v>1.3766</v>
+        <v>1.3377</v>
       </c>
       <c r="N11" t="n">
-        <v>180</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7874</v>
+        <v>1.4563</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6875</v>
+        <v>0.5602</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2682</v>
+        <v>0.0194</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7874</v>
+        <v>1.4563</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7874</v>
+        <v>1.4563</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,44 +980,44 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3749</v>
+        <v>1.0437</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3749</v>
+        <v>1.0437</v>
       </c>
       <c r="N12" t="n">
-        <v>105</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4299</v>
+        <v>1.4559</v>
       </c>
       <c r="C13" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1258</v>
+        <v>0.0193</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4299</v>
+        <v>1.4559</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4299</v>
+        <v>1.4559</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,19 +1026,19 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0999</v>
+        <v>1.0434</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="M13" t="n">
-        <v>1.0999</v>
+        <v>1.0434</v>
       </c>
       <c r="N13" t="n">
-        <v>46</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.3374</v>
+        <v>1.2222</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5144</v>
+        <v>0.4701</v>
       </c>
       <c r="D14" t="n">
-        <v>0.08890000000000001</v>
+        <v>-0.0863</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3374</v>
+        <v>1.2222</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3374</v>
+        <v>1.2222</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0288</v>
+        <v>0.8759</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>53</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0288</v>
+        <v>0.8759</v>
       </c>
       <c r="N14" t="n">
         <v>53</v>
@@ -1090,26 +1090,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BELCHONOKK</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.299</v>
+        <v>0.9458</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4997</v>
+        <v>0.3638</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0736</v>
+        <v>-0.211</v>
       </c>
       <c r="E15" t="n">
-        <v>1.299</v>
+        <v>0.9458</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.299</v>
+        <v>0.9458</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,44 +1118,44 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9992</v>
+        <v>0.6778</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>176</v>
+        <v>105</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9992</v>
+        <v>0.6778</v>
       </c>
       <c r="N15" t="n">
-        <v>176</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1834</v>
+        <v>0.8417</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4552</v>
+        <v>0.3238</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0276</v>
+        <v>-0.258</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1834</v>
+        <v>0.8417</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1834</v>
+        <v>0.8417</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,44 +1164,44 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9103</v>
+        <v>0.6032</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9103</v>
+        <v>0.6032</v>
       </c>
       <c r="N16" t="n">
-        <v>105</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>BELCHONOKK</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6626</v>
+        <v>0.8217</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2549</v>
+        <v>0.3161</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1799</v>
+        <v>-0.2671</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6626</v>
+        <v>0.8217</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6626</v>
+        <v>0.8217</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,44 +1210,44 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5097</v>
+        <v>0.5889</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5097</v>
+        <v>0.5889</v>
       </c>
       <c r="N17" t="n">
-        <v>98</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6365</v>
+        <v>0.786</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2448</v>
+        <v>0.3023</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1903</v>
+        <v>-0.2832</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6365</v>
+        <v>0.786</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6365</v>
+        <v>0.786</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4896</v>
+        <v>0.5633</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>61</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4896</v>
+        <v>0.5633</v>
       </c>
       <c r="N18" t="n">
         <v>61</v>
@@ -1274,26 +1274,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5169</v>
+        <v>0.7552</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1988</v>
+        <v>0.2905</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.238</v>
+        <v>-0.2971</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5169</v>
+        <v>0.7552</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5169</v>
+        <v>0.7552</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,44 +1302,44 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3976</v>
+        <v>0.5412</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3976</v>
+        <v>0.5412</v>
       </c>
       <c r="N19" t="n">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4939</v>
+        <v>0.4356</v>
       </c>
       <c r="C20" t="n">
-        <v>0.19</v>
+        <v>0.1676</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2471</v>
+        <v>-0.4414</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4939</v>
+        <v>0.4356</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4939</v>
+        <v>0.4356</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,44 +1348,44 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3799</v>
+        <v>0.3122</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3799</v>
+        <v>0.3122</v>
       </c>
       <c r="N20" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3868</v>
+        <v>0.4242</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1488</v>
+        <v>0.1632</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2898</v>
+        <v>-0.4465</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3868</v>
+        <v>0.4242</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3868</v>
+        <v>0.4242</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2975</v>
+        <v>0.304</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>51</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2975</v>
+        <v>0.304</v>
       </c>
       <c r="N21" t="n">
         <v>51</v>
@@ -1412,26 +1412,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3825</v>
+        <v>0.3953</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1471</v>
+        <v>0.1521</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2915</v>
+        <v>-0.4596</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3825</v>
+        <v>0.3953</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3825</v>
+        <v>0.3953</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,44 +1440,44 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2942</v>
+        <v>0.2833</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>51</v>
+        <v>180</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2942</v>
+        <v>0.2833</v>
       </c>
       <c r="N22" t="n">
-        <v>51</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3076</v>
+        <v>0.3706</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1183</v>
+        <v>0.1426</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3214</v>
+        <v>-0.4707</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3076</v>
+        <v>0.3706</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3076</v>
+        <v>0.3706</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2366</v>
+        <v>0.2656</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>61</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2366</v>
+        <v>0.2656</v>
       </c>
       <c r="N23" t="n">
         <v>61</v>
@@ -1504,26 +1504,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3067</v>
+        <v>0.3674</v>
       </c>
       <c r="C24" t="n">
-        <v>0.118</v>
+        <v>0.1413</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3217</v>
+        <v>-0.4722</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3067</v>
+        <v>0.3674</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3067</v>
+        <v>0.3674</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,44 +1532,44 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2359</v>
+        <v>0.2633</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2359</v>
+        <v>0.2633</v>
       </c>
       <c r="N24" t="n">
-        <v>105</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2831</v>
+        <v>0.3297</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1089</v>
+        <v>0.1268</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3311</v>
+        <v>-0.4892</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2831</v>
+        <v>0.3297</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2831</v>
+        <v>0.3297</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,44 +1578,44 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2178</v>
+        <v>0.2363</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2178</v>
+        <v>0.2363</v>
       </c>
       <c r="N25" t="n">
-        <v>61</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hypex</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.3244</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0357</v>
+        <v>0.1248</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4069</v>
+        <v>-0.4916</v>
       </c>
       <c r="E26" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.3244</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.3244</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,44 +1624,44 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.2325</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="M26" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.2325</v>
       </c>
       <c r="N26" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nilo</t>
+          <t>Chr1zN</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0476</v>
+        <v>0.2269</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0183</v>
+        <v>0.0873</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4249</v>
+        <v>-0.5356</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0476</v>
+        <v>0.2269</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0476</v>
+        <v>0.2269</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0366</v>
+        <v>0.1626</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>53</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0366</v>
+        <v>0.1626</v>
       </c>
       <c r="N27" t="n">
         <v>53</v>
@@ -1688,26 +1688,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Chr1zN</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0408</v>
+        <v>0.0999</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0157</v>
+        <v>0.0384</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4277</v>
+        <v>-0.5929</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0408</v>
+        <v>0.0999</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0408</v>
+        <v>0.0999</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,44 +1716,44 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0314</v>
+        <v>0.0716</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0314</v>
+        <v>0.0716</v>
       </c>
       <c r="N28" t="n">
-        <v>53</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>hypex</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0061</v>
+        <v>0.0858</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0023</v>
+        <v>0.033</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4415</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0061</v>
+        <v>0.0858</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0061</v>
+        <v>0.0858</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,44 +1762,44 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0047</v>
+        <v>0.0615</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0047</v>
+        <v>0.0615</v>
       </c>
       <c r="N29" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>nilo</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0659</v>
+        <v>0.0682</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0253</v>
+        <v>0.0262</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4702</v>
+        <v>-0.6072</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0659</v>
+        <v>0.0682</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0659</v>
+        <v>0.0682</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,44 +1808,44 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.0507</v>
+        <v>0.0489</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0507</v>
+        <v>0.0489</v>
       </c>
       <c r="N30" t="n">
-        <v>98</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.168</v>
+        <v>-0.0155</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0646</v>
+        <v>-0.006</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5108</v>
+        <v>-0.645</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.168</v>
+        <v>-0.0155</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.168</v>
+        <v>-0.0155</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.1292</v>
+        <v>-0.0111</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>51</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1292</v>
+        <v>-0.0111</v>
       </c>
       <c r="N31" t="n">
         <v>51</v>
@@ -1872,26 +1872,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.189</v>
+        <v>-0.1372</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0727</v>
+        <v>-0.0528</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5192</v>
+        <v>-0.7</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.189</v>
+        <v>-0.1372</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.189</v>
+        <v>-0.1372</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.1454</v>
+        <v>-0.0983</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1454</v>
+        <v>-0.0983</v>
       </c>
       <c r="N32" t="n">
-        <v>180</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33">
@@ -1922,22 +1922,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.62</v>
+        <v>-0.3561</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2385</v>
+        <v>-0.137</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6909</v>
+        <v>-0.7988</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.62</v>
+        <v>-0.3561</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.62</v>
+        <v>-0.3561</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.4769</v>
+        <v>-0.2552</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>53</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4769</v>
+        <v>-0.2552</v>
       </c>
       <c r="N33" t="n">
         <v>53</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.8428</v>
+        <v>-0.571</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3242</v>
+        <v>-0.2196</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7796999999999999</v>
+        <v>-0.8958</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.8428</v>
+        <v>-0.571</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.8428</v>
+        <v>-0.571</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.6483</v>
+        <v>-0.4092</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6483</v>
+        <v>-0.4092</v>
       </c>
       <c r="N34" t="n">
         <v>46</v>
@@ -2010,26 +2010,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8844</v>
+        <v>-0.6188</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3402</v>
+        <v>-0.238</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7963</v>
+        <v>-0.9174</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8844</v>
+        <v>-0.6188</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.8844</v>
+        <v>-0.6188</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,44 +2038,44 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.6803</v>
+        <v>-0.4435</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6803</v>
+        <v>-0.4435</v>
       </c>
       <c r="N35" t="n">
-        <v>105</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8947000000000001</v>
+        <v>-0.8325</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3441</v>
+        <v>-0.3202</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8004</v>
+        <v>-1.0138</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8947000000000001</v>
+        <v>-0.8325</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.8947000000000001</v>
+        <v>-0.8325</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.6882</v>
+        <v>-0.5966</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>46</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6882</v>
+        <v>-0.5966</v>
       </c>
       <c r="N36" t="n">
         <v>46</v>
@@ -2102,26 +2102,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>susp</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2006</v>
+        <v>-0.9649</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4618</v>
+        <v>-0.3712</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9222</v>
+        <v>-1.0736</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2006</v>
+        <v>-0.9649</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.2006</v>
+        <v>-0.9649</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2130,44 +2130,44 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.9235</v>
+        <v>-0.6915</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9235</v>
+        <v>-0.6915</v>
       </c>
       <c r="N37" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NucleonZ</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.224</v>
+        <v>-0.9946</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4708</v>
+        <v>-0.3826</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9316</v>
+        <v>-1.087</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.224</v>
+        <v>-0.9946</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.224</v>
+        <v>-0.9946</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2176,44 +2176,44 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.9415</v>
+        <v>-0.7128</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>180</v>
+        <v>105</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9415</v>
+        <v>-0.7128</v>
       </c>
       <c r="N38" t="n">
-        <v>180</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>susp</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3</v>
+        <v>-1.0398</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9618</v>
+        <v>-1.1074</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3</v>
+        <v>-1.0398</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.3</v>
+        <v>-1.0398</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2222,19 +2222,19 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-1</v>
+        <v>-0.7452</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="M39" t="n">
-        <v>-1</v>
+        <v>-0.7452</v>
       </c>
       <c r="N39" t="n">
-        <v>53</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40">
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3</v>
+        <v>-1.213</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5</v>
+        <v>-0.4666</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.9618</v>
+        <v>-1.1856</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3</v>
+        <v>-1.213</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.3</v>
+        <v>-1.213</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-1</v>
+        <v>-0.8693</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>51</v>
       </c>
       <c r="M40" t="n">
-        <v>-1</v>
+        <v>-0.8693</v>
       </c>
       <c r="N40" t="n">
         <v>51</v>
@@ -2286,26 +2286,26 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>NucleonZ</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.5038</v>
+        <v>-1.4693</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5784</v>
+        <v>-0.5652</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.043</v>
+        <v>-1.3013</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.5038</v>
+        <v>-1.4693</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.5038</v>
+        <v>-1.4693</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2314,19 +2314,19 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.1568</v>
+        <v>-1.053</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>98</v>
+        <v>180</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.1568</v>
+        <v>-1.053</v>
       </c>
       <c r="N41" t="n">
-        <v>98</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>1.14</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3124</v>
+        <v>0.3418</v>
       </c>
       <c r="J2" t="n">
-        <v>6.8728</v>
+        <v>7.5196</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.14</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3124</v>
+        <v>0.3418</v>
       </c>
       <c r="J3" t="n">
-        <v>6.8728</v>
+        <v>7.5196</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.99</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0038</v>
+        <v>-0.0164</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.3608</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3555</v>
+        <v>-0.2228</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.821</v>
+        <v>-4.9016</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.66</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5624</v>
+        <v>-0.3679</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.3728</v>
+        <v>-8.0938</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.8</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7867</v>
+        <v>1.5177</v>
       </c>
       <c r="J7" t="n">
-        <v>39.3074</v>
+        <v>33.3894</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.13</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3264</v>
+        <v>0.3864</v>
       </c>
       <c r="J8" t="n">
-        <v>7.1808</v>
+        <v>8.5008</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0533</v>
+        <v>0.1212</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1726</v>
+        <v>2.6664</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.02</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0196</v>
+        <v>0.0494</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4312</v>
+        <v>1.0868</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.97</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2582</v>
+        <v>-0.18</v>
       </c>
       <c r="J11" t="n">
-        <v>-5.6804</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.35</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6092</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>14.6208</v>
+        <v>17.6736</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.95</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0882</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.1168</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.87</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2533</v>
+        <v>-0.1587</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.0792</v>
+        <v>-3.8088</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.85</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2866</v>
+        <v>-0.1795</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.8784</v>
+        <v>-4.308</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.62</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6095</v>
+        <v>-0.4028</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.628</v>
+        <v>-9.667199999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.47</v>
       </c>
       <c r="I17" t="n">
-        <v>1.228</v>
+        <v>1.1386</v>
       </c>
       <c r="J17" t="n">
-        <v>29.472</v>
+        <v>27.3264</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.28</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8179</v>
+        <v>0.7905</v>
       </c>
       <c r="J18" t="n">
-        <v>19.6296</v>
+        <v>18.972</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.99</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1245</v>
+        <v>-0.0704</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.988</v>
+        <v>-1.6896</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.84</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5935</v>
+        <v>-0.5365</v>
       </c>
       <c r="J20" t="n">
-        <v>-14.244</v>
+        <v>-12.876</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.78</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.742</v>
+        <v>-0.6937</v>
       </c>
       <c r="J21" t="n">
-        <v>-17.808</v>
+        <v>-16.6488</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.4</v>
       </c>
       <c r="I22" t="n">
-        <v>0.656</v>
+        <v>0.8017</v>
       </c>
       <c r="J22" t="n">
-        <v>15.744</v>
+        <v>19.2408</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.22</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4225</v>
+        <v>0.4857</v>
       </c>
       <c r="J23" t="n">
-        <v>10.14</v>
+        <v>11.6568</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.79</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3908</v>
+        <v>-0.2455</v>
       </c>
       <c r="J24" t="n">
-        <v>-9.379200000000001</v>
+        <v>-5.892</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.78</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4052</v>
+        <v>-0.2554</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.7248</v>
+        <v>-6.1296</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.66</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5664</v>
+        <v>-0.3705</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.5936</v>
+        <v>-8.891999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.51</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2837</v>
+        <v>1.1769</v>
       </c>
       <c r="J27" t="n">
-        <v>30.8088</v>
+        <v>28.2456</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.37</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9941</v>
+        <v>0.9766</v>
       </c>
       <c r="J28" t="n">
-        <v>23.8584</v>
+        <v>23.4384</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0888</v>
+        <v>-0.0276</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.1312</v>
+        <v>-0.6624</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.99</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1482</v>
+        <v>-0.0824</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.5568</v>
+        <v>-1.9776</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.72</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8933</v>
+        <v>-0.8565</v>
       </c>
       <c r="J31" t="n">
-        <v>-21.4392</v>
+        <v>-20.556</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.51</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2226</v>
+        <v>0.8711</v>
       </c>
       <c r="J32" t="n">
-        <v>25.6746</v>
+        <v>18.2931</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.36</v>
       </c>
       <c r="I33" t="n">
-        <v>0.907</v>
+        <v>0.6781</v>
       </c>
       <c r="J33" t="n">
-        <v>19.047</v>
+        <v>14.2401</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.34</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8617</v>
+        <v>0.6518</v>
       </c>
       <c r="J34" t="n">
-        <v>18.0957</v>
+        <v>13.6878</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.25</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6382</v>
+        <v>0.5319</v>
       </c>
       <c r="J35" t="n">
-        <v>13.4022</v>
+        <v>11.1699</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.74</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.876</v>
+        <v>-0.8355</v>
       </c>
       <c r="J36" t="n">
-        <v>-18.396</v>
+        <v>-17.5455</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.11</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2863</v>
+        <v>0.302</v>
       </c>
       <c r="J37" t="n">
-        <v>6.0123</v>
+        <v>6.342</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.96</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0478</v>
+        <v>-0.0527</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.0038</v>
+        <v>-1.1067</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.86</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2534</v>
+        <v>-0.165</v>
       </c>
       <c r="J39" t="n">
-        <v>-5.3214</v>
+        <v>-3.465</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.8</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3523</v>
+        <v>-0.2256</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.3983</v>
+        <v>-4.7376</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.72</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4692</v>
+        <v>-0.3037</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.853199999999999</v>
+        <v>-6.3777</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.2</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6287</v>
+        <v>0.4879</v>
       </c>
       <c r="J42" t="n">
-        <v>15.0888</v>
+        <v>11.7096</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.16</v>
       </c>
       <c r="I43" t="n">
-        <v>0.524</v>
+        <v>0.4271</v>
       </c>
       <c r="J43" t="n">
-        <v>12.576</v>
+        <v>10.2504</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.11</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3812</v>
+        <v>0.3475</v>
       </c>
       <c r="J44" t="n">
-        <v>9.1488</v>
+        <v>8.34</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.01</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0016</v>
+        <v>0.0408</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0384</v>
+        <v>0.9792</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.84</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5906</v>
+        <v>-0.5342</v>
       </c>
       <c r="J46" t="n">
-        <v>-14.1744</v>
+        <v>-12.8208</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.34</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5867</v>
+        <v>0.5527</v>
       </c>
       <c r="J47" t="n">
-        <v>14.0808</v>
+        <v>13.2648</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.24</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4552</v>
+        <v>0.4481</v>
       </c>
       <c r="J48" t="n">
-        <v>10.9248</v>
+        <v>10.7544</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3578</v>
+        <v>-0.2237</v>
       </c>
       <c r="J49" t="n">
-        <v>-8.587199999999999</v>
+        <v>-5.3688</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.72</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4851</v>
+        <v>-0.312</v>
       </c>
       <c r="J50" t="n">
-        <v>-11.6424</v>
+        <v>-7.488</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.67</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.551</v>
+        <v>-0.3595</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.224</v>
+        <v>-8.628</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.49</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7725</v>
+        <v>0.7075</v>
       </c>
       <c r="J52" t="n">
-        <v>17.7675</v>
+        <v>16.2725</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.23</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4464</v>
+        <v>0.4407</v>
       </c>
       <c r="J53" t="n">
-        <v>10.2672</v>
+        <v>10.1361</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.78</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.398</v>
+        <v>-0.252</v>
       </c>
       <c r="J54" t="n">
-        <v>-9.154</v>
+        <v>-5.796</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.67</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5483</v>
+        <v>-0.3578</v>
       </c>
       <c r="J55" t="n">
-        <v>-12.6109</v>
+        <v>-8.2294</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.54</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7096</v>
+        <v>-0.4777</v>
       </c>
       <c r="J56" t="n">
-        <v>-16.3208</v>
+        <v>-10.9871</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.49</v>
       </c>
       <c r="I57" t="n">
-        <v>1.2303</v>
+        <v>0.8695000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>28.2969</v>
+        <v>19.9985</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.36</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9585</v>
+        <v>0.697</v>
       </c>
       <c r="J58" t="n">
-        <v>22.0455</v>
+        <v>16.031</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.08</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2064</v>
+        <v>0.2581</v>
       </c>
       <c r="J59" t="n">
-        <v>4.7472</v>
+        <v>5.9363</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.97</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2401</v>
+        <v>-0.1676</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.5223</v>
+        <v>-3.8548</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.82</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6669</v>
+        <v>-0.6091</v>
       </c>
       <c r="J61" t="n">
-        <v>-15.3387</v>
+        <v>-14.0093</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.93</v>
       </c>
       <c r="I62" t="n">
-        <v>1.1001</v>
+        <v>0.7387</v>
       </c>
       <c r="J62" t="n">
-        <v>18.7017</v>
+        <v>12.5579</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.83</v>
       </c>
       <c r="I63" t="n">
-        <v>1.0016</v>
+        <v>0.6811</v>
       </c>
       <c r="J63" t="n">
-        <v>17.0272</v>
+        <v>11.5787</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.3</v>
       </c>
       <c r="I64" t="n">
-        <v>0.372</v>
+        <v>0.3609</v>
       </c>
       <c r="J64" t="n">
-        <v>6.324</v>
+        <v>6.1353</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.02</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0489</v>
+        <v>-0.0001</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.8313</v>
+        <v>-0.0017</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.95</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.22</v>
+        <v>-0.1144</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.74</v>
+        <v>-1.9448</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.32</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5936</v>
+        <v>0.46</v>
       </c>
       <c r="J67" t="n">
-        <v>10.0912</v>
+        <v>7.82</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.89</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.174</v>
+        <v>-0.1323</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.958</v>
+        <v>-2.2491</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.88</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1936</v>
+        <v>-0.1428</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.2912</v>
+        <v>-2.4276</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.63</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5847</v>
+        <v>-0.386</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.9399</v>
+        <v>-6.562</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.62</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5976</v>
+        <v>-0.3954</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.1592</v>
+        <v>-6.7218</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>0.0949</v>
+        <v>0.0568</v>
       </c>
       <c r="J72" t="n">
-        <v>1.8031</v>
+        <v>1.0792</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.97</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0128</v>
+        <v>-0.0225</v>
       </c>
       <c r="J73" t="n">
-        <v>0.2432</v>
+        <v>-0.4275</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.83</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2434</v>
+        <v>-0.1865</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.6246</v>
+        <v>-3.5435</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.64</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5541</v>
+        <v>-0.3672</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.5279</v>
+        <v>-6.9768</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6595</v>
+        <v>-0.442</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.5305</v>
+        <v>-8.398</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>2.18</v>
       </c>
       <c r="I77" t="n">
-        <v>2.0596</v>
+        <v>1.6252</v>
       </c>
       <c r="J77" t="n">
-        <v>39.1324</v>
+        <v>30.8788</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.57</v>
       </c>
       <c r="I78" t="n">
-        <v>1.279</v>
+        <v>0.9192</v>
       </c>
       <c r="J78" t="n">
-        <v>24.301</v>
+        <v>17.4648</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.17</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3529</v>
+        <v>0.4028</v>
       </c>
       <c r="J79" t="n">
-        <v>6.7051</v>
+        <v>7.6532</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.14</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2772</v>
+        <v>0.3567</v>
       </c>
       <c r="J80" t="n">
-        <v>5.2668</v>
+        <v>6.7773</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.8</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7654</v>
+        <v>-0.7119</v>
       </c>
       <c r="J81" t="n">
-        <v>-14.5426</v>
+        <v>-13.5261</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.2</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4005</v>
+        <v>0.3414</v>
       </c>
       <c r="J82" t="n">
-        <v>7.209</v>
+        <v>6.1452</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.07</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1936</v>
+        <v>0.1497</v>
       </c>
       <c r="J83" t="n">
-        <v>3.4848</v>
+        <v>2.6946</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.88</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2455</v>
+        <v>-0.1507</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.419</v>
+        <v>-2.7126</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.82</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3416</v>
+        <v>-0.2131</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.1488</v>
+        <v>-3.8358</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3862</v>
+        <v>-0.2433</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.9516</v>
+        <v>-4.3794</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>2.11</v>
       </c>
       <c r="I87" t="n">
-        <v>1.2692</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="J87" t="n">
-        <v>22.8456</v>
+        <v>15.1236</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.53</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6788</v>
+        <v>0.5033</v>
       </c>
       <c r="J88" t="n">
-        <v>12.2184</v>
+        <v>9.0594</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.3</v>
       </c>
       <c r="I89" t="n">
-        <v>0.371</v>
+        <v>0.3607</v>
       </c>
       <c r="J89" t="n">
-        <v>6.678</v>
+        <v>6.4926</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.22</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2647</v>
+        <v>0.2851</v>
       </c>
       <c r="J90" t="n">
-        <v>4.7646</v>
+        <v>5.1318</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.89</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3177</v>
+        <v>-0.1842</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.7186</v>
+        <v>-3.3156</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.14</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4874</v>
+        <v>0.4012</v>
       </c>
       <c r="J92" t="n">
-        <v>10.7228</v>
+        <v>8.8264</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.11</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4015</v>
+        <v>0.3525</v>
       </c>
       <c r="J93" t="n">
-        <v>8.833</v>
+        <v>7.755</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.98</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1464</v>
+        <v>-0.102</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.2208</v>
+        <v>-2.244</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.98</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1464</v>
+        <v>-0.102</v>
       </c>
       <c r="J95" t="n">
-        <v>-3.2208</v>
+        <v>-2.244</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.97</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1863</v>
+        <v>-0.1389</v>
       </c>
       <c r="J96" t="n">
-        <v>-4.0986</v>
+        <v>-3.0558</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.32</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5394</v>
+        <v>0.5167</v>
       </c>
       <c r="J97" t="n">
-        <v>11.8668</v>
+        <v>11.3674</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.21</v>
       </c>
       <c r="I98" t="n">
-        <v>0.391</v>
+        <v>0.4028</v>
       </c>
       <c r="J98" t="n">
-        <v>8.602</v>
+        <v>8.861599999999999</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.99</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0514</v>
+        <v>-0.0221</v>
       </c>
       <c r="J99" t="n">
-        <v>-1.1308</v>
+        <v>-0.4862</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.92</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1993</v>
+        <v>-0.1138</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.3846</v>
+        <v>-2.5036</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.66</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5748</v>
+        <v>-0.376</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.6456</v>
+        <v>-8.272</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.51</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2461</v>
+        <v>0.8825</v>
       </c>
       <c r="J102" t="n">
-        <v>26.1681</v>
+        <v>18.5325</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.28</v>
       </c>
       <c r="I103" t="n">
-        <v>0.749</v>
+        <v>0.5788</v>
       </c>
       <c r="J103" t="n">
-        <v>15.729</v>
+        <v>12.1548</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.16</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4115</v>
+        <v>0.4107</v>
       </c>
       <c r="J104" t="n">
-        <v>8.641500000000001</v>
+        <v>8.624700000000001</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.06</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1191</v>
+        <v>0.1861</v>
       </c>
       <c r="J105" t="n">
-        <v>2.5011</v>
+        <v>3.9081</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.95</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3258</v>
+        <v>-0.2484</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.8418</v>
+        <v>-5.2164</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.14</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3243</v>
+        <v>0.3447</v>
       </c>
       <c r="J107" t="n">
-        <v>6.8103</v>
+        <v>7.2387</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0461</v>
+        <v>0.0164</v>
       </c>
       <c r="J108" t="n">
-        <v>0.9681</v>
+        <v>0.3444</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.83</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.3145</v>
+        <v>-0.1986</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.6045</v>
+        <v>-4.1706</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.83</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3145</v>
+        <v>-0.1986</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.6045</v>
+        <v>-4.1706</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.78</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3908</v>
+        <v>-0.2487</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.206799999999999</v>
+        <v>-5.2227</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.11</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2666</v>
+        <v>0.2835</v>
       </c>
       <c r="J112" t="n">
-        <v>5.8652</v>
+        <v>6.237</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.97</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0511</v>
+        <v>-0.0456</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.1242</v>
+        <v>-1.0032</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.92</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1682</v>
+        <v>-0.1058</v>
       </c>
       <c r="J114" t="n">
-        <v>-3.7004</v>
+        <v>-2.3276</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.89</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2242</v>
+        <v>-0.1388</v>
       </c>
       <c r="J115" t="n">
-        <v>-4.9324</v>
+        <v>-3.0536</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.82</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3386</v>
+        <v>-0.2119</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.4492</v>
+        <v>-4.6618</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.31</v>
       </c>
       <c r="I117" t="n">
-        <v>0.86</v>
+        <v>0.6339</v>
       </c>
       <c r="J117" t="n">
-        <v>18.92</v>
+        <v>13.9458</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.28</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.592</v>
       </c>
       <c r="J118" t="n">
-        <v>17.3976</v>
+        <v>13.024</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.22</v>
       </c>
       <c r="I119" t="n">
-        <v>0.6452</v>
+        <v>0.5064</v>
       </c>
       <c r="J119" t="n">
-        <v>14.1944</v>
+        <v>11.1408</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.95</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.299</v>
+        <v>-0.2296</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.578</v>
+        <v>-5.0512</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.84</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6098</v>
+        <v>-0.5496</v>
       </c>
       <c r="J121" t="n">
-        <v>-13.4156</v>
+        <v>-12.0912</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.54</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8333</v>
+        <v>0.7602</v>
       </c>
       <c r="J122" t="n">
-        <v>19.9992</v>
+        <v>18.2448</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.03</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1225</v>
+        <v>0.1071</v>
       </c>
       <c r="J123" t="n">
-        <v>2.94</v>
+        <v>2.5704</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.76</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.4241</v>
+        <v>-0.2704</v>
       </c>
       <c r="J124" t="n">
-        <v>-10.1784</v>
+        <v>-6.4896</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.52</v>
+        <v>-0.3377</v>
       </c>
       <c r="J125" t="n">
-        <v>-12.48</v>
+        <v>-8.104799999999999</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.64</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5849</v>
+        <v>-0.3847</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.0376</v>
+        <v>-9.232799999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.35</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9516</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J127" t="n">
-        <v>22.8384</v>
+        <v>16.56</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.34</v>
       </c>
       <c r="I128" t="n">
-        <v>0.9295</v>
+        <v>0.6762</v>
       </c>
       <c r="J128" t="n">
-        <v>22.308</v>
+        <v>16.2288</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0878</v>
+        <v>-0.0271</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.1072</v>
+        <v>-0.6504</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.98</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.19</v>
+        <v>-0.123</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.56</v>
+        <v>-2.952</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.91</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4199</v>
+        <v>-0.3523</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.0776</v>
+        <v>-8.4552</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.74</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9202</v>
+        <v>0.6331</v>
       </c>
       <c r="J132" t="n">
-        <v>14.7232</v>
+        <v>10.1296</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.52</v>
       </c>
       <c r="I133" t="n">
-        <v>0.68</v>
+        <v>0.5007</v>
       </c>
       <c r="J133" t="n">
-        <v>10.88</v>
+        <v>8.011200000000001</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.35</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4538</v>
+        <v>0.3956</v>
       </c>
       <c r="J134" t="n">
-        <v>7.2608</v>
+        <v>6.3296</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.19</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2328</v>
+        <v>0.2529</v>
       </c>
       <c r="J135" t="n">
-        <v>3.7248</v>
+        <v>4.0464</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.02</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.0429</v>
+        <v>0.0044</v>
       </c>
       <c r="J136" t="n">
-        <v>-0.6864</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.24</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5344</v>
+        <v>0.4257</v>
       </c>
       <c r="J137" t="n">
-        <v>8.5504</v>
+        <v>6.8112</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.88</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1353</v>
+        <v>-0.1253</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.1648</v>
+        <v>-2.0048</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.79</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2866</v>
+        <v>-0.2204</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.5856</v>
+        <v>-3.5264</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.51</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.713</v>
+        <v>-0.482</v>
       </c>
       <c r="J140" t="n">
-        <v>-11.408</v>
+        <v>-7.712</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.36</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.8945</v>
+        <v>-0.6204</v>
       </c>
       <c r="J141" t="n">
-        <v>-14.312</v>
+        <v>-9.926399999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>0.71</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.3665</v>
+        <v>-0.284</v>
       </c>
       <c r="J142" t="n">
-        <v>-5.4975</v>
+        <v>-4.26</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.7</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.3832</v>
+        <v>-0.2935</v>
       </c>
       <c r="J143" t="n">
-        <v>-5.748</v>
+        <v>-4.4025</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.68</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.4185</v>
+        <v>-0.3119</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.2775</v>
+        <v>-4.6785</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.66</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4639</v>
+        <v>-0.3292</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.9585</v>
+        <v>-4.938</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.59</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5774</v>
+        <v>-0.3932</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.661</v>
+        <v>-5.898</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.83</v>
       </c>
       <c r="I147" t="n">
-        <v>1.6952</v>
+        <v>1.1981</v>
       </c>
       <c r="J147" t="n">
-        <v>25.428</v>
+        <v>17.9715</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.56</v>
       </c>
       <c r="I148" t="n">
-        <v>1.193</v>
+        <v>0.8889</v>
       </c>
       <c r="J148" t="n">
-        <v>17.895</v>
+        <v>13.3335</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.47</v>
       </c>
       <c r="I149" t="n">
-        <v>0.9781</v>
+        <v>0.785</v>
       </c>
       <c r="J149" t="n">
-        <v>14.6715</v>
+        <v>11.775</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.34</v>
       </c>
       <c r="I150" t="n">
-        <v>0.697</v>
+        <v>0.623</v>
       </c>
       <c r="J150" t="n">
-        <v>10.455</v>
+        <v>9.345000000000001</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.33</v>
       </c>
       <c r="I151" t="n">
-        <v>0.6753</v>
+        <v>0.61</v>
       </c>
       <c r="J151" t="n">
-        <v>10.1295</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.44</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7153</v>
+        <v>0.6592</v>
       </c>
       <c r="J152" t="n">
-        <v>15.7366</v>
+        <v>14.5024</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.08</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2171</v>
+        <v>0.2216</v>
       </c>
       <c r="J153" t="n">
-        <v>4.7762</v>
+        <v>4.8752</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.84</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3062</v>
+        <v>-0.191</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.7364</v>
+        <v>-4.202</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.67</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5475</v>
+        <v>-0.3573</v>
       </c>
       <c r="J155" t="n">
-        <v>-12.045</v>
+        <v>-7.8606</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.66</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5604</v>
+        <v>-0.3667</v>
       </c>
       <c r="J156" t="n">
-        <v>-12.3288</v>
+        <v>-8.067399999999999</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.79</v>
       </c>
       <c r="I157" t="n">
-        <v>1.7422</v>
+        <v>1.2291</v>
       </c>
       <c r="J157" t="n">
-        <v>38.3284</v>
+        <v>27.0402</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.27</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7198</v>
+        <v>0.5638</v>
       </c>
       <c r="J158" t="n">
-        <v>15.8356</v>
+        <v>12.4036</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.26</v>
       </c>
       <c r="I159" t="n">
-        <v>0.695</v>
+        <v>0.5501</v>
       </c>
       <c r="J159" t="n">
-        <v>15.29</v>
+        <v>12.1022</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.88</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.5303</v>
+        <v>-0.4605</v>
       </c>
       <c r="J160" t="n">
-        <v>-11.6666</v>
+        <v>-10.131</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.8</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7299</v>
+        <v>-0.6751</v>
       </c>
       <c r="J161" t="n">
-        <v>-16.0578</v>
+        <v>-14.8522</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.18</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3551</v>
+        <v>0.3743</v>
       </c>
       <c r="J162" t="n">
-        <v>10.653</v>
+        <v>11.229</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.15</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3098</v>
+        <v>0.3393</v>
       </c>
       <c r="J163" t="n">
-        <v>9.294</v>
+        <v>10.179</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.01</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0418</v>
+        <v>0.038</v>
       </c>
       <c r="J164" t="n">
-        <v>1.254</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.96</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1136</v>
+        <v>-0.063</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.408</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5329</v>
+        <v>-0.3455</v>
       </c>
       <c r="J166" t="n">
-        <v>-15.987</v>
+        <v>-10.365</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.4</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0701</v>
+        <v>0.7633</v>
       </c>
       <c r="J167" t="n">
-        <v>32.103</v>
+        <v>22.899</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.09</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2766</v>
+        <v>0.2964</v>
       </c>
       <c r="J168" t="n">
-        <v>8.298</v>
+        <v>8.891999999999999</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.05</v>
       </c>
       <c r="I169" t="n">
-        <v>0.138</v>
+        <v>0.1775</v>
       </c>
       <c r="J169" t="n">
-        <v>4.14</v>
+        <v>5.325</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.97</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.219</v>
+        <v>-0.1549</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.57</v>
+        <v>-4.647</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.97</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.219</v>
+        <v>-0.1549</v>
       </c>
       <c r="J171" t="n">
-        <v>-6.57</v>
+        <v>-4.647</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.97</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0156</v>
+        <v>-0.0353</v>
       </c>
       <c r="J172" t="n">
-        <v>-0.3276</v>
+        <v>-0.7413</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.97</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0156</v>
+        <v>-0.0353</v>
       </c>
       <c r="J173" t="n">
-        <v>-0.3276</v>
+        <v>-0.7413</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.96</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0371</v>
+        <v>-0.0491</v>
       </c>
       <c r="J174" t="n">
-        <v>-0.7791</v>
+        <v>-1.0311</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.95</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0576</v>
+        <v>-0.0621</v>
       </c>
       <c r="J175" t="n">
-        <v>-1.2096</v>
+        <v>-1.3041</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.48</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.7698</v>
+        <v>-0.5238</v>
       </c>
       <c r="J176" t="n">
-        <v>-16.1658</v>
+        <v>-10.9998</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.96</v>
       </c>
       <c r="I177" t="n">
-        <v>1.8742</v>
+        <v>1.3898</v>
       </c>
       <c r="J177" t="n">
-        <v>39.3582</v>
+        <v>29.1858</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.67</v>
       </c>
       <c r="I178" t="n">
-        <v>1.49</v>
+        <v>1.0486</v>
       </c>
       <c r="J178" t="n">
-        <v>31.29</v>
+        <v>22.0206</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.1</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1858</v>
+        <v>0.2731</v>
       </c>
       <c r="J179" t="n">
-        <v>3.9018</v>
+        <v>5.7351</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.03</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0276</v>
+        <v>0.0543</v>
       </c>
       <c r="J180" t="n">
-        <v>-0.5796</v>
+        <v>1.1403</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.87</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5874</v>
+        <v>-0.5174</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.3354</v>
+        <v>-10.8654</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/8246/event_8246_evp_summary.xlsx
+++ b/database/event/8246/event_8246_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.2786</v>
+        <v>5.1226</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0304</v>
+        <v>1.9704</v>
       </c>
       <c r="D2" t="n">
-        <v>1.745</v>
+        <v>1.7077</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2786</v>
+        <v>5.1226</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>5.2786</v>
+        <v>5.1226</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>3.783</v>
+        <v>4.0267</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>180</v>
       </c>
       <c r="M2" t="n">
-        <v>3.783</v>
+        <v>4.0267</v>
       </c>
       <c r="N2" t="n">
         <v>180</v>
@@ -538,26 +538,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.0613</v>
+        <v>4.0202</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5622</v>
+        <v>1.5464</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1955</v>
+        <v>1.2059</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0613</v>
+        <v>4.0202</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0613</v>
+        <v>4.0202</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,44 +566,44 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9106</v>
+        <v>3.1601</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9106</v>
+        <v>3.1601</v>
       </c>
       <c r="N3" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>nota</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.043</v>
+        <v>3.8352</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5552</v>
+        <v>1.4752</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1872</v>
+        <v>1.1217</v>
       </c>
       <c r="E4" t="n">
-        <v>4.043</v>
+        <v>3.8352</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>4.043</v>
+        <v>3.8352</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,19 +612,19 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8974</v>
+        <v>3.0147</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8974</v>
+        <v>3.0147</v>
       </c>
       <c r="N4" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5">
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.4064</v>
+        <v>3.3895</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3103</v>
+        <v>1.3038</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8998</v>
+        <v>0.9188</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4064</v>
+        <v>3.3895</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4064</v>
+        <v>3.3895</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4412</v>
+        <v>2.6644</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>176</v>
       </c>
       <c r="M5" t="n">
-        <v>2.4412</v>
+        <v>2.6644</v>
       </c>
       <c r="N5" t="n">
         <v>176</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.8814</v>
+        <v>3.0203</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1083</v>
+        <v>1.1618</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.7507</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8814</v>
+        <v>3.0203</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8814</v>
+        <v>3.0203</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.065</v>
+        <v>2.3742</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>98</v>
       </c>
       <c r="M6" t="n">
-        <v>2.065</v>
+        <v>2.3742</v>
       </c>
       <c r="N6" t="n">
         <v>98</v>
@@ -722,26 +722,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.4939</v>
+        <v>2.417</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9593</v>
+        <v>0.9297</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4879</v>
+        <v>0.4761</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4939</v>
+        <v>2.417</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4939</v>
+        <v>2.417</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,44 +750,44 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7873</v>
+        <v>1.8999</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>176</v>
+        <v>98</v>
       </c>
       <c r="M7" t="n">
-        <v>1.7873</v>
+        <v>1.8999</v>
       </c>
       <c r="N7" t="n">
-        <v>176</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.382</v>
+        <v>2.3997</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9162</v>
+        <v>0.9231</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4373</v>
+        <v>0.4682</v>
       </c>
       <c r="E8" t="n">
-        <v>2.382</v>
+        <v>2.3997</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.382</v>
+        <v>2.3997</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,19 +796,19 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7071</v>
+        <v>1.8863</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="M8" t="n">
-        <v>1.7071</v>
+        <v>1.8863</v>
       </c>
       <c r="N8" t="n">
-        <v>98</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9">
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2656</v>
+        <v>2.231</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8715000000000001</v>
+        <v>0.8582</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3848</v>
+        <v>0.3914</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2656</v>
+        <v>2.231</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2656</v>
+        <v>2.231</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6237</v>
+        <v>1.7537</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>176</v>
       </c>
       <c r="M9" t="n">
-        <v>1.6237</v>
+        <v>1.7537</v>
       </c>
       <c r="N9" t="n">
         <v>176</v>
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1465</v>
+        <v>2.0687</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8257</v>
+        <v>0.7957</v>
       </c>
       <c r="D10" t="n">
-        <v>0.331</v>
+        <v>0.3175</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1465</v>
+        <v>2.0687</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1465</v>
+        <v>2.0687</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5383</v>
+        <v>1.6261</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>180</v>
       </c>
       <c r="M10" t="n">
-        <v>1.5383</v>
+        <v>1.6261</v>
       </c>
       <c r="N10" t="n">
         <v>180</v>
@@ -910,22 +910,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8666</v>
+        <v>1.8621</v>
       </c>
       <c r="C11" t="n">
-        <v>0.718</v>
+        <v>0.7163</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2047</v>
+        <v>0.2235</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8666</v>
+        <v>1.8621</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8666</v>
+        <v>1.8621</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3377</v>
+        <v>1.4637</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>105</v>
       </c>
       <c r="M11" t="n">
-        <v>1.3377</v>
+        <v>1.4637</v>
       </c>
       <c r="N11" t="n">
         <v>105</v>
@@ -952,26 +952,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.4563</v>
+        <v>1.6058</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5602</v>
+        <v>0.6177</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0194</v>
+        <v>0.1068</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4563</v>
+        <v>1.6058</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4563</v>
+        <v>1.6058</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,44 +980,44 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0437</v>
+        <v>1.2623</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="M12" t="n">
-        <v>1.0437</v>
+        <v>1.2623</v>
       </c>
       <c r="N12" t="n">
-        <v>46</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4559</v>
+        <v>1.4335</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5514</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0193</v>
+        <v>0.0284</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4559</v>
+        <v>1.4335</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4559</v>
+        <v>1.4335</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,19 +1026,19 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0434</v>
+        <v>1.1268</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="M13" t="n">
-        <v>1.0434</v>
+        <v>1.1268</v>
       </c>
       <c r="N13" t="n">
-        <v>105</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.2222</v>
+        <v>1.2738</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4701</v>
+        <v>0.49</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0863</v>
+        <v>-0.0443</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2222</v>
+        <v>1.2738</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2222</v>
+        <v>1.2738</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8759</v>
+        <v>1.0013</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>53</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8759</v>
+        <v>1.0013</v>
       </c>
       <c r="N14" t="n">
         <v>53</v>
@@ -1094,22 +1094,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9458</v>
+        <v>1.1082</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3638</v>
+        <v>0.4263</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.211</v>
+        <v>-0.1197</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9458</v>
+        <v>1.1082</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9458</v>
+        <v>1.1082</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6778</v>
+        <v>0.8711</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>105</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6778</v>
+        <v>0.8711</v>
       </c>
       <c r="N15" t="n">
         <v>105</v>
@@ -1136,26 +1136,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>BELCHONOKK</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8417</v>
+        <v>0.9367</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3238</v>
+        <v>0.3603</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.258</v>
+        <v>-0.1978</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8417</v>
+        <v>0.9367</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8417</v>
+        <v>0.9367</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,44 +1164,44 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6032</v>
+        <v>0.7363</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6032</v>
+        <v>0.7363</v>
       </c>
       <c r="N16" t="n">
-        <v>61</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BELCHONOKK</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8217</v>
+        <v>0.8497</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3161</v>
+        <v>0.3268</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2671</v>
+        <v>-0.2374</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8217</v>
+        <v>0.8497</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8217</v>
+        <v>0.8497</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,44 +1210,44 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5889</v>
+        <v>0.6679</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>176</v>
+        <v>61</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5889</v>
+        <v>0.6679</v>
       </c>
       <c r="N17" t="n">
-        <v>176</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.786</v>
+        <v>0.8081</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3023</v>
+        <v>0.3108</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2832</v>
+        <v>-0.2563</v>
       </c>
       <c r="E18" t="n">
-        <v>0.786</v>
+        <v>0.8081</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.786</v>
+        <v>0.8081</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,44 +1256,44 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5633</v>
+        <v>0.6352</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5633</v>
+        <v>0.6352</v>
       </c>
       <c r="N18" t="n">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7552</v>
+        <v>0.7653</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2905</v>
+        <v>0.2944</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2971</v>
+        <v>-0.2758</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7552</v>
+        <v>0.7653</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7552</v>
+        <v>0.7653</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,44 +1302,44 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5412</v>
+        <v>0.6016</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5412</v>
+        <v>0.6016</v>
       </c>
       <c r="N19" t="n">
-        <v>98</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4356</v>
+        <v>0.467</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1676</v>
+        <v>0.1796</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4414</v>
+        <v>-0.4116</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4356</v>
+        <v>0.467</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4356</v>
+        <v>0.467</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,44 +1348,44 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3122</v>
+        <v>0.3671</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3122</v>
+        <v>0.3671</v>
       </c>
       <c r="N20" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4242</v>
+        <v>0.4122</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1632</v>
+        <v>0.1586</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4465</v>
+        <v>-0.4366</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4242</v>
+        <v>0.4122</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4242</v>
+        <v>0.4122</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.304</v>
+        <v>0.324</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>51</v>
       </c>
       <c r="M21" t="n">
-        <v>0.304</v>
+        <v>0.324</v>
       </c>
       <c r="N21" t="n">
         <v>51</v>
@@ -1412,26 +1412,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3953</v>
+        <v>0.3811</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1521</v>
+        <v>0.1466</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4596</v>
+        <v>-0.4507</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3953</v>
+        <v>0.3811</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3953</v>
+        <v>0.3811</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,44 +1440,44 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2833</v>
+        <v>0.2996</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2833</v>
+        <v>0.2996</v>
       </c>
       <c r="N22" t="n">
-        <v>180</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3706</v>
+        <v>0.3755</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1426</v>
+        <v>0.1444</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4707</v>
+        <v>-0.4533</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3706</v>
+        <v>0.3755</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3706</v>
+        <v>0.3755</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,44 +1486,44 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2656</v>
+        <v>0.2952</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2656</v>
+        <v>0.2952</v>
       </c>
       <c r="N23" t="n">
-        <v>61</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3674</v>
+        <v>0.3675</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1413</v>
+        <v>0.1414</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4722</v>
+        <v>-0.4569</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3674</v>
+        <v>0.3675</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3674</v>
+        <v>0.3675</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2633</v>
+        <v>0.2889</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>61</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2633</v>
+        <v>0.2889</v>
       </c>
       <c r="N24" t="n">
         <v>61</v>
@@ -1550,26 +1550,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3297</v>
+        <v>0.3621</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1268</v>
+        <v>0.1393</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4892</v>
+        <v>-0.4594</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3297</v>
+        <v>0.3621</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3297</v>
+        <v>0.3621</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,44 +1578,44 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2363</v>
+        <v>0.2846</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2363</v>
+        <v>0.2846</v>
       </c>
       <c r="N25" t="n">
-        <v>105</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3244</v>
+        <v>0.3267</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1248</v>
+        <v>0.1257</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4916</v>
+        <v>-0.4755</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3244</v>
+        <v>0.3267</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3244</v>
+        <v>0.3267</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,44 +1624,44 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2325</v>
+        <v>0.2568</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>61</v>
+        <v>180</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2325</v>
+        <v>0.2568</v>
       </c>
       <c r="N26" t="n">
-        <v>61</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Chr1zN</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2269</v>
+        <v>0.2833</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0873</v>
+        <v>0.109</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5356</v>
+        <v>-0.4952</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2269</v>
+        <v>0.2833</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2269</v>
+        <v>0.2833</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,44 +1670,44 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1626</v>
+        <v>0.2227</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1626</v>
+        <v>0.2227</v>
       </c>
       <c r="N27" t="n">
-        <v>53</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>Chr1zN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0999</v>
+        <v>0.2122</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0384</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5929</v>
+        <v>-0.5276</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0999</v>
+        <v>0.2122</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0999</v>
+        <v>0.2122</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,44 +1716,44 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0716</v>
+        <v>0.1668</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0716</v>
+        <v>0.1668</v>
       </c>
       <c r="N28" t="n">
-        <v>98</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>hypex</t>
+          <t>nilo</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0858</v>
+        <v>0.1438</v>
       </c>
       <c r="C29" t="n">
-        <v>0.033</v>
+        <v>0.0553</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5993000000000001</v>
+        <v>-0.5587</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0858</v>
+        <v>0.1438</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0858</v>
+        <v>0.1438</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,44 +1762,44 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0615</v>
+        <v>0.113</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0615</v>
+        <v>0.113</v>
       </c>
       <c r="N29" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>nilo</t>
+          <t>hypex</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0682</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0262</v>
+        <v>0.0275</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6072</v>
+        <v>-0.5917</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0682</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0682</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,19 +1808,19 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0489</v>
+        <v>0.0561</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0489</v>
+        <v>0.0561</v>
       </c>
       <c r="N30" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31">
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0155</v>
+        <v>-0.0232</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.006</v>
+        <v>-0.0089</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.645</v>
+        <v>-0.6348</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0155</v>
+        <v>-0.0232</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.0155</v>
+        <v>-0.0232</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.0111</v>
+        <v>-0.0182</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>51</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0111</v>
+        <v>-0.0182</v>
       </c>
       <c r="N31" t="n">
         <v>51</v>
@@ -1876,22 +1876,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1372</v>
+        <v>-0.1519</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0528</v>
+        <v>-0.0584</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7</v>
+        <v>-0.6934</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1372</v>
+        <v>-0.1519</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.1372</v>
+        <v>-0.1519</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.0983</v>
+        <v>-0.1194</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>51</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.0983</v>
+        <v>-0.1194</v>
       </c>
       <c r="N32" t="n">
         <v>51</v>
@@ -1922,22 +1922,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3561</v>
+        <v>-0.2986</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.137</v>
+        <v>-0.1149</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7988</v>
+        <v>-0.7601</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3561</v>
+        <v>-0.2986</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.3561</v>
+        <v>-0.2986</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.2552</v>
+        <v>-0.2347</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>53</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.2552</v>
+        <v>-0.2347</v>
       </c>
       <c r="N33" t="n">
         <v>53</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.571</v>
+        <v>-0.5576</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2196</v>
+        <v>-0.2145</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8958</v>
+        <v>-0.878</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.571</v>
+        <v>-0.5576</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.571</v>
+        <v>-0.5576</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.4092</v>
+        <v>-0.4383</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4092</v>
+        <v>-0.4383</v>
       </c>
       <c r="N34" t="n">
         <v>46</v>
@@ -2014,22 +2014,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6188</v>
+        <v>-0.5975</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.238</v>
+        <v>-0.2298</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9174</v>
+        <v>-0.8962</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6188</v>
+        <v>-0.5975</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.6188</v>
+        <v>-0.5975</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.4435</v>
+        <v>-0.4697</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>46</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.4435</v>
+        <v>-0.4697</v>
       </c>
       <c r="N35" t="n">
         <v>46</v>
@@ -2060,22 +2060,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8325</v>
+        <v>-0.7924</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3202</v>
+        <v>-0.3048</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0138</v>
+        <v>-0.9849</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8325</v>
+        <v>-0.7924</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.8325</v>
+        <v>-0.7924</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.5966</v>
+        <v>-0.6229</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>46</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5966</v>
+        <v>-0.6229</v>
       </c>
       <c r="N36" t="n">
         <v>46</v>
@@ -2102,26 +2102,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>susp</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9649</v>
+        <v>-0.8133</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3712</v>
+        <v>-0.3128</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0736</v>
+        <v>-0.9944</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9649</v>
+        <v>-0.8133</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.9649</v>
+        <v>-0.8133</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2130,44 +2130,44 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.6915</v>
+        <v>-0.6393</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.6915</v>
+        <v>-0.6393</v>
       </c>
       <c r="N37" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9946</v>
+        <v>-0.8353</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3826</v>
+        <v>-0.3213</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.087</v>
+        <v>-1.0044</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9946</v>
+        <v>-0.8353</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.9946</v>
+        <v>-0.8353</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2176,44 +2176,44 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.7128</v>
+        <v>-0.6566</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.7128</v>
+        <v>-0.6566</v>
       </c>
       <c r="N38" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>susp</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0398</v>
+        <v>-0.8975</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4</v>
+        <v>-0.3452</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1074</v>
+        <v>-1.0328</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0398</v>
+        <v>-0.8975</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.0398</v>
+        <v>-0.8975</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2222,19 +2222,19 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.7452</v>
+        <v>-0.7055</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.7452</v>
+        <v>-0.7055</v>
       </c>
       <c r="N39" t="n">
-        <v>98</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40">
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.213</v>
+        <v>-1.1269</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4666</v>
+        <v>-0.4335</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1856</v>
+        <v>-1.1372</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.213</v>
+        <v>-1.1269</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.213</v>
+        <v>-1.1269</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.8693</v>
+        <v>-0.8858</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>51</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.8693</v>
+        <v>-0.8858</v>
       </c>
       <c r="N40" t="n">
         <v>51</v>
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.4693</v>
+        <v>-1.172</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5652</v>
+        <v>-0.4508</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3013</v>
+        <v>-1.1577</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.4693</v>
+        <v>-1.172</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.4693</v>
+        <v>-1.172</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.053</v>
+        <v>-0.9213</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>180</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.053</v>
+        <v>-0.9213</v>
       </c>
       <c r="N41" t="n">
         <v>180</v>
@@ -2429,10 +2429,10 @@
         <v>1.14</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3418</v>
+        <v>0.3398</v>
       </c>
       <c r="J2" t="n">
-        <v>7.5196</v>
+        <v>7.4756</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.14</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3418</v>
+        <v>0.3398</v>
       </c>
       <c r="J3" t="n">
-        <v>7.5196</v>
+        <v>7.4756</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.99</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0164</v>
+        <v>-0.0221</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3608</v>
+        <v>-0.4862</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2228</v>
+        <v>-0.2376</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.9016</v>
+        <v>-5.2272</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.66</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3679</v>
+        <v>-0.3794</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.0938</v>
+        <v>-8.3468</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.8</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5177</v>
+        <v>1.6421</v>
       </c>
       <c r="J7" t="n">
-        <v>33.3894</v>
+        <v>36.1262</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.13</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3864</v>
+        <v>0.387</v>
       </c>
       <c r="J8" t="n">
-        <v>8.5008</v>
+        <v>8.513999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1212</v>
+        <v>0.1392</v>
       </c>
       <c r="J9" t="n">
-        <v>2.6664</v>
+        <v>3.0624</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.02</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0494</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0868</v>
+        <v>1.518</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.97</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.18</v>
+        <v>-0.1701</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.96</v>
+        <v>-3.7422</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.35</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7364000000000001</v>
+        <v>0.6998</v>
       </c>
       <c r="J12" t="n">
-        <v>17.6736</v>
+        <v>16.7952</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.95</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.68</v>
+        <v>-1.9584</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.87</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1587</v>
+        <v>-0.1738</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.8088</v>
+        <v>-4.1712</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.85</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1795</v>
+        <v>-0.1949</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.308</v>
+        <v>-4.6776</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.62</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4028</v>
+        <v>-0.4133</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.667199999999999</v>
+        <v>-9.9192</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.47</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1386</v>
+        <v>1.1263</v>
       </c>
       <c r="J17" t="n">
-        <v>27.3264</v>
+        <v>27.0312</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.28</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7905</v>
+        <v>0.7423</v>
       </c>
       <c r="J18" t="n">
-        <v>18.972</v>
+        <v>17.8152</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.99</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0704</v>
+        <v>-0.0703</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.6896</v>
+        <v>-1.6872</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.84</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5365</v>
+        <v>-0.5078</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.876</v>
+        <v>-12.1872</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.78</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6937</v>
+        <v>-0.6478</v>
       </c>
       <c r="J21" t="n">
-        <v>-16.6488</v>
+        <v>-15.5472</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.4</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8017</v>
+        <v>0.7615</v>
       </c>
       <c r="J22" t="n">
-        <v>19.2408</v>
+        <v>18.276</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.22</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4857</v>
+        <v>0.4752</v>
       </c>
       <c r="J23" t="n">
-        <v>11.6568</v>
+        <v>11.4048</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.79</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2455</v>
+        <v>-0.2595</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.892</v>
+        <v>-6.228</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.78</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2554</v>
+        <v>-0.2693</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.1296</v>
+        <v>-6.4632</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.66</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3705</v>
+        <v>-0.3814</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.891999999999999</v>
+        <v>-9.153600000000001</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.51</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1769</v>
+        <v>1.1852</v>
       </c>
       <c r="J27" t="n">
-        <v>28.2456</v>
+        <v>28.4448</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.37</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9766</v>
+        <v>0.9137</v>
       </c>
       <c r="J28" t="n">
-        <v>23.4384</v>
+        <v>21.9288</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0276</v>
+        <v>-0.0189</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.6624</v>
+        <v>-0.4536</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.99</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0824</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.9776</v>
+        <v>-1.8888</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.72</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8565</v>
+        <v>-0.7887</v>
       </c>
       <c r="J31" t="n">
-        <v>-20.556</v>
+        <v>-18.9288</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.51</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8711</v>
+        <v>0.9623</v>
       </c>
       <c r="J32" t="n">
-        <v>18.2931</v>
+        <v>20.2083</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.36</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6781</v>
+        <v>0.7532</v>
       </c>
       <c r="J33" t="n">
-        <v>14.2401</v>
+        <v>15.8172</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.34</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6518</v>
+        <v>0.7244</v>
       </c>
       <c r="J34" t="n">
-        <v>13.6878</v>
+        <v>15.2124</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.25</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5319</v>
+        <v>0.5914</v>
       </c>
       <c r="J35" t="n">
-        <v>11.1699</v>
+        <v>12.4194</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.74</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8355</v>
+        <v>-0.7655</v>
       </c>
       <c r="J36" t="n">
-        <v>-17.5455</v>
+        <v>-16.0755</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.11</v>
       </c>
       <c r="I37" t="n">
-        <v>0.302</v>
+        <v>0.2978</v>
       </c>
       <c r="J37" t="n">
-        <v>6.342</v>
+        <v>6.2538</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.96</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0527</v>
+        <v>-0.0645</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.1067</v>
+        <v>-1.3545</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.86</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.165</v>
+        <v>-0.1813</v>
       </c>
       <c r="J39" t="n">
-        <v>-3.465</v>
+        <v>-3.8073</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.8</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2256</v>
+        <v>-0.242</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.7376</v>
+        <v>-5.082</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.72</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3037</v>
+        <v>-0.3186</v>
       </c>
       <c r="J41" t="n">
-        <v>-6.3777</v>
+        <v>-6.6906</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.2</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4879</v>
+        <v>0.5352</v>
       </c>
       <c r="J42" t="n">
-        <v>11.7096</v>
+        <v>12.8448</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.16</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4271</v>
+        <v>0.4667</v>
       </c>
       <c r="J43" t="n">
-        <v>10.2504</v>
+        <v>11.2008</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.11</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3475</v>
+        <v>0.3545</v>
       </c>
       <c r="J44" t="n">
-        <v>8.34</v>
+        <v>8.507999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.01</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0408</v>
+        <v>0.0502</v>
       </c>
       <c r="J45" t="n">
-        <v>0.9792</v>
+        <v>1.2048</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.84</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5342</v>
+        <v>-0.5063</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.8208</v>
+        <v>-12.1512</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.34</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5527</v>
+        <v>0.6127</v>
       </c>
       <c r="J47" t="n">
-        <v>13.2648</v>
+        <v>14.7048</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.24</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4481</v>
+        <v>0.4934</v>
       </c>
       <c r="J48" t="n">
-        <v>10.7544</v>
+        <v>11.8416</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2237</v>
+        <v>-0.2384</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.3688</v>
+        <v>-5.7216</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.72</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.312</v>
+        <v>-0.3251</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.488</v>
+        <v>-7.8024</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.67</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3595</v>
+        <v>-0.3711</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.628</v>
+        <v>-8.9064</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.49</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7075</v>
+        <v>0.7851</v>
       </c>
       <c r="J52" t="n">
-        <v>16.2725</v>
+        <v>18.0573</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.23</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4407</v>
+        <v>0.484</v>
       </c>
       <c r="J53" t="n">
-        <v>10.1361</v>
+        <v>11.132</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.78</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.252</v>
+        <v>-0.2666</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.796</v>
+        <v>-6.1318</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.67</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3578</v>
+        <v>-0.3698</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.2294</v>
+        <v>-8.5054</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.54</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4777</v>
+        <v>-0.4844</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.9871</v>
+        <v>-11.1412</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.49</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.956</v>
       </c>
       <c r="J57" t="n">
-        <v>19.9985</v>
+        <v>21.988</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.36</v>
       </c>
       <c r="I58" t="n">
-        <v>0.697</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>16.031</v>
+        <v>17.7031</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.08</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2581</v>
+        <v>0.2658</v>
       </c>
       <c r="J59" t="n">
-        <v>5.9363</v>
+        <v>6.1134</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.97</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1676</v>
+        <v>-0.1614</v>
       </c>
       <c r="J60" t="n">
-        <v>-3.8548</v>
+        <v>-3.7122</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.82</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6091</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="J61" t="n">
-        <v>-14.0093</v>
+        <v>-13.0893</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.93</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7387</v>
+        <v>0.8517</v>
       </c>
       <c r="J62" t="n">
-        <v>12.5579</v>
+        <v>14.4789</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.83</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6811</v>
+        <v>0.7857</v>
       </c>
       <c r="J63" t="n">
-        <v>11.5787</v>
+        <v>13.3569</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.3</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3609</v>
+        <v>0.3985</v>
       </c>
       <c r="J64" t="n">
-        <v>6.1353</v>
+        <v>6.7745</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.02</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0001</v>
+        <v>0.0188</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.0017</v>
+        <v>0.3196</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.95</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1144</v>
+        <v>-0.1161</v>
       </c>
       <c r="J66" t="n">
-        <v>-1.9448</v>
+        <v>-1.9737</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.32</v>
       </c>
       <c r="I67" t="n">
-        <v>0.46</v>
+        <v>0.5059</v>
       </c>
       <c r="J67" t="n">
-        <v>7.82</v>
+        <v>8.600300000000001</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.89</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1323</v>
+        <v>-0.1483</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.2491</v>
+        <v>-2.5211</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.88</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1428</v>
+        <v>-0.1591</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.4276</v>
+        <v>-2.7047</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.63</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.386</v>
+        <v>-0.3985</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.562</v>
+        <v>-6.7745</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.62</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3954</v>
+        <v>-0.4074</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.7218</v>
+        <v>-6.9258</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>0.0568</v>
+        <v>0.0412</v>
       </c>
       <c r="J72" t="n">
-        <v>1.0792</v>
+        <v>0.7828000000000001</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.97</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0225</v>
+        <v>-0.0369</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.4275</v>
+        <v>-0.7010999999999999</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.83</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1865</v>
+        <v>-0.2052</v>
       </c>
       <c r="J74" t="n">
-        <v>-3.5435</v>
+        <v>-3.8988</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.64</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3672</v>
+        <v>-0.3821</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.9768</v>
+        <v>-7.2599</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.442</v>
+        <v>-0.4533</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.398</v>
+        <v>-8.6127</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>2.18</v>
       </c>
       <c r="I77" t="n">
-        <v>1.6252</v>
+        <v>1.7608</v>
       </c>
       <c r="J77" t="n">
-        <v>30.8788</v>
+        <v>33.4552</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.57</v>
       </c>
       <c r="I78" t="n">
-        <v>0.9192</v>
+        <v>1.0191</v>
       </c>
       <c r="J78" t="n">
-        <v>17.4648</v>
+        <v>19.3629</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.17</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4028</v>
+        <v>0.4488</v>
       </c>
       <c r="J79" t="n">
-        <v>7.6532</v>
+        <v>8.527200000000001</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.14</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3567</v>
+        <v>0.3831</v>
       </c>
       <c r="J80" t="n">
-        <v>6.7773</v>
+        <v>7.2789</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.8</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7119</v>
+        <v>-0.6513</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.5261</v>
+        <v>-12.3747</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.2</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3414</v>
+        <v>0.3493</v>
       </c>
       <c r="J82" t="n">
-        <v>6.1452</v>
+        <v>6.2874</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.07</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1497</v>
+        <v>0.1569</v>
       </c>
       <c r="J83" t="n">
-        <v>2.6946</v>
+        <v>2.8242</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.88</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1507</v>
+        <v>-0.1651</v>
       </c>
       <c r="J84" t="n">
-        <v>-2.7126</v>
+        <v>-2.9718</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.82</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2131</v>
+        <v>-0.2279</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.8358</v>
+        <v>-4.1022</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2433</v>
+        <v>-0.2578</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.3794</v>
+        <v>-4.6404</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>2.11</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="J87" t="n">
-        <v>15.1236</v>
+        <v>17.4096</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.53</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5033</v>
+        <v>0.5794</v>
       </c>
       <c r="J88" t="n">
-        <v>9.0594</v>
+        <v>10.4292</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.3</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3607</v>
+        <v>0.3982</v>
       </c>
       <c r="J89" t="n">
-        <v>6.4926</v>
+        <v>7.1676</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.22</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2851</v>
+        <v>0.3072</v>
       </c>
       <c r="J90" t="n">
-        <v>5.1318</v>
+        <v>5.5296</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.89</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1842</v>
+        <v>-0.1888</v>
       </c>
       <c r="J91" t="n">
-        <v>-3.3156</v>
+        <v>-3.3984</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.14</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4012</v>
+        <v>0.4327</v>
       </c>
       <c r="J92" t="n">
-        <v>8.8264</v>
+        <v>9.519399999999999</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.11</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3525</v>
+        <v>0.3599</v>
       </c>
       <c r="J93" t="n">
-        <v>7.755</v>
+        <v>7.9178</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.98</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.102</v>
+        <v>-0.1052</v>
       </c>
       <c r="J94" t="n">
-        <v>-2.244</v>
+        <v>-2.3144</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.98</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.102</v>
+        <v>-0.1052</v>
       </c>
       <c r="J95" t="n">
-        <v>-2.244</v>
+        <v>-2.3144</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.97</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1389</v>
+        <v>-0.1415</v>
       </c>
       <c r="J96" t="n">
-        <v>-3.0558</v>
+        <v>-3.113</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.32</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5167</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="J97" t="n">
-        <v>11.3674</v>
+        <v>12.6522</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.21</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4028</v>
+        <v>0.4422</v>
       </c>
       <c r="J98" t="n">
-        <v>8.861599999999999</v>
+        <v>9.728400000000001</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.99</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0221</v>
+        <v>-0.0264</v>
       </c>
       <c r="J99" t="n">
-        <v>-0.4862</v>
+        <v>-0.5808</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.92</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1138</v>
+        <v>-0.1253</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.5036</v>
+        <v>-2.7566</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.66</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.376</v>
+        <v>-0.3857</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.272</v>
+        <v>-8.4854</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.51</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8825</v>
+        <v>0.9724</v>
       </c>
       <c r="J102" t="n">
-        <v>18.5325</v>
+        <v>20.4204</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.28</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5788</v>
+        <v>0.642</v>
       </c>
       <c r="J103" t="n">
-        <v>12.1548</v>
+        <v>13.482</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.16</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4107</v>
+        <v>0.4519</v>
       </c>
       <c r="J104" t="n">
-        <v>8.624700000000001</v>
+        <v>9.4899</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.06</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1861</v>
+        <v>0.201</v>
       </c>
       <c r="J105" t="n">
-        <v>3.9081</v>
+        <v>4.221</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.95</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2484</v>
+        <v>-0.2359</v>
       </c>
       <c r="J106" t="n">
-        <v>-5.2164</v>
+        <v>-4.9539</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.14</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3447</v>
+        <v>0.3482</v>
       </c>
       <c r="J107" t="n">
-        <v>7.2387</v>
+        <v>7.3122</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0164</v>
+        <v>0.0117</v>
       </c>
       <c r="J108" t="n">
-        <v>0.3444</v>
+        <v>0.2457</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.83</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1986</v>
+        <v>-0.2144</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.1706</v>
+        <v>-4.5024</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.83</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1986</v>
+        <v>-0.2144</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.1706</v>
+        <v>-4.5024</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.78</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2487</v>
+        <v>-0.2641</v>
       </c>
       <c r="J111" t="n">
-        <v>-5.2227</v>
+        <v>-5.5461</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.11</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2835</v>
+        <v>0.2841</v>
       </c>
       <c r="J112" t="n">
-        <v>6.237</v>
+        <v>6.2502</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.97</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0456</v>
+        <v>-0.0549</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.0032</v>
+        <v>-1.2078</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.92</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1058</v>
+        <v>-0.1191</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.3276</v>
+        <v>-2.6202</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.89</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1388</v>
+        <v>-0.1533</v>
       </c>
       <c r="J115" t="n">
-        <v>-3.0536</v>
+        <v>-3.3726</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.82</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2119</v>
+        <v>-0.227</v>
       </c>
       <c r="J116" t="n">
-        <v>-4.6618</v>
+        <v>-4.994</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.31</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6339</v>
+        <v>0.6996</v>
       </c>
       <c r="J117" t="n">
-        <v>13.9458</v>
+        <v>15.3912</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.28</v>
       </c>
       <c r="I118" t="n">
-        <v>0.592</v>
+        <v>0.6536</v>
       </c>
       <c r="J118" t="n">
-        <v>13.024</v>
+        <v>14.3792</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.22</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5064</v>
+        <v>0.5586</v>
       </c>
       <c r="J119" t="n">
-        <v>11.1408</v>
+        <v>12.2892</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.95</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2296</v>
+        <v>-0.2227</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.0512</v>
+        <v>-4.8994</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.84</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5496</v>
+        <v>-0.5171</v>
       </c>
       <c r="J121" t="n">
-        <v>-12.0912</v>
+        <v>-11.3762</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.54</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7602</v>
+        <v>0.8427</v>
       </c>
       <c r="J122" t="n">
-        <v>18.2448</v>
+        <v>20.2248</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.03</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1071</v>
+        <v>0.111</v>
       </c>
       <c r="J123" t="n">
-        <v>2.5704</v>
+        <v>2.664</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.76</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2704</v>
+        <v>-0.285</v>
       </c>
       <c r="J124" t="n">
-        <v>-6.4896</v>
+        <v>-6.84</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3377</v>
+        <v>-0.3506</v>
       </c>
       <c r="J125" t="n">
-        <v>-8.104799999999999</v>
+        <v>-8.414400000000001</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.64</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3847</v>
+        <v>-0.3959</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.232799999999999</v>
+        <v>-9.5016</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.35</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7607</v>
       </c>
       <c r="J127" t="n">
-        <v>16.56</v>
+        <v>18.2568</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.34</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6762</v>
+        <v>0.7458</v>
       </c>
       <c r="J128" t="n">
-        <v>16.2288</v>
+        <v>17.8992</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0271</v>
+        <v>-0.0186</v>
       </c>
       <c r="J129" t="n">
-        <v>-0.6504</v>
+        <v>-0.4464</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.98</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.123</v>
+        <v>-0.1197</v>
       </c>
       <c r="J130" t="n">
-        <v>-2.952</v>
+        <v>-2.8728</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.91</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3523</v>
+        <v>-0.3378</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.4552</v>
+        <v>-8.107200000000001</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.74</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6331</v>
+        <v>0.7297</v>
       </c>
       <c r="J132" t="n">
-        <v>10.1296</v>
+        <v>11.6752</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.52</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5007</v>
+        <v>0.5755</v>
       </c>
       <c r="J133" t="n">
-        <v>8.011200000000001</v>
+        <v>9.208</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.35</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3956</v>
+        <v>0.4492</v>
       </c>
       <c r="J134" t="n">
-        <v>6.3296</v>
+        <v>7.1872</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.19</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2529</v>
+        <v>0.2747</v>
       </c>
       <c r="J135" t="n">
-        <v>4.0464</v>
+        <v>4.3952</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.02</v>
       </c>
       <c r="I136" t="n">
-        <v>0.0044</v>
+        <v>0.0223</v>
       </c>
       <c r="J136" t="n">
-        <v>0.0704</v>
+        <v>0.3568</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.24</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4257</v>
+        <v>0.4589</v>
       </c>
       <c r="J137" t="n">
-        <v>6.8112</v>
+        <v>7.3424</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.88</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1253</v>
+        <v>-0.1456</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.0048</v>
+        <v>-2.3296</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.79</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2204</v>
+        <v>-0.2402</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.5264</v>
+        <v>-3.8432</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.51</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.482</v>
+        <v>-0.4921</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.712</v>
+        <v>-7.8736</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.36</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6204</v>
+        <v>-0.621</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.926399999999999</v>
+        <v>-9.936</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>0.71</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.284</v>
+        <v>-0.3053</v>
       </c>
       <c r="J142" t="n">
-        <v>-4.26</v>
+        <v>-4.5795</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.7</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.2935</v>
+        <v>-0.3145</v>
       </c>
       <c r="J143" t="n">
-        <v>-4.4025</v>
+        <v>-4.7175</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.68</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3119</v>
+        <v>-0.3324</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.6785</v>
+        <v>-4.986</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.66</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3292</v>
+        <v>-0.3493</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.938</v>
+        <v>-5.2395</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.59</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3932</v>
+        <v>-0.4105</v>
       </c>
       <c r="J146" t="n">
-        <v>-5.898</v>
+        <v>-6.1575</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.83</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1981</v>
+        <v>1.3202</v>
       </c>
       <c r="J147" t="n">
-        <v>17.9715</v>
+        <v>19.803</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.56</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8889</v>
+        <v>0.9903</v>
       </c>
       <c r="J148" t="n">
-        <v>13.3335</v>
+        <v>14.8545</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.47</v>
       </c>
       <c r="I149" t="n">
-        <v>0.785</v>
+        <v>0.8771</v>
       </c>
       <c r="J149" t="n">
-        <v>11.775</v>
+        <v>13.1565</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.34</v>
       </c>
       <c r="I150" t="n">
-        <v>0.623</v>
+        <v>0.6996</v>
       </c>
       <c r="J150" t="n">
-        <v>9.345000000000001</v>
+        <v>10.494</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.33</v>
       </c>
       <c r="I151" t="n">
-        <v>0.61</v>
+        <v>0.6852</v>
       </c>
       <c r="J151" t="n">
-        <v>9.15</v>
+        <v>10.278</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.44</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6592</v>
+        <v>0.7311</v>
       </c>
       <c r="J152" t="n">
-        <v>14.5024</v>
+        <v>16.0842</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.08</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2216</v>
+        <v>0.2245</v>
       </c>
       <c r="J153" t="n">
-        <v>4.8752</v>
+        <v>4.939</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.84</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.191</v>
+        <v>-0.2062</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.202</v>
+        <v>-4.5364</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.67</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3573</v>
+        <v>-0.3694</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.8606</v>
+        <v>-8.126799999999999</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.66</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3667</v>
+        <v>-0.3785</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.067399999999999</v>
+        <v>-8.327</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.79</v>
       </c>
       <c r="I157" t="n">
-        <v>1.2291</v>
+        <v>1.34</v>
       </c>
       <c r="J157" t="n">
-        <v>27.0402</v>
+        <v>29.48</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.27</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5638</v>
+        <v>0.6258</v>
       </c>
       <c r="J158" t="n">
-        <v>12.4036</v>
+        <v>13.7676</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.26</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5501</v>
+        <v>0.6105</v>
       </c>
       <c r="J159" t="n">
-        <v>12.1022</v>
+        <v>13.431</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.88</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4605</v>
+        <v>-0.4323</v>
       </c>
       <c r="J160" t="n">
-        <v>-10.131</v>
+        <v>-9.5106</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.8</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6751</v>
+        <v>-0.6254</v>
       </c>
       <c r="J161" t="n">
-        <v>-14.8522</v>
+        <v>-13.7588</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.18</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3743</v>
+        <v>0.3996</v>
       </c>
       <c r="J162" t="n">
-        <v>11.229</v>
+        <v>11.988</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.15</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3393</v>
+        <v>0.3466</v>
       </c>
       <c r="J163" t="n">
-        <v>10.179</v>
+        <v>10.398</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.01</v>
       </c>
       <c r="I164" t="n">
-        <v>0.038</v>
+        <v>0.0435</v>
       </c>
       <c r="J164" t="n">
-        <v>1.14</v>
+        <v>1.305</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.96</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.063</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="J165" t="n">
-        <v>-1.89</v>
+        <v>-2.172</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3455</v>
+        <v>-0.3567</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.365</v>
+        <v>-10.701</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.4</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7633</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="J167" t="n">
-        <v>22.899</v>
+        <v>25.176</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.09</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2964</v>
+        <v>0.2992</v>
       </c>
       <c r="J168" t="n">
-        <v>8.891999999999999</v>
+        <v>8.976000000000001</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.05</v>
       </c>
       <c r="I169" t="n">
-        <v>0.1775</v>
+        <v>0.1869</v>
       </c>
       <c r="J169" t="n">
-        <v>5.325</v>
+        <v>5.607</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.97</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1549</v>
+        <v>-0.1526</v>
       </c>
       <c r="J170" t="n">
-        <v>-4.647</v>
+        <v>-4.578</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.97</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1549</v>
+        <v>-0.1526</v>
       </c>
       <c r="J171" t="n">
-        <v>-4.647</v>
+        <v>-4.578</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.97</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0353</v>
+        <v>-0.047</v>
       </c>
       <c r="J172" t="n">
-        <v>-0.7413</v>
+        <v>-0.987</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.97</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0353</v>
+        <v>-0.047</v>
       </c>
       <c r="J173" t="n">
-        <v>-0.7413</v>
+        <v>-0.987</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.96</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0491</v>
+        <v>-0.0617</v>
       </c>
       <c r="J174" t="n">
-        <v>-1.0311</v>
+        <v>-1.2957</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.95</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0621</v>
+        <v>-0.0756</v>
       </c>
       <c r="J175" t="n">
-        <v>-1.3041</v>
+        <v>-1.5876</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.48</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5238</v>
+        <v>-0.5291</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.9998</v>
+        <v>-11.1111</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.96</v>
       </c>
       <c r="I177" t="n">
-        <v>1.3898</v>
+        <v>1.5143</v>
       </c>
       <c r="J177" t="n">
-        <v>29.1858</v>
+        <v>31.8003</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.67</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0486</v>
+        <v>1.1555</v>
       </c>
       <c r="J178" t="n">
-        <v>22.0206</v>
+        <v>24.2655</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.1</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2731</v>
+        <v>0.2898</v>
       </c>
       <c r="J179" t="n">
-        <v>5.7351</v>
+        <v>6.0858</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.03</v>
       </c>
       <c r="I180" t="n">
-        <v>0.0543</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="J180" t="n">
-        <v>1.1403</v>
+        <v>1.7451</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.87</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5174</v>
+        <v>-0.4781</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.8654</v>
+        <v>-10.0401</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/8246/event_8246_evp_summary.xlsx
+++ b/database/event/8246/event_8246_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.1226</v>
+        <v>5.3738</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9704</v>
+        <v>2.067</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7077</v>
+        <v>1.7865</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1226</v>
+        <v>5.3738</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1226</v>
+        <v>5.122</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0267</v>
+        <v>4.0262</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>180</v>
       </c>
       <c r="M2" t="n">
-        <v>4.0267</v>
+        <v>4.0262</v>
       </c>
       <c r="N2" t="n">
         <v>180</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.0202</v>
+        <v>4.1732</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5464</v>
+        <v>1.6052</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2059</v>
+        <v>1.2503</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0202</v>
+        <v>4.1732</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0202</v>
+        <v>4.02</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1601</v>
+        <v>3.16</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>180</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1601</v>
+        <v>3.16</v>
       </c>
       <c r="N3" t="n">
         <v>180</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.8352</v>
+        <v>3.9035</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4752</v>
+        <v>1.5015</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1217</v>
+        <v>1.1298</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8352</v>
+        <v>3.9035</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8352</v>
+        <v>3.8193</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0147</v>
+        <v>3.0022</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>176</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0147</v>
+        <v>3.0022</v>
       </c>
       <c r="N4" t="n">
         <v>176</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.3895</v>
+        <v>3.3955</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3038</v>
+        <v>1.3061</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9188</v>
+        <v>0.9029</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3895</v>
+        <v>3.3955</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3895</v>
+        <v>3.3899</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6644</v>
+        <v>2.6647</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>176</v>
       </c>
       <c r="M5" t="n">
-        <v>2.6644</v>
+        <v>2.6647</v>
       </c>
       <c r="N5" t="n">
         <v>176</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.0203</v>
+        <v>3.259</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1618</v>
+        <v>1.2536</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7507</v>
+        <v>0.8419</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0203</v>
+        <v>3.259</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.417</v>
+        <v>2.5883</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9297</v>
+        <v>0.9956</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4761</v>
+        <v>0.5423</v>
       </c>
       <c r="E7" t="n">
-        <v>2.417</v>
+        <v>2.5883</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.3997</v>
+        <v>2.3818</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9231</v>
+        <v>0.9162</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4682</v>
+        <v>0.4501</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3997</v>
+        <v>2.3818</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3997</v>
+        <v>2.4</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8863</v>
+        <v>1.8866</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>176</v>
       </c>
       <c r="M8" t="n">
-        <v>1.8863</v>
+        <v>1.8866</v>
       </c>
       <c r="N8" t="n">
         <v>176</v>
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.231</v>
+        <v>2.2597</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8582</v>
+        <v>0.8692</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3914</v>
+        <v>0.3955</v>
       </c>
       <c r="E9" t="n">
-        <v>2.231</v>
+        <v>2.2597</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.231</v>
+        <v>2.2315</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7537</v>
+        <v>1.7541</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>176</v>
       </c>
       <c r="M9" t="n">
-        <v>1.7537</v>
+        <v>1.7541</v>
       </c>
       <c r="N9" t="n">
         <v>176</v>
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.0687</v>
+        <v>2.018</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7957</v>
+        <v>0.7762</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3175</v>
+        <v>0.2876</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0687</v>
+        <v>2.018</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.0687</v>
+        <v>2.0684</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6261</v>
+        <v>1.6259</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>180</v>
       </c>
       <c r="M10" t="n">
-        <v>1.6261</v>
+        <v>1.6259</v>
       </c>
       <c r="N10" t="n">
         <v>180</v>
@@ -906,26 +906,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8621</v>
+        <v>1.7747</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7163</v>
+        <v>0.6826</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2235</v>
+        <v>0.1789</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8621</v>
+        <v>1.7747</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8621</v>
+        <v>1.6058</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4637</v>
+        <v>1.2623</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>105</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4637</v>
+        <v>1.2623</v>
       </c>
       <c r="N11" t="n">
         <v>105</v>
@@ -952,26 +952,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.6058</v>
+        <v>1.7697</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6177</v>
+        <v>0.6807</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1068</v>
+        <v>0.1767</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6058</v>
+        <v>1.7697</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6058</v>
+        <v>1.8621</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.2623</v>
+        <v>1.4637</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>105</v>
       </c>
       <c r="M12" t="n">
-        <v>1.2623</v>
+        <v>1.4637</v>
       </c>
       <c r="N12" t="n">
         <v>105</v>
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4335</v>
+        <v>1.7267</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5514</v>
+        <v>0.6642</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0284</v>
+        <v>0.1575</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4335</v>
+        <v>1.7267</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.2738</v>
+        <v>1.2979</v>
       </c>
       <c r="C14" t="n">
-        <v>0.49</v>
+        <v>0.4992</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0443</v>
+        <v>-0.0341</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2738</v>
+        <v>1.2979</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2738</v>
+        <v>1.2734</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0013</v>
+        <v>1.001</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>53</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0013</v>
+        <v>1.001</v>
       </c>
       <c r="N14" t="n">
         <v>53</v>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.1082</v>
+        <v>1.1408</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4263</v>
+        <v>0.4388</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1197</v>
+        <v>-0.1042</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1082</v>
+        <v>1.1408</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1136,26 +1136,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BELCHONOKK</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9367</v>
+        <v>0.9509</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3603</v>
+        <v>0.3658</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1978</v>
+        <v>-0.1891</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9367</v>
+        <v>0.9509</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9367</v>
+        <v>0.8494</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,44 +1164,44 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7363</v>
+        <v>0.6677</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>176</v>
+        <v>61</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7363</v>
+        <v>0.6677</v>
       </c>
       <c r="N16" t="n">
-        <v>176</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>BELCHONOKK</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8497</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3268</v>
+        <v>0.3302</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2374</v>
+        <v>-0.2304</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8497</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8497</v>
+        <v>0.9367</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,44 +1210,44 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6679</v>
+        <v>0.7363</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6679</v>
+        <v>0.7363</v>
       </c>
       <c r="N17" t="n">
-        <v>61</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8081</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3108</v>
+        <v>0.2926</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2563</v>
+        <v>-0.2741</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8081</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8081</v>
+        <v>0.3673</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,19 +1256,19 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6352</v>
+        <v>0.2887</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6352</v>
+        <v>0.2887</v>
       </c>
       <c r="N18" t="n">
-        <v>98</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -1278,22 +1278,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7653</v>
+        <v>0.6698</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2944</v>
+        <v>0.2576</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2758</v>
+        <v>-0.3146</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7653</v>
+        <v>0.6698</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7653</v>
+        <v>0.7647</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6016</v>
+        <v>0.6011</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>61</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6016</v>
+        <v>0.6011</v>
       </c>
       <c r="N19" t="n">
         <v>61</v>
@@ -1320,26 +1320,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.467</v>
+        <v>0.6663</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1796</v>
+        <v>0.2563</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4116</v>
+        <v>-0.3162</v>
       </c>
       <c r="E20" t="n">
-        <v>0.467</v>
+        <v>0.6663</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.467</v>
+        <v>0.3815</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,19 +1348,19 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3671</v>
+        <v>0.2999</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3671</v>
+        <v>0.2999</v>
       </c>
       <c r="N20" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21">
@@ -1370,22 +1370,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4122</v>
+        <v>0.6611</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1586</v>
+        <v>0.2543</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4366</v>
+        <v>-0.3185</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4122</v>
+        <v>0.6611</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4122</v>
+        <v>0.4126</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.324</v>
+        <v>0.3243</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>51</v>
       </c>
       <c r="M21" t="n">
-        <v>0.324</v>
+        <v>0.3243</v>
       </c>
       <c r="N21" t="n">
         <v>51</v>
@@ -1412,26 +1412,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3811</v>
+        <v>0.5544</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1466</v>
+        <v>0.2133</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4507</v>
+        <v>-0.3662</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3811</v>
+        <v>0.5544</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3811</v>
+        <v>0.8081</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,44 +1440,44 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2996</v>
+        <v>0.6352</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2996</v>
+        <v>0.6352</v>
       </c>
       <c r="N22" t="n">
-        <v>51</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3755</v>
+        <v>0.5384</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1444</v>
+        <v>0.2071</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4533</v>
+        <v>-0.3733</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3755</v>
+        <v>0.5384</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3755</v>
+        <v>0.4797</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,44 +1486,44 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2952</v>
+        <v>0.3771</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2952</v>
+        <v>0.3771</v>
       </c>
       <c r="N23" t="n">
-        <v>105</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>hypex</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3675</v>
+        <v>0.4598</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1414</v>
+        <v>0.1769</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4569</v>
+        <v>-0.4084</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3675</v>
+        <v>0.4598</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3675</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,44 +1532,44 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2889</v>
+        <v>0.0561</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2889</v>
+        <v>0.0561</v>
       </c>
       <c r="N24" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3621</v>
+        <v>0.3918</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1393</v>
+        <v>0.1507</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4594</v>
+        <v>-0.4388</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3621</v>
+        <v>0.3918</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3621</v>
+        <v>0.3755</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,44 +1578,44 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2846</v>
+        <v>0.2952</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2846</v>
+        <v>0.2952</v>
       </c>
       <c r="N25" t="n">
-        <v>61</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>nilo</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3267</v>
+        <v>0.2558</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1257</v>
+        <v>0.0984</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4755</v>
+        <v>-0.4996</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3267</v>
+        <v>0.2558</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3267</v>
+        <v>0.1547</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,44 +1624,44 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2568</v>
+        <v>0.1216</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>180</v>
+        <v>53</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2568</v>
+        <v>0.1216</v>
       </c>
       <c r="N26" t="n">
-        <v>180</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>Chr1zN</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2833</v>
+        <v>0.252</v>
       </c>
       <c r="C27" t="n">
-        <v>0.109</v>
+        <v>0.0969</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4952</v>
+        <v>-0.5013</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2833</v>
+        <v>0.252</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2833</v>
+        <v>0.2119</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,44 +1670,44 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2227</v>
+        <v>0.1666</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2227</v>
+        <v>0.1666</v>
       </c>
       <c r="N27" t="n">
-        <v>98</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Chr1zN</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2122</v>
+        <v>0.2442</v>
       </c>
       <c r="C28" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0939</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5276</v>
+        <v>-0.5047</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2122</v>
+        <v>0.2442</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2122</v>
+        <v>0.3615</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,44 +1716,44 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1668</v>
+        <v>0.2842</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1668</v>
+        <v>0.2842</v>
       </c>
       <c r="N28" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>nilo</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1438</v>
+        <v>0.131</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0553</v>
+        <v>0.0504</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5587</v>
+        <v>-0.5553</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1438</v>
+        <v>0.131</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1438</v>
+        <v>0.2833</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,44 +1762,44 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.113</v>
+        <v>0.2227</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="M29" t="n">
-        <v>0.113</v>
+        <v>0.2227</v>
       </c>
       <c r="N29" t="n">
-        <v>53</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>hypex</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.019</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0275</v>
+        <v>0.0073</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5917</v>
+        <v>-0.6052999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.019</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.07140000000000001</v>
+        <v>-0.0228</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,44 +1808,44 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0561</v>
+        <v>-0.0179</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0561</v>
+        <v>-0.0179</v>
       </c>
       <c r="N30" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0232</v>
+        <v>-0.0048</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0089</v>
+        <v>-0.0018</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6348</v>
+        <v>-0.616</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0232</v>
+        <v>-0.0048</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.0232</v>
+        <v>0.3495</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,44 +1854,44 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.0182</v>
+        <v>0.2747</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>51</v>
+        <v>180</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0182</v>
+        <v>0.2747</v>
       </c>
       <c r="N31" t="n">
-        <v>51</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>yxngstxr</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1519</v>
+        <v>-0.2463</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0584</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6934</v>
+        <v>-0.7238</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1519</v>
+        <v>-0.2463</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.1519</v>
+        <v>-0.2988</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,44 +1900,44 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.1194</v>
+        <v>-0.2349</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1194</v>
+        <v>-0.2349</v>
       </c>
       <c r="N32" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yxngstxr</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2986</v>
+        <v>-0.4266</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1149</v>
+        <v>-0.1641</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7601</v>
+        <v>-0.8044</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2986</v>
+        <v>-0.4266</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.2986</v>
+        <v>-0.1515</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,44 +1946,44 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.2347</v>
+        <v>-0.1191</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.2347</v>
+        <v>-0.1191</v>
       </c>
       <c r="N33" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tauson</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5576</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2145</v>
+        <v>-0.2786</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.878</v>
+        <v>-0.9373</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5576</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.5576</v>
+        <v>-0.5975</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.4383</v>
+        <v>-0.4697</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4383</v>
+        <v>-0.4697</v>
       </c>
       <c r="N34" t="n">
         <v>46</v>
@@ -2010,26 +2010,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>Tauson</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5975</v>
+        <v>-0.7631</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2298</v>
+        <v>-0.2935</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8962</v>
+        <v>-0.9547</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5975</v>
+        <v>-0.7631</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.5975</v>
+        <v>-0.5576</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.4697</v>
+        <v>-0.4383</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>46</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.4697</v>
+        <v>-0.4383</v>
       </c>
       <c r="N35" t="n">
         <v>46</v>
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7924</v>
+        <v>-0.9967</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3048</v>
+        <v>-0.3834</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9849</v>
+        <v>-1.059</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7924</v>
+        <v>-0.9967</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -2102,26 +2102,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8133</v>
+        <v>-1.0991</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3128</v>
+        <v>-0.4228</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9944</v>
+        <v>-1.1048</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8133</v>
+        <v>-1.0991</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.8133</v>
+        <v>-0.8353</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2130,44 +2130,44 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.6393</v>
+        <v>-0.6566</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.6393</v>
+        <v>-0.6566</v>
       </c>
       <c r="N37" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.8353</v>
+        <v>-1.1086</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3213</v>
+        <v>-0.4264</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0044</v>
+        <v>-1.109</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.8353</v>
+        <v>-1.1086</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.8353</v>
+        <v>-0.8133</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2176,44 +2176,44 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.6566</v>
+        <v>-0.6393</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.6566</v>
+        <v>-0.6393</v>
       </c>
       <c r="N38" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>susp</t>
+          <t>NucleonZ</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.8975</v>
+        <v>-1.1976</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3452</v>
+        <v>-0.4607</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0328</v>
+        <v>-1.1488</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.8975</v>
+        <v>-1.1976</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.8975</v>
+        <v>-1.172</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2222,44 +2222,44 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.7055</v>
+        <v>-0.9213</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>53</v>
+        <v>180</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.7055</v>
+        <v>-0.9213</v>
       </c>
       <c r="N39" t="n">
-        <v>53</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>susp</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.1269</v>
+        <v>-1.204</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4335</v>
+        <v>-0.4631</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1372</v>
+        <v>-1.1516</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.1269</v>
+        <v>-1.204</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.1269</v>
+        <v>-0.8976</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2268,44 +2268,44 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.8858</v>
+        <v>-0.7056</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.8858</v>
+        <v>-0.7056</v>
       </c>
       <c r="N40" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NucleonZ</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.172</v>
+        <v>-1.4023</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4508</v>
+        <v>-0.5394</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1577</v>
+        <v>-1.2402</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.172</v>
+        <v>-1.4023</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.172</v>
+        <v>-1.1376</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2314,19 +2314,19 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9213</v>
+        <v>-0.8942</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.9213</v>
+        <v>-0.8942</v>
       </c>
       <c r="N41" t="n">
-        <v>180</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -2426,13 +2426,13 @@
         <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3398</v>
+        <v>0.3577</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4756</v>
+        <v>7.8694</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.14</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3398</v>
+        <v>0.3393</v>
       </c>
       <c r="J3" t="n">
-        <v>7.4756</v>
+        <v>7.4646</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.99</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0221</v>
+        <v>-0.0222</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4862</v>
+        <v>-0.4884</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2376</v>
+        <v>-0.2378</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.2272</v>
+        <v>-5.2316</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.66</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3794</v>
+        <v>-0.3796</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.3468</v>
+        <v>-8.3512</v>
       </c>
     </row>
     <row r="7">
@@ -2626,13 +2626,13 @@
         <v>22</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6421</v>
+        <v>1.6296</v>
       </c>
       <c r="J7" t="n">
-        <v>36.1262</v>
+        <v>35.8512</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.13</v>
       </c>
       <c r="I8" t="n">
-        <v>0.387</v>
+        <v>0.3873</v>
       </c>
       <c r="J8" t="n">
-        <v>8.513999999999999</v>
+        <v>8.5206</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1392</v>
+        <v>0.1395</v>
       </c>
       <c r="J9" t="n">
-        <v>3.0624</v>
+        <v>3.069</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.02</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0694</v>
       </c>
       <c r="J10" t="n">
-        <v>1.518</v>
+        <v>1.5268</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.97</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1701</v>
+        <v>-0.1697</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.7422</v>
+        <v>-3.7334</v>
       </c>
     </row>
     <row r="12">
@@ -6629,10 +6629,10 @@
         <v>1.14</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3482</v>
+        <v>0.3477</v>
       </c>
       <c r="J107" t="n">
-        <v>7.3122</v>
+        <v>7.3017</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0117</v>
+        <v>0.0113</v>
       </c>
       <c r="J108" t="n">
-        <v>0.2457</v>
+        <v>0.2373</v>
       </c>
     </row>
     <row r="109">
@@ -6706,13 +6706,13 @@
         <v>21</v>
       </c>
       <c r="H109" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2144</v>
+        <v>-0.2044</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.5024</v>
+        <v>-4.2924</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.83</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2144</v>
+        <v>-0.2146</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.5024</v>
+        <v>-4.5066</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.78</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2641</v>
+        <v>-0.2643</v>
       </c>
       <c r="J111" t="n">
-        <v>-5.5461</v>
+        <v>-5.5503</v>
       </c>
     </row>
     <row r="112">
@@ -8029,10 +8029,10 @@
         <v>0.71</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.3053</v>
+        <v>-0.3056</v>
       </c>
       <c r="J142" t="n">
-        <v>-4.5795</v>
+        <v>-4.584</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.7</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.3145</v>
+        <v>-0.3147</v>
       </c>
       <c r="J143" t="n">
-        <v>-4.7175</v>
+        <v>-4.7205</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.68</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3324</v>
+        <v>-0.3326</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.986</v>
+        <v>-4.989</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.66</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3493</v>
+        <v>-0.3494</v>
       </c>
       <c r="J145" t="n">
-        <v>-5.2395</v>
+        <v>-5.241</v>
       </c>
     </row>
     <row r="146">
@@ -8186,13 +8186,13 @@
         <v>15</v>
       </c>
       <c r="H146" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4105</v>
+        <v>-0.4019</v>
       </c>
       <c r="J146" t="n">
-        <v>-6.1575</v>
+        <v>-6.0285</v>
       </c>
     </row>
     <row r="147">
@@ -9229,10 +9229,10 @@
         <v>0.97</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.047</v>
+        <v>-0.0467</v>
       </c>
       <c r="J172" t="n">
-        <v>-0.987</v>
+        <v>-0.9807</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.97</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.047</v>
+        <v>-0.0467</v>
       </c>
       <c r="J173" t="n">
-        <v>-0.987</v>
+        <v>-0.9807</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.96</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0617</v>
+        <v>-0.0614</v>
       </c>
       <c r="J174" t="n">
-        <v>-1.2957</v>
+        <v>-1.2894</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.95</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0756</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="J175" t="n">
-        <v>-1.5876</v>
+        <v>-1.5813</v>
       </c>
     </row>
     <row r="176">
@@ -9386,13 +9386,13 @@
         <v>21</v>
       </c>
       <c r="H176" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5291</v>
+        <v>-0.5375</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.1111</v>
+        <v>-11.2875</v>
       </c>
     </row>
     <row r="177">

--- a/database/event/8246/event_8246_evp_summary.xlsx
+++ b/database/event/8246/event_8246_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.3738</v>
+        <v>5.3189</v>
       </c>
       <c r="C2" t="n">
-        <v>2.067</v>
+        <v>2.0459</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7865</v>
+        <v>1.8172</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3738</v>
+        <v>5.3189</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>5.122</v>
+        <v>5.0671</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0262</v>
+        <v>4.0061</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>180</v>
       </c>
       <c r="M2" t="n">
-        <v>4.0262</v>
+        <v>4.0061</v>
       </c>
       <c r="N2" t="n">
         <v>180</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.1732</v>
+        <v>4.1913</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6052</v>
+        <v>1.6122</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2503</v>
+        <v>1.3035</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1732</v>
+        <v>4.1913</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4.02</v>
+        <v>4.0381</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3.16</v>
+        <v>3.1926</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>180</v>
       </c>
       <c r="M3" t="n">
-        <v>3.16</v>
+        <v>3.1926</v>
       </c>
       <c r="N3" t="n">
         <v>180</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.9035</v>
+        <v>3.8887</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5015</v>
+        <v>1.4958</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1298</v>
+        <v>1.1657</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9035</v>
+        <v>3.8887</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8193</v>
+        <v>3.8045</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0022</v>
+        <v>3.0079</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>176</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0022</v>
+        <v>3.0079</v>
       </c>
       <c r="N4" t="n">
         <v>176</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.3955</v>
+        <v>3.2954</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3061</v>
+        <v>1.2676</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9029</v>
+        <v>0.8954</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3955</v>
+        <v>3.2954</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3899</v>
+        <v>3.2898</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6647</v>
+        <v>2.601</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>176</v>
       </c>
       <c r="M5" t="n">
-        <v>2.6647</v>
+        <v>2.601</v>
       </c>
       <c r="N5" t="n">
         <v>176</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.259</v>
+        <v>3.2922</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2536</v>
+        <v>1.2664</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8419</v>
+        <v>0.894</v>
       </c>
       <c r="E6" t="n">
-        <v>3.259</v>
+        <v>3.2922</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3.0203</v>
+        <v>3.0535</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3742</v>
+        <v>2.4142</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>98</v>
       </c>
       <c r="M6" t="n">
-        <v>2.3742</v>
+        <v>2.4142</v>
       </c>
       <c r="N6" t="n">
         <v>98</v>
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.5883</v>
+        <v>2.4372</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9956</v>
+        <v>0.9375</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5423</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5883</v>
+        <v>2.4372</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.417</v>
+        <v>2.2659</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8999</v>
+        <v>1.7914</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>98</v>
       </c>
       <c r="M7" t="n">
-        <v>1.8999</v>
+        <v>1.7914</v>
       </c>
       <c r="N7" t="n">
         <v>98</v>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.3818</v>
+        <v>2.3613</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9162</v>
+        <v>0.9083</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4501</v>
+        <v>0.4699</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3818</v>
+        <v>2.3613</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4</v>
+        <v>2.3795</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8866</v>
+        <v>1.8813</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>176</v>
       </c>
       <c r="M8" t="n">
-        <v>1.8866</v>
+        <v>1.8813</v>
       </c>
       <c r="N8" t="n">
         <v>176</v>
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2597</v>
+        <v>2.2806</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8692</v>
+        <v>0.8772</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3955</v>
+        <v>0.4331</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2597</v>
+        <v>2.2806</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2315</v>
+        <v>2.2524</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7541</v>
+        <v>1.7808</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>176</v>
       </c>
       <c r="M9" t="n">
-        <v>1.7541</v>
+        <v>1.7808</v>
       </c>
       <c r="N9" t="n">
         <v>176</v>
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.018</v>
+        <v>1.8749</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7762</v>
+        <v>0.7212</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2876</v>
+        <v>0.2483</v>
       </c>
       <c r="E10" t="n">
-        <v>2.018</v>
+        <v>1.8749</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.0684</v>
+        <v>1.9253</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6259</v>
+        <v>1.5222</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>180</v>
       </c>
       <c r="M10" t="n">
-        <v>1.6259</v>
+        <v>1.5222</v>
       </c>
       <c r="N10" t="n">
         <v>180</v>
@@ -910,22 +910,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.7747</v>
+        <v>1.6722</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6826</v>
+        <v>0.6432</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1789</v>
+        <v>0.156</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7747</v>
+        <v>1.6722</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6058</v>
+        <v>1.5033</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2623</v>
+        <v>1.1885</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>105</v>
       </c>
       <c r="M11" t="n">
-        <v>1.2623</v>
+        <v>1.1885</v>
       </c>
       <c r="N11" t="n">
         <v>105</v>
@@ -956,22 +956,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7697</v>
+        <v>1.6135</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6807</v>
+        <v>0.6206</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1767</v>
+        <v>0.1292</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7697</v>
+        <v>1.6135</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8621</v>
+        <v>1.7059</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4637</v>
+        <v>1.3487</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>105</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4637</v>
+        <v>1.3487</v>
       </c>
       <c r="N12" t="n">
         <v>105</v>
@@ -1002,22 +1002,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.7267</v>
+        <v>1.6092</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6642</v>
+        <v>0.619</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1575</v>
+        <v>0.1273</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7267</v>
+        <v>1.6092</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4335</v>
+        <v>1.316</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1268</v>
+        <v>1.0405</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>46</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1268</v>
+        <v>1.0405</v>
       </c>
       <c r="N13" t="n">
         <v>46</v>
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.2979</v>
+        <v>1.2168</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4992</v>
+        <v>0.468</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0341</v>
+        <v>-0.0515</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2979</v>
+        <v>1.2168</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2734</v>
+        <v>1.1923</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.001</v>
+        <v>0.9426</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>53</v>
       </c>
       <c r="M14" t="n">
-        <v>1.001</v>
+        <v>0.9426</v>
       </c>
       <c r="N14" t="n">
         <v>53</v>
@@ -1094,22 +1094,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.1408</v>
+        <v>1.136</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4388</v>
+        <v>0.437</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1042</v>
+        <v>-0.0883</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1408</v>
+        <v>1.136</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1082</v>
+        <v>1.1034</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8711</v>
+        <v>0.8724</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>105</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8711</v>
+        <v>0.8724</v>
       </c>
       <c r="N15" t="n">
         <v>105</v>
@@ -1140,22 +1140,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9509</v>
+        <v>0.8692</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3658</v>
+        <v>0.3343</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1891</v>
+        <v>-0.2098</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9509</v>
+        <v>0.8692</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8494</v>
+        <v>0.7677</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6677</v>
+        <v>0.607</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>61</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6677</v>
+        <v>0.607</v>
       </c>
       <c r="N16" t="n">
         <v>61</v>
@@ -1186,22 +1186,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.7855</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3302</v>
+        <v>0.3021</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2304</v>
+        <v>-0.248</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.7855</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9367</v>
+        <v>0.8638</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7363</v>
+        <v>0.6829</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>176</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7363</v>
+        <v>0.6829</v>
       </c>
       <c r="N17" t="n">
         <v>176</v>
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.747</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2926</v>
+        <v>0.2873</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2741</v>
+        <v>-0.2655</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.747</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3673</v>
+        <v>0.3537</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2887</v>
+        <v>0.2797</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>61</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2887</v>
+        <v>0.2797</v>
       </c>
       <c r="N18" t="n">
         <v>61</v>
@@ -1274,26 +1274,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6698</v>
+        <v>0.6059</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2576</v>
+        <v>0.2331</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3146</v>
+        <v>-0.3298</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6698</v>
+        <v>0.6059</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7647</v>
+        <v>0.3211</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,44 +1302,44 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6011</v>
+        <v>0.2538</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6011</v>
+        <v>0.2538</v>
       </c>
       <c r="N19" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6663</v>
+        <v>0.6006</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2563</v>
+        <v>0.231</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3162</v>
+        <v>-0.3322</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6663</v>
+        <v>0.6006</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3815</v>
+        <v>0.3521</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2999</v>
+        <v>0.2784</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>51</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2999</v>
+        <v>0.2784</v>
       </c>
       <c r="N20" t="n">
         <v>51</v>
@@ -1366,26 +1366,26 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6611</v>
+        <v>0.581</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2543</v>
+        <v>0.2235</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3185</v>
+        <v>-0.3411</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6611</v>
+        <v>0.581</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4126</v>
+        <v>0.8347</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,44 +1394,44 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3243</v>
+        <v>0.6599</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3243</v>
+        <v>0.6599</v>
       </c>
       <c r="N21" t="n">
-        <v>51</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5544</v>
+        <v>0.547</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2133</v>
+        <v>0.2104</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3662</v>
+        <v>-0.3566</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5544</v>
+        <v>0.547</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8081</v>
+        <v>0.6419</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,19 +1440,19 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6352</v>
+        <v>0.5075</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6352</v>
+        <v>0.5075</v>
       </c>
       <c r="N22" t="n">
-        <v>98</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23">
@@ -1462,22 +1462,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5384</v>
+        <v>0.4988</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2071</v>
+        <v>0.1919</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3733</v>
+        <v>-0.3786</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5384</v>
+        <v>0.4988</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4797</v>
+        <v>0.4401</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3771</v>
+        <v>0.348</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>61</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3771</v>
+        <v>0.348</v>
       </c>
       <c r="N23" t="n">
         <v>61</v>
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4598</v>
+        <v>0.4363</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1769</v>
+        <v>0.1678</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4084</v>
+        <v>-0.407</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4598</v>
+        <v>0.4363</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0479</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0561</v>
+        <v>0.0378</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>46</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0561</v>
+        <v>0.0378</v>
       </c>
       <c r="N24" t="n">
         <v>46</v>
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3918</v>
+        <v>0.4265</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1507</v>
+        <v>0.1641</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4388</v>
+        <v>-0.4115</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3918</v>
+        <v>0.4265</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3755</v>
+        <v>0.4102</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2952</v>
+        <v>0.3243</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>105</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2952</v>
+        <v>0.3243</v>
       </c>
       <c r="N25" t="n">
         <v>105</v>
@@ -1600,22 +1600,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2558</v>
+        <v>0.232</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0984</v>
+        <v>0.0892</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4996</v>
+        <v>-0.5001</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2558</v>
+        <v>0.232</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1547</v>
+        <v>0.1309</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1216</v>
+        <v>0.1035</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>53</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1216</v>
+        <v>0.1035</v>
       </c>
       <c r="N26" t="n">
         <v>53</v>
@@ -1642,26 +1642,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Chr1zN</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.252</v>
+        <v>0.1869</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0969</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5013</v>
+        <v>-0.5206</v>
       </c>
       <c r="E27" t="n">
-        <v>0.252</v>
+        <v>0.1869</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2119</v>
+        <v>0.3042</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,44 +1670,44 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1666</v>
+        <v>0.2405</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1666</v>
+        <v>0.2405</v>
       </c>
       <c r="N27" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2442</v>
+        <v>0.1702</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0939</v>
+        <v>0.0655</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5047</v>
+        <v>-0.5283</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2442</v>
+        <v>0.1702</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3615</v>
+        <v>0.3225</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,44 +1716,44 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2842</v>
+        <v>0.2549</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2842</v>
+        <v>0.2549</v>
       </c>
       <c r="N28" t="n">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>Chr1zN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.131</v>
+        <v>0.1499</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0504</v>
+        <v>0.0577</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5553</v>
+        <v>-0.5375</v>
       </c>
       <c r="E29" t="n">
-        <v>0.131</v>
+        <v>0.1499</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2833</v>
+        <v>0.1098</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,19 +1762,19 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2227</v>
+        <v>0.0868</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2227</v>
+        <v>0.0868</v>
       </c>
       <c r="N29" t="n">
-        <v>98</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30">
@@ -1784,22 +1784,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.019</v>
+        <v>0.0151</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0073</v>
+        <v>0.0058</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6052999999999999</v>
+        <v>-0.5989</v>
       </c>
       <c r="E30" t="n">
-        <v>0.019</v>
+        <v>0.0151</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0228</v>
+        <v>-0.0267</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.0179</v>
+        <v>-0.0211</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>51</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0179</v>
+        <v>-0.0211</v>
       </c>
       <c r="N30" t="n">
         <v>51</v>
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0048</v>
+        <v>-0.1995</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0018</v>
+        <v>-0.0767</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.616</v>
+        <v>-0.6967</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0048</v>
+        <v>-0.1995</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3495</v>
+        <v>0.1548</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.2747</v>
+        <v>0.1224</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>180</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2747</v>
+        <v>0.1224</v>
       </c>
       <c r="N31" t="n">
         <v>180</v>
@@ -1876,22 +1876,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2463</v>
+        <v>-0.2833</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.109</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7238</v>
+        <v>-0.7348</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2463</v>
+        <v>-0.2833</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.2988</v>
+        <v>-0.3358</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.2349</v>
+        <v>-0.2655</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>53</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2349</v>
+        <v>-0.2655</v>
       </c>
       <c r="N32" t="n">
         <v>53</v>
@@ -1922,22 +1922,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4266</v>
+        <v>-0.3958</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1641</v>
+        <v>-0.1522</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8044</v>
+        <v>-0.7861</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4266</v>
+        <v>-0.3958</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.1515</v>
+        <v>-0.1207</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.1191</v>
+        <v>-0.0954</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>51</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.1191</v>
+        <v>-0.0954</v>
       </c>
       <c r="N33" t="n">
         <v>51</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2786</v>
+        <v>-0.2615</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9373</v>
+        <v>-0.9155</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.5975</v>
+        <v>-0.5531</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.4697</v>
+        <v>-0.4373</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4697</v>
+        <v>-0.4373</v>
       </c>
       <c r="N34" t="n">
         <v>46</v>
@@ -2014,22 +2014,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7631</v>
+        <v>-0.7118</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2935</v>
+        <v>-0.2738</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9547</v>
+        <v>-0.93</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7631</v>
+        <v>-0.7118</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.5576</v>
+        <v>-0.5063</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.4383</v>
+        <v>-0.4003</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>46</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.4383</v>
+        <v>-0.4003</v>
       </c>
       <c r="N35" t="n">
         <v>46</v>
@@ -2060,22 +2060,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9967</v>
+        <v>-0.9523</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3834</v>
+        <v>-0.3663</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.059</v>
+        <v>-1.0396</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9967</v>
+        <v>-0.9523</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.7924</v>
+        <v>-0.748</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.6229</v>
+        <v>-0.5914</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>46</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6229</v>
+        <v>-0.5914</v>
       </c>
       <c r="N36" t="n">
         <v>46</v>
@@ -2102,26 +2102,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0991</v>
+        <v>-1.0204</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4228</v>
+        <v>-0.3925</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1048</v>
+        <v>-1.0706</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0991</v>
+        <v>-1.0204</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.8353</v>
+        <v>-0.7251</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2130,44 +2130,44 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.6566</v>
+        <v>-0.5733</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.6566</v>
+        <v>-0.5733</v>
       </c>
       <c r="N37" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1086</v>
+        <v>-1.0236</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4264</v>
+        <v>-0.3937</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.109</v>
+        <v>-1.0721</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1086</v>
+        <v>-1.0236</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.8133</v>
+        <v>-0.7598</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2176,19 +2176,19 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.6393</v>
+        <v>-0.6007</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.6393</v>
+        <v>-0.6007</v>
       </c>
       <c r="N38" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39">
@@ -2198,22 +2198,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1976</v>
+        <v>-1.0572</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4607</v>
+        <v>-0.4067</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1488</v>
+        <v>-1.0874</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1976</v>
+        <v>-1.0572</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.172</v>
+        <v>-1.0316</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.9213</v>
+        <v>-0.8156</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>180</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9213</v>
+        <v>-0.8156</v>
       </c>
       <c r="N39" t="n">
         <v>180</v>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.204</v>
+        <v>-1.1818</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4631</v>
+        <v>-0.4546</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1516</v>
+        <v>-1.1442</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.204</v>
+        <v>-1.1818</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.8976</v>
+        <v>-0.8754</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.7056</v>
+        <v>-0.6921</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>53</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.7056</v>
+        <v>-0.6921</v>
       </c>
       <c r="N40" t="n">
         <v>53</v>
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.4023</v>
+        <v>-1.3845</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5394</v>
+        <v>-0.5326</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2402</v>
+        <v>-1.2365</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.4023</v>
+        <v>-1.3845</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.1376</v>
+        <v>-1.1198</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.8942</v>
+        <v>-0.8853</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>51</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.8942</v>
+        <v>-0.8853</v>
       </c>
       <c r="N41" t="n">
         <v>51</v>
@@ -2429,10 +2429,10 @@
         <v>1.15</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3577</v>
+        <v>0.3036</v>
       </c>
       <c r="J2" t="n">
-        <v>7.8694</v>
+        <v>6.6792</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.14</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3393</v>
+        <v>0.2861</v>
       </c>
       <c r="J3" t="n">
-        <v>7.4646</v>
+        <v>6.2942</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.99</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0222</v>
+        <v>-0.0165</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4884</v>
+        <v>-0.363</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2378</v>
+        <v>-0.2177</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.2316</v>
+        <v>-4.7894</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.66</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3796</v>
+        <v>-0.367</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.3512</v>
+        <v>-8.074</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.79</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6296</v>
+        <v>1.6622</v>
       </c>
       <c r="J7" t="n">
-        <v>35.8512</v>
+        <v>36.5684</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.13</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3873</v>
+        <v>0.3527</v>
       </c>
       <c r="J8" t="n">
-        <v>8.5206</v>
+        <v>7.7594</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1395</v>
+        <v>0.1158</v>
       </c>
       <c r="J9" t="n">
-        <v>3.069</v>
+        <v>2.5476</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.02</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0694</v>
+        <v>0.0532</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5268</v>
+        <v>1.1704</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.97</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1697</v>
+        <v>-0.1383</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.7334</v>
+        <v>-3.0426</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.35</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6998</v>
+        <v>0.6473</v>
       </c>
       <c r="J12" t="n">
-        <v>16.7952</v>
+        <v>15.5352</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.95</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.0679</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.9584</v>
+        <v>-1.6296</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.87</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1738</v>
+        <v>-0.1542</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.1712</v>
+        <v>-3.7008</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.85</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1949</v>
+        <v>-0.1749</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.6776</v>
+        <v>-4.1976</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.62</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4133</v>
+        <v>-0.4037</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.9192</v>
+        <v>-9.688800000000001</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.47</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1263</v>
+        <v>1.1349</v>
       </c>
       <c r="J17" t="n">
-        <v>27.0312</v>
+        <v>27.2376</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.28</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7423</v>
+        <v>0.7114</v>
       </c>
       <c r="J18" t="n">
-        <v>17.8152</v>
+        <v>17.0736</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.99</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0703</v>
+        <v>-0.0509</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.6872</v>
+        <v>-1.2216</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.84</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5078</v>
+        <v>-0.4662</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.1872</v>
+        <v>-11.1888</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.78</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6478</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-15.5472</v>
+        <v>-14.6976</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.4</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7615</v>
+        <v>0.7095</v>
       </c>
       <c r="J22" t="n">
-        <v>18.276</v>
+        <v>17.028</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.22</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4752</v>
+        <v>0.4171</v>
       </c>
       <c r="J23" t="n">
-        <v>11.4048</v>
+        <v>10.0104</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.79</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2595</v>
+        <v>-0.2398</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.228</v>
+        <v>-5.7552</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.78</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2693</v>
+        <v>-0.2499</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.4632</v>
+        <v>-5.9976</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.66</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3814</v>
+        <v>-0.3691</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.153600000000001</v>
+        <v>-8.8584</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.51</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1852</v>
+        <v>1.2001</v>
       </c>
       <c r="J27" t="n">
-        <v>28.4448</v>
+        <v>28.8024</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.37</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9137</v>
+        <v>0.8968</v>
       </c>
       <c r="J28" t="n">
-        <v>21.9288</v>
+        <v>21.5232</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0189</v>
+        <v>-0.014</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.4536</v>
+        <v>-0.336</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.99</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0581</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.8888</v>
+        <v>-1.3944</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.72</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7887</v>
+        <v>-0.765</v>
       </c>
       <c r="J31" t="n">
-        <v>-18.9288</v>
+        <v>-18.36</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.51</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9623</v>
+        <v>0.9487</v>
       </c>
       <c r="J32" t="n">
-        <v>20.2083</v>
+        <v>19.9227</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.36</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7532</v>
+        <v>0.7391</v>
       </c>
       <c r="J33" t="n">
-        <v>15.8172</v>
+        <v>15.5211</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.34</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7244</v>
+        <v>0.7109</v>
       </c>
       <c r="J34" t="n">
-        <v>15.2124</v>
+        <v>14.9289</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.25</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5914</v>
+        <v>0.5835</v>
       </c>
       <c r="J35" t="n">
-        <v>12.4194</v>
+        <v>12.2535</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.74</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7655</v>
+        <v>-0.7432</v>
       </c>
       <c r="J36" t="n">
-        <v>-16.0755</v>
+        <v>-15.6072</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.11</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2978</v>
+        <v>0.2484</v>
       </c>
       <c r="J37" t="n">
-        <v>6.2538</v>
+        <v>5.2164</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.96</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0645</v>
+        <v>-0.0531</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.3545</v>
+        <v>-1.1151</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.86</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1813</v>
+        <v>-0.1622</v>
       </c>
       <c r="J39" t="n">
-        <v>-3.8073</v>
+        <v>-3.4062</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.8</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.242</v>
+        <v>-0.2224</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.082</v>
+        <v>-4.6704</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.72</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3186</v>
+        <v>-0.3015</v>
       </c>
       <c r="J41" t="n">
-        <v>-6.6906</v>
+        <v>-6.3315</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.2</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5352</v>
+        <v>0.5231</v>
       </c>
       <c r="J42" t="n">
-        <v>12.8448</v>
+        <v>12.5544</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.16</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4667</v>
+        <v>0.4355</v>
       </c>
       <c r="J43" t="n">
-        <v>11.2008</v>
+        <v>10.452</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.11</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3545</v>
+        <v>0.3145</v>
       </c>
       <c r="J44" t="n">
-        <v>8.507999999999999</v>
+        <v>7.548</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.01</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0502</v>
+        <v>0.0378</v>
       </c>
       <c r="J45" t="n">
-        <v>1.2048</v>
+        <v>0.9072</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.84</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5063</v>
+        <v>-0.4645</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.1512</v>
+        <v>-11.148</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.34</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6127</v>
+        <v>0.5856</v>
       </c>
       <c r="J47" t="n">
-        <v>14.7048</v>
+        <v>14.0544</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.24</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4934</v>
+        <v>0.4546</v>
       </c>
       <c r="J48" t="n">
-        <v>11.8416</v>
+        <v>10.9104</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2384</v>
+        <v>-0.2182</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.7216</v>
+        <v>-5.2368</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.72</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3251</v>
+        <v>-0.3085</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.8024</v>
+        <v>-7.404</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.67</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3711</v>
+        <v>-0.3578</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.9064</v>
+        <v>-8.587199999999999</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.49</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7851</v>
+        <v>0.7543</v>
       </c>
       <c r="J52" t="n">
-        <v>18.0573</v>
+        <v>17.3489</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.23</v>
       </c>
       <c r="I53" t="n">
-        <v>0.484</v>
+        <v>0.4424</v>
       </c>
       <c r="J53" t="n">
-        <v>11.132</v>
+        <v>10.1752</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.78</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2666</v>
+        <v>-0.2472</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.1318</v>
+        <v>-5.6856</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.67</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3698</v>
+        <v>-0.3563</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.5054</v>
+        <v>-8.194900000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.54</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4844</v>
+        <v>-0.4832</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.1412</v>
+        <v>-11.1136</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.49</v>
       </c>
       <c r="I57" t="n">
-        <v>0.956</v>
+        <v>0.9426</v>
       </c>
       <c r="J57" t="n">
-        <v>21.988</v>
+        <v>21.6798</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.36</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.7537</v>
       </c>
       <c r="J58" t="n">
-        <v>17.7031</v>
+        <v>17.3351</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.08</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2658</v>
+        <v>0.2333</v>
       </c>
       <c r="J59" t="n">
-        <v>6.1134</v>
+        <v>5.3659</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.97</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1614</v>
+        <v>-0.1299</v>
       </c>
       <c r="J60" t="n">
-        <v>-3.7122</v>
+        <v>-2.9877</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.82</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5691000000000001</v>
+        <v>-0.531</v>
       </c>
       <c r="J61" t="n">
-        <v>-13.0893</v>
+        <v>-12.213</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.93</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8517</v>
+        <v>0.7972</v>
       </c>
       <c r="J62" t="n">
-        <v>14.4789</v>
+        <v>13.5524</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.83</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7857</v>
+        <v>0.7345</v>
       </c>
       <c r="J63" t="n">
-        <v>13.3569</v>
+        <v>12.4865</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.3</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3985</v>
+        <v>0.3415</v>
       </c>
       <c r="J64" t="n">
-        <v>6.7745</v>
+        <v>5.8055</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.02</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0188</v>
+        <v>0.0075</v>
       </c>
       <c r="J65" t="n">
-        <v>0.3196</v>
+        <v>0.1275</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.95</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1161</v>
+        <v>-0.1012</v>
       </c>
       <c r="J66" t="n">
-        <v>-1.9737</v>
+        <v>-1.7204</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.32</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5059</v>
+        <v>0.5396</v>
       </c>
       <c r="J67" t="n">
-        <v>8.600300000000001</v>
+        <v>9.1732</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.89</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1483</v>
+        <v>-0.1312</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.5211</v>
+        <v>-2.2304</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.88</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1591</v>
+        <v>-0.1415</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.7047</v>
+        <v>-2.4055</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.63</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3985</v>
+        <v>-0.387</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.7745</v>
+        <v>-6.579</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.62</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4074</v>
+        <v>-0.3968</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.9258</v>
+        <v>-6.7456</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>0.0412</v>
+        <v>0.0356</v>
       </c>
       <c r="J72" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.6764</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.97</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0369</v>
+        <v>-0.0276</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.7010999999999999</v>
+        <v>-0.5244</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.83</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2052</v>
+        <v>-0.1882</v>
       </c>
       <c r="J74" t="n">
-        <v>-3.8988</v>
+        <v>-3.5758</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.64</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3821</v>
+        <v>-0.3692</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.2599</v>
+        <v>-7.0148</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4533</v>
+        <v>-0.4468</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.6127</v>
+        <v>-8.4892</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>2.18</v>
       </c>
       <c r="I77" t="n">
-        <v>1.7608</v>
+        <v>1.8099</v>
       </c>
       <c r="J77" t="n">
-        <v>33.4552</v>
+        <v>34.3881</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.57</v>
       </c>
       <c r="I78" t="n">
-        <v>1.0191</v>
+        <v>1.0085</v>
       </c>
       <c r="J78" t="n">
-        <v>19.3629</v>
+        <v>19.1615</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.17</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4488</v>
+        <v>0.4233</v>
       </c>
       <c r="J79" t="n">
-        <v>8.527200000000001</v>
+        <v>8.0427</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.14</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3831</v>
+        <v>0.3513</v>
       </c>
       <c r="J80" t="n">
-        <v>7.2789</v>
+        <v>6.6747</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.8</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6513</v>
+        <v>-0.6242</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.3747</v>
+        <v>-11.8598</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.2</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3493</v>
+        <v>0.3418</v>
       </c>
       <c r="J82" t="n">
-        <v>6.2874</v>
+        <v>6.1524</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.07</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1569</v>
+        <v>0.1396</v>
       </c>
       <c r="J83" t="n">
-        <v>2.8242</v>
+        <v>2.5128</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.88</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1651</v>
+        <v>-0.1454</v>
       </c>
       <c r="J84" t="n">
-        <v>-2.9718</v>
+        <v>-2.6172</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.82</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2279</v>
+        <v>-0.2076</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.1022</v>
+        <v>-3.7368</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2578</v>
+        <v>-0.2381</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.6404</v>
+        <v>-4.2858</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>2.11</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9092</v>
       </c>
       <c r="J87" t="n">
-        <v>17.4096</v>
+        <v>16.3656</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.53</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5794</v>
+        <v>0.5453</v>
       </c>
       <c r="J88" t="n">
-        <v>10.4292</v>
+        <v>9.8154</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.3</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3982</v>
+        <v>0.3413</v>
       </c>
       <c r="J89" t="n">
-        <v>7.1676</v>
+        <v>6.1434</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.22</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3072</v>
+        <v>0.2572</v>
       </c>
       <c r="J90" t="n">
-        <v>5.5296</v>
+        <v>4.6296</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.89</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1888</v>
+        <v>-0.1717</v>
       </c>
       <c r="J91" t="n">
-        <v>-3.3984</v>
+        <v>-3.0906</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.14</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4327</v>
+        <v>0.3929</v>
       </c>
       <c r="J92" t="n">
-        <v>9.519399999999999</v>
+        <v>8.643800000000001</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.11</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3599</v>
+        <v>0.3186</v>
       </c>
       <c r="J93" t="n">
-        <v>7.9178</v>
+        <v>7.0092</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.98</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1052</v>
+        <v>-0.0804</v>
       </c>
       <c r="J94" t="n">
-        <v>-2.3144</v>
+        <v>-1.7688</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.98</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1052</v>
+        <v>-0.0804</v>
       </c>
       <c r="J95" t="n">
-        <v>-2.3144</v>
+        <v>-1.7688</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.97</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1415</v>
+        <v>-0.112</v>
       </c>
       <c r="J96" t="n">
-        <v>-3.113</v>
+        <v>-2.464</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.32</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5750999999999999</v>
+        <v>0.5486</v>
       </c>
       <c r="J97" t="n">
-        <v>12.6522</v>
+        <v>12.0692</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.21</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4422</v>
+        <v>0.3881</v>
       </c>
       <c r="J98" t="n">
-        <v>9.728400000000001</v>
+        <v>8.5382</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.99</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0264</v>
+        <v>-0.0188</v>
       </c>
       <c r="J99" t="n">
-        <v>-0.5808</v>
+        <v>-0.4136</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.92</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1253</v>
+        <v>-0.1065</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.7566</v>
+        <v>-2.343</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.66</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3857</v>
+        <v>-0.3744</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.4854</v>
+        <v>-8.236800000000001</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.51</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9724</v>
+        <v>0.9591</v>
       </c>
       <c r="J102" t="n">
-        <v>20.4204</v>
+        <v>20.1411</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.28</v>
       </c>
       <c r="I103" t="n">
-        <v>0.642</v>
+        <v>0.6299</v>
       </c>
       <c r="J103" t="n">
-        <v>13.482</v>
+        <v>13.2279</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.16</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4519</v>
+        <v>0.4228</v>
       </c>
       <c r="J104" t="n">
-        <v>9.4899</v>
+        <v>8.8788</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.06</v>
       </c>
       <c r="I105" t="n">
-        <v>0.201</v>
+        <v>0.1728</v>
       </c>
       <c r="J105" t="n">
-        <v>4.221</v>
+        <v>3.6288</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.95</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2359</v>
+        <v>-0.1992</v>
       </c>
       <c r="J106" t="n">
-        <v>-4.9539</v>
+        <v>-4.1832</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.14</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3477</v>
+        <v>0.2946</v>
       </c>
       <c r="J107" t="n">
-        <v>7.3017</v>
+        <v>6.1866</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0113</v>
+        <v>0.0074</v>
       </c>
       <c r="J108" t="n">
-        <v>0.2373</v>
+        <v>0.1554</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.84</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2044</v>
+        <v>-0.1844</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.2924</v>
+        <v>-3.8724</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.83</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2146</v>
+        <v>-0.1946</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.5066</v>
+        <v>-4.0866</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.78</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2643</v>
+        <v>-0.2449</v>
       </c>
       <c r="J111" t="n">
-        <v>-5.5503</v>
+        <v>-5.1429</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.11</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2841</v>
+        <v>0.2347</v>
       </c>
       <c r="J112" t="n">
-        <v>6.2502</v>
+        <v>5.1634</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.97</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0549</v>
+        <v>-0.0439</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.2078</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.92</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1191</v>
+        <v>-0.1018</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.6202</v>
+        <v>-2.2396</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.89</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1533</v>
+        <v>-0.1341</v>
       </c>
       <c r="J115" t="n">
-        <v>-3.3726</v>
+        <v>-2.9502</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.82</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.227</v>
+        <v>-0.2068</v>
       </c>
       <c r="J116" t="n">
-        <v>-4.994</v>
+        <v>-4.5496</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.31</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6996</v>
+        <v>0.6843</v>
       </c>
       <c r="J117" t="n">
-        <v>15.3912</v>
+        <v>15.0546</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.28</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6536</v>
+        <v>0.6394</v>
       </c>
       <c r="J118" t="n">
-        <v>14.3792</v>
+        <v>14.0668</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.22</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5586</v>
+        <v>0.5485</v>
       </c>
       <c r="J119" t="n">
-        <v>12.2892</v>
+        <v>12.067</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.95</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2227</v>
+        <v>-0.1857</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.8994</v>
+        <v>-4.0854</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.84</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5171</v>
+        <v>-0.4764</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.3762</v>
+        <v>-10.4808</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.54</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8427</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="J122" t="n">
-        <v>20.2248</v>
+        <v>19.512</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.03</v>
       </c>
       <c r="I123" t="n">
-        <v>0.111</v>
+        <v>0.082</v>
       </c>
       <c r="J123" t="n">
-        <v>2.664</v>
+        <v>1.968</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.76</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.285</v>
+        <v>-0.2662</v>
       </c>
       <c r="J124" t="n">
-        <v>-6.84</v>
+        <v>-6.3888</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3506</v>
+        <v>-0.3355</v>
       </c>
       <c r="J125" t="n">
-        <v>-8.414400000000001</v>
+        <v>-8.052</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.64</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3959</v>
+        <v>-0.3846</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.5016</v>
+        <v>-9.230399999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.35</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7607</v>
+        <v>0.7446</v>
       </c>
       <c r="J127" t="n">
-        <v>18.2568</v>
+        <v>17.8704</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.34</v>
       </c>
       <c r="I128" t="n">
-        <v>0.7458</v>
+        <v>0.7298</v>
       </c>
       <c r="J128" t="n">
-        <v>17.8992</v>
+        <v>17.5152</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0186</v>
+        <v>-0.0136</v>
       </c>
       <c r="J129" t="n">
-        <v>-0.4464</v>
+        <v>-0.3264</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.98</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1197</v>
+        <v>-0.0927</v>
       </c>
       <c r="J130" t="n">
-        <v>-2.8728</v>
+        <v>-2.2248</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.91</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3378</v>
+        <v>-0.2958</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.107200000000001</v>
+        <v>-7.0992</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.74</v>
       </c>
       <c r="I132" t="n">
-        <v>0.7297</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="J132" t="n">
-        <v>11.6752</v>
+        <v>10.912</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.52</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5755</v>
+        <v>0.5411</v>
       </c>
       <c r="J133" t="n">
-        <v>9.208</v>
+        <v>8.6576</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.35</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4492</v>
+        <v>0.3926</v>
       </c>
       <c r="J134" t="n">
-        <v>7.1872</v>
+        <v>6.2816</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.19</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2747</v>
+        <v>0.2274</v>
       </c>
       <c r="J135" t="n">
-        <v>4.3952</v>
+        <v>3.6384</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.02</v>
       </c>
       <c r="I136" t="n">
-        <v>0.0223</v>
+        <v>0.011</v>
       </c>
       <c r="J136" t="n">
-        <v>0.3568</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.24</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4589</v>
+        <v>0.4889</v>
       </c>
       <c r="J137" t="n">
-        <v>7.3424</v>
+        <v>7.8224</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.88</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1456</v>
+        <v>-0.1302</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.3296</v>
+        <v>-2.0832</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.79</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2402</v>
+        <v>-0.2242</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.8432</v>
+        <v>-3.5872</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.51</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4921</v>
+        <v>-0.4898</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.8736</v>
+        <v>-7.8368</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.36</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.621</v>
+        <v>-0.6384</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.936</v>
+        <v>-10.2144</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>0.71</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.3056</v>
+        <v>-0.2929</v>
       </c>
       <c r="J142" t="n">
-        <v>-4.584</v>
+        <v>-4.3935</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.7</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.3147</v>
+        <v>-0.3022</v>
       </c>
       <c r="J143" t="n">
-        <v>-4.7205</v>
+        <v>-4.533</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.68</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3326</v>
+        <v>-0.3203</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.989</v>
+        <v>-4.8045</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.66</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3494</v>
+        <v>-0.3374</v>
       </c>
       <c r="J145" t="n">
-        <v>-5.241</v>
+        <v>-5.061</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.6</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4019</v>
+        <v>-0.3918</v>
       </c>
       <c r="J146" t="n">
-        <v>-6.0285</v>
+        <v>-5.877</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.83</v>
       </c>
       <c r="I147" t="n">
-        <v>1.3202</v>
+        <v>1.3244</v>
       </c>
       <c r="J147" t="n">
-        <v>19.803</v>
+        <v>19.866</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.56</v>
       </c>
       <c r="I148" t="n">
-        <v>0.9903</v>
+        <v>0.983</v>
       </c>
       <c r="J148" t="n">
-        <v>14.8545</v>
+        <v>14.745</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.47</v>
       </c>
       <c r="I149" t="n">
-        <v>0.8771</v>
+        <v>0.8698</v>
       </c>
       <c r="J149" t="n">
-        <v>13.1565</v>
+        <v>13.047</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.34</v>
       </c>
       <c r="I150" t="n">
-        <v>0.6996</v>
+        <v>0.6945</v>
       </c>
       <c r="J150" t="n">
-        <v>10.494</v>
+        <v>10.4175</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.33</v>
       </c>
       <c r="I151" t="n">
-        <v>0.6852</v>
+        <v>0.6804</v>
       </c>
       <c r="J151" t="n">
-        <v>10.278</v>
+        <v>10.206</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.44</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7311</v>
+        <v>0.701</v>
       </c>
       <c r="J152" t="n">
-        <v>16.0842</v>
+        <v>15.422</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.08</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2245</v>
+        <v>0.1803</v>
       </c>
       <c r="J153" t="n">
-        <v>4.939</v>
+        <v>3.9666</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.84</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2062</v>
+        <v>-0.186</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.5364</v>
+        <v>-4.092</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.67</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3694</v>
+        <v>-0.3559</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.126799999999999</v>
+        <v>-7.8298</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.66</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3785</v>
+        <v>-0.3657</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.327</v>
+        <v>-8.045400000000001</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.79</v>
       </c>
       <c r="I157" t="n">
-        <v>1.34</v>
+        <v>1.3494</v>
       </c>
       <c r="J157" t="n">
-        <v>29.48</v>
+        <v>29.6868</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.27</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6258</v>
+        <v>0.6146</v>
       </c>
       <c r="J158" t="n">
-        <v>13.7676</v>
+        <v>13.5212</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.26</v>
       </c>
       <c r="I159" t="n">
-        <v>0.6105</v>
+        <v>0.6001</v>
       </c>
       <c r="J159" t="n">
-        <v>13.431</v>
+        <v>13.2022</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.88</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4323</v>
+        <v>-0.3915</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.5106</v>
+        <v>-8.613</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.8</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6254</v>
+        <v>-0.5915</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.7588</v>
+        <v>-13.013</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.18</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3996</v>
+        <v>0.3434</v>
       </c>
       <c r="J162" t="n">
-        <v>11.988</v>
+        <v>10.302</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.15</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3466</v>
+        <v>0.2929</v>
       </c>
       <c r="J163" t="n">
-        <v>10.398</v>
+        <v>8.787000000000001</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.01</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0435</v>
+        <v>0.0294</v>
       </c>
       <c r="J164" t="n">
-        <v>1.305</v>
+        <v>0.882</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.96</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.0581</v>
       </c>
       <c r="J165" t="n">
-        <v>-2.172</v>
+        <v>-1.743</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3567</v>
+        <v>-0.3426</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.701</v>
+        <v>-10.278</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.4</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8391999999999999</v>
+        <v>0.8236</v>
       </c>
       <c r="J167" t="n">
-        <v>25.176</v>
+        <v>24.708</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.09</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2992</v>
+        <v>0.263</v>
       </c>
       <c r="J168" t="n">
-        <v>8.976000000000001</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.05</v>
       </c>
       <c r="I169" t="n">
-        <v>0.1869</v>
+        <v>0.158</v>
       </c>
       <c r="J169" t="n">
-        <v>5.607</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.97</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1526</v>
+        <v>-0.1214</v>
       </c>
       <c r="J170" t="n">
-        <v>-4.578</v>
+        <v>-3.642</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.97</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1526</v>
+        <v>-0.1214</v>
       </c>
       <c r="J171" t="n">
-        <v>-4.578</v>
+        <v>-3.642</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.97</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0467</v>
+        <v>-0.0373</v>
       </c>
       <c r="J172" t="n">
-        <v>-0.9807</v>
+        <v>-0.7833</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.97</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0467</v>
+        <v>-0.0373</v>
       </c>
       <c r="J173" t="n">
-        <v>-0.9807</v>
+        <v>-0.7833</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.96</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0614</v>
+        <v>-0.0505</v>
       </c>
       <c r="J174" t="n">
-        <v>-1.2894</v>
+        <v>-1.0605</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.95</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.0631</v>
       </c>
       <c r="J175" t="n">
-        <v>-1.5813</v>
+        <v>-1.3251</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.47</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5375</v>
+        <v>-0.5427</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.2875</v>
+        <v>-11.3967</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.96</v>
       </c>
       <c r="I177" t="n">
-        <v>1.5143</v>
+        <v>1.536</v>
       </c>
       <c r="J177" t="n">
-        <v>31.8003</v>
+        <v>32.256</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.67</v>
       </c>
       <c r="I178" t="n">
-        <v>1.1555</v>
+        <v>1.1493</v>
       </c>
       <c r="J178" t="n">
-        <v>24.2655</v>
+        <v>24.1353</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.1</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2898</v>
+        <v>0.2582</v>
       </c>
       <c r="J179" t="n">
-        <v>6.0858</v>
+        <v>5.4222</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.03</v>
       </c>
       <c r="I180" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0619</v>
       </c>
       <c r="J180" t="n">
-        <v>1.7451</v>
+        <v>1.2999</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.87</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4781</v>
+        <v>-0.4416</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.0401</v>
+        <v>-9.2736</v>
       </c>
     </row>
   </sheetData>
